--- a/output/yearly_surface_area_iteration_24_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_24_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.8449765829449</v>
+        <v>10.84497622078869</v>
       </c>
       <c r="C21" t="n">
-        <v>37.78907281557191</v>
+        <v>37.78907155364685</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.982369599052562</v>
+        <v>5.668611244321084</v>
       </c>
       <c r="C2" t="n">
-        <v>7.009678608322226</v>
+        <v>4.716315971201677</v>
       </c>
       <c r="D2" t="n">
-        <v>19.41798784229766</v>
+        <v>19.57801271808989</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.49474408967816</v>
+        <v>18.67284133477433</v>
       </c>
       <c r="C3" t="n">
-        <v>22.05005343738336</v>
+        <v>18.94282195344221</v>
       </c>
       <c r="D3" t="n">
-        <v>66.01271563355553</v>
+        <v>64.09339887175302</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>34.90603962449534</v>
+        <v>39.38575439897354</v>
       </c>
       <c r="C4" t="n">
-        <v>75.89989676302515</v>
+        <v>55.37744275344983</v>
       </c>
       <c r="D4" t="n">
-        <v>85.86758120424302</v>
+        <v>82.26849412047422</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>43.6632291463769</v>
+        <v>50.04458922398117</v>
       </c>
       <c r="C5" t="n">
-        <v>114.594500778209</v>
+        <v>80.57694282605698</v>
       </c>
       <c r="D5" t="n">
-        <v>66.75884388878312</v>
+        <v>64.15721247252907</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>38.07806645691679</v>
+        <v>47.77871552257953</v>
       </c>
       <c r="C6" t="n">
-        <v>107.8744377426395</v>
+        <v>71.88945739117695</v>
       </c>
       <c r="D6" t="n">
-        <v>48.5434969841878</v>
+        <v>46.41015922285948</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>26.70942804173872</v>
+        <v>33.65627479698915</v>
       </c>
       <c r="C7" t="n">
-        <v>90.18923459833748</v>
+        <v>57.31148573081605</v>
       </c>
       <c r="D7" t="n">
-        <v>40.00425545264903</v>
+        <v>40.36357511240336</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>14.18625432636641</v>
+        <v>18.19178495969339</v>
       </c>
       <c r="C8" t="n">
-        <v>63.42090169434395</v>
+        <v>43.47669708257</v>
       </c>
       <c r="D8" t="n">
-        <v>36.30012136452581</v>
+        <v>36.55046702910875</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>7.543749359432489</v>
+        <v>8.542186774651494</v>
       </c>
       <c r="C9" t="n">
-        <v>39.04999668412111</v>
+        <v>32.06093477758807</v>
       </c>
       <c r="D9" t="n">
-        <v>34.16874709860598</v>
+        <v>34.39062207976576</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.409429850399925</v>
+        <v>5.694136684631501</v>
       </c>
       <c r="C10" t="n">
-        <v>30.46363126277853</v>
+        <v>29.75186417719959</v>
       </c>
       <c r="D10" t="n">
-        <v>35.01894061048373</v>
+        <v>35.58835427894688</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.620104696185489</v>
+        <v>4.797801030654161</v>
       </c>
       <c r="C11" t="n">
-        <v>30.03068052520567</v>
+        <v>29.852984190737</v>
       </c>
       <c r="D11" t="n">
-        <v>36.60544490054656</v>
+        <v>35.7169632282032</v>
       </c>
     </row>
     <row r="12">
@@ -920,13 +920,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.688426124855267</v>
+        <v>3.905392367493811</v>
       </c>
       <c r="C12" t="n">
-        <v>27.98864530037232</v>
+        <v>28.63954402828795</v>
       </c>
       <c r="D12" t="n">
-        <v>34.28066633689012</v>
+        <v>35.58246379272139</v>
       </c>
     </row>
     <row r="13">
@@ -937,10 +937,10 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>25.75615102091507</v>
+        <v>26.27647730416588</v>
       </c>
       <c r="D13" t="n">
-        <v>32.780555844801</v>
+        <v>32.5203927031756</v>
       </c>
     </row>
     <row r="14">
@@ -954,7 +954,7 @@
         <v>23.96838845148163</v>
       </c>
       <c r="D14" t="n">
-        <v>31.03599017435442</v>
+        <v>30.72870314292517</v>
       </c>
     </row>
     <row r="15">
@@ -965,10 +965,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>21.50027472300514</v>
+        <v>21.85861263505523</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>29.38370878810703</v>
       </c>
     </row>
     <row r="16">
@@ -979,10 +979,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>19.01252604044373</v>
+        <v>19.42584182393164</v>
       </c>
       <c r="D16" t="n">
-        <v>27.27884171020187</v>
+        <v>26.86552592671396</v>
       </c>
     </row>
     <row r="17">
@@ -993,7 +993,7 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>17.9443845382232</v>
+        <v>18.41660518396592</v>
       </c>
       <c r="D17" t="n">
         <v>24.55547357862122</v>
@@ -1010,7 +1010,7 @@
         <v>18.1917849596934</v>
       </c>
       <c r="D18" t="n">
-        <v>21.40209995258047</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.702372374389972</v>
+        <v>7.730355042985162</v>
       </c>
       <c r="C21" t="n">
-        <v>95.31685813307591</v>
+        <v>96.62943803731453</v>
       </c>
       <c r="D21" t="n">
-        <v>8.665168921188718</v>
+        <v>8.696649423358307</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.615016031215008</v>
+        <v>7.162831250184728</v>
       </c>
       <c r="C2" t="n">
-        <v>6.696501090667494</v>
+        <v>7.215845626214056</v>
       </c>
       <c r="D2" t="n">
-        <v>25.35657970528662</v>
+        <v>18.16625951938298</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.01368771459722</v>
+        <v>19.10971906316416</v>
       </c>
       <c r="C3" t="n">
-        <v>24.67131980772234</v>
+        <v>18.54521413322225</v>
       </c>
       <c r="D3" t="n">
-        <v>65.80163987714246</v>
+        <v>64.54991155422778</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>33.82120841130262</v>
+        <v>37.31819373382976</v>
       </c>
       <c r="C4" t="n">
-        <v>65.21749999311561</v>
+        <v>50.56589725493621</v>
       </c>
       <c r="D4" t="n">
-        <v>96.42235077260048</v>
+        <v>93.55073873767856</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>47.63930734857648</v>
+        <v>54.5606286635165</v>
       </c>
       <c r="C5" t="n">
-        <v>125.8600556844411</v>
+        <v>91.81795403968295</v>
       </c>
       <c r="D5" t="n">
-        <v>80.77329236690633</v>
+        <v>78.44164156932015</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>48.26173539306896</v>
+        <v>58.32464936159877</v>
       </c>
       <c r="C6" t="n">
-        <v>143.6581598147316</v>
+        <v>99.34108669732626</v>
       </c>
       <c r="D6" t="n">
-        <v>56.75483478250812</v>
+        <v>55.34602682691394</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>35.39298648580176</v>
+        <v>45.21439051908685</v>
       </c>
       <c r="C7" t="n">
-        <v>120.9110655073329</v>
+        <v>81.08646988456105</v>
       </c>
       <c r="D7" t="n">
-        <v>44.6155244194963</v>
+        <v>44.01665831990574</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>21.11248437982766</v>
+        <v>27.45457454926205</v>
       </c>
       <c r="C8" t="n">
-        <v>90.79202768874502</v>
+        <v>60.16640805476577</v>
       </c>
       <c r="D8" t="n">
-        <v>38.38633523605029</v>
+        <v>39.22082078466007</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.87187407682917</v>
+        <v>13.31249886958674</v>
       </c>
       <c r="C9" t="n">
-        <v>57.68749510154256</v>
+        <v>43.04374634499714</v>
       </c>
       <c r="D9" t="n">
-        <v>35.83280945730432</v>
+        <v>35.72187196672443</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6.26355035309465</v>
+        <v>6.975317438673588</v>
       </c>
       <c r="C10" t="n">
-        <v>38.43542262126263</v>
+        <v>34.59188035913637</v>
       </c>
       <c r="D10" t="n">
-        <v>35.44600086183109</v>
+        <v>36.44247478164161</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.797801030654161</v>
+        <v>5.153193699591506</v>
       </c>
       <c r="C11" t="n">
-        <v>32.69612554223576</v>
+        <v>32.51842920776709</v>
       </c>
       <c r="D11" t="n">
-        <v>37.13853390395258</v>
+        <v>36.07235589714055</v>
       </c>
     </row>
     <row r="12">
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.905392367493811</v>
+        <v>4.122358610132356</v>
       </c>
       <c r="C12" t="n">
-        <v>31.24313893995049</v>
+        <v>31.67707142522758</v>
       </c>
       <c r="D12" t="n">
-        <v>34.71459882216721</v>
+        <v>36.23336252063703</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>3.121957699504857</v>
       </c>
       <c r="C13" t="n">
-        <v>28.09761929554372</v>
+        <v>29.13827186204534</v>
       </c>
       <c r="D13" t="n">
-        <v>33.30088212805181</v>
+        <v>33.04071898642641</v>
       </c>
     </row>
     <row r="14">
@@ -1276,10 +1276,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>23.29196428325557</v>
+        <v>23.65030219530566</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>29.74204670015712</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>20.66578917439536</v>
+        <v>21.07910495788326</v>
       </c>
       <c r="D16" t="n">
-        <v>27.27884171020187</v>
+        <v>26.86552592671396</v>
       </c>
     </row>
     <row r="17">
@@ -1304,7 +1304,7 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>18.88882582970863</v>
+        <v>19.36104647545135</v>
       </c>
       <c r="D17" t="n">
         <v>24.55547357862122</v>
@@ -1321,7 +1321,7 @@
         <v>18.72683745850791</v>
       </c>
       <c r="D18" t="n">
-        <v>21.40209995258047</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.887141459889282</v>
+        <v>7.925883625523781</v>
       </c>
       <c r="C21" t="n">
-        <v>104.504624343533</v>
+        <v>106.0086934913806</v>
       </c>
       <c r="D21" t="n">
-        <v>9.858926824861603</v>
+        <v>9.907354531904726</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.514296928305087</v>
+        <v>9.534733703645022</v>
       </c>
       <c r="C2" t="n">
-        <v>7.314020396638737</v>
+        <v>12.36805757810132</v>
       </c>
       <c r="D2" t="n">
-        <v>28.94094057349172</v>
+        <v>19.52598008976481</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.15880644837651</v>
+        <v>21.35301256736813</v>
       </c>
       <c r="C3" t="n">
-        <v>25.13764996723958</v>
+        <v>23.21833320543707</v>
       </c>
       <c r="D3" t="n">
-        <v>69.28684422721864</v>
+        <v>63.78414834491527</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>32.55769911593697</v>
+        <v>36.42480332296516</v>
       </c>
       <c r="C4" t="n">
-        <v>63.36690557061038</v>
+        <v>47.92401418280805</v>
       </c>
       <c r="D4" t="n">
-        <v>104.9478478362798</v>
+        <v>102.8164735703599</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>49.21010367537139</v>
+        <v>55.19876467127693</v>
       </c>
       <c r="C5" t="n">
-        <v>121.8348900970292</v>
+        <v>92.40700266223104</v>
       </c>
       <c r="D5" t="n">
-        <v>92.60335220308041</v>
+        <v>90.88529372064848</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>54.94351026817275</v>
+        <v>66.17372225705202</v>
       </c>
       <c r="C6" t="n">
-        <v>168.8154447360561</v>
+        <v>120.0304378166235</v>
       </c>
       <c r="D6" t="n">
-        <v>66.89825206278616</v>
+        <v>65.85170901005907</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>44.79518424937346</v>
+        <v>56.35329997147116</v>
       </c>
       <c r="C7" t="n">
-        <v>157.8611038520701</v>
+        <v>109.6523828350305</v>
       </c>
       <c r="D7" t="n">
-        <v>49.1669067763845</v>
+        <v>48.74770050667112</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>28.53940576245478</v>
+        <v>37.38495257771854</v>
       </c>
       <c r="C8" t="n">
-        <v>121.0004045484194</v>
+        <v>82.86441497695203</v>
       </c>
       <c r="D8" t="n">
-        <v>41.22358610132356</v>
+        <v>42.05807164993335</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>15.42031119060464</v>
+        <v>19.96874830438012</v>
       </c>
       <c r="C9" t="n">
-        <v>82.31561801027804</v>
+        <v>57.79843259212245</v>
       </c>
       <c r="D9" t="n">
-        <v>36.94218436310322</v>
+        <v>37.16405934426299</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7.971791358484101</v>
+        <v>9.537678946757763</v>
       </c>
       <c r="C10" t="n">
-        <v>51.24723016168351</v>
+        <v>42.84837855185204</v>
       </c>
       <c r="D10" t="n">
-        <v>36.30012136452581</v>
+        <v>37.29659528433633</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>5.153193699591506</v>
+        <v>5.686282702997524</v>
       </c>
       <c r="C11" t="n">
-        <v>38.20471191076462</v>
+        <v>36.25005223160922</v>
       </c>
       <c r="D11" t="n">
-        <v>37.13853390395258</v>
+        <v>36.42774856607789</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4.122358610132356</v>
+        <v>4.339324852770901</v>
       </c>
       <c r="C12" t="n">
-        <v>33.84673385161303</v>
+        <v>34.49763257952867</v>
       </c>
       <c r="D12" t="n">
-        <v>35.58246379272139</v>
+        <v>36.66729500591412</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.121957699504857</v>
+        <v>3.382120841130262</v>
       </c>
       <c r="C13" t="n">
-        <v>30.69925071179776</v>
+        <v>31.73990327829938</v>
       </c>
       <c r="D13" t="n">
-        <v>33.30088212805181</v>
+        <v>33.56104526967722</v>
       </c>
     </row>
     <row r="14">
@@ -1573,7 +1573,7 @@
         <v>2.151009220004762</v>
       </c>
       <c r="C14" t="n">
-        <v>28.27040689149115</v>
+        <v>28.88498095434966</v>
       </c>
       <c r="D14" t="n">
         <v>31.65056423721292</v>
@@ -1587,10 +1587,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>25.083653843506</v>
+        <v>25.44199175555609</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>29.74204670015712</v>
       </c>
     </row>
     <row r="16">
@@ -1601,7 +1601,7 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>22.31905230834699</v>
+        <v>22.7323680918349</v>
       </c>
       <c r="D16" t="n">
         <v>27.27884171020187</v>
@@ -1615,7 +1615,7 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>19.83326712119407</v>
+        <v>20.30548776693678</v>
       </c>
       <c r="D17" t="n">
         <v>24.55547357862122</v>
@@ -1629,10 +1629,10 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>18.72683745850791</v>
+        <v>19.26188995732242</v>
       </c>
       <c r="D18" t="n">
-        <v>21.40209995258047</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -1643,7 +1643,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>19.25796296650543</v>
+        <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
         <v>16.24890625298896</v>
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8.056569565897146</v>
+        <v>8.107836240710899</v>
       </c>
       <c r="C21" t="n">
-        <v>112.79197392256</v>
+        <v>114.5231869000414</v>
       </c>
       <c r="D21" t="n">
-        <v>11.07778315310857</v>
+        <v>11.14827483097748</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.835909264670541</v>
+        <v>8.44008501340983</v>
       </c>
       <c r="C2" t="n">
-        <v>4.914629007459533</v>
+        <v>8.014006509766713</v>
       </c>
       <c r="D2" t="n">
-        <v>23.6846633649543</v>
+        <v>15.83166347868406</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>22.90908267859932</v>
+        <v>26.12430641000763</v>
       </c>
       <c r="C3" t="n">
-        <v>38.40106145161399</v>
+        <v>38.58759351542088</v>
       </c>
       <c r="D3" t="n">
-        <v>75.86455384567226</v>
+        <v>71.56449890107125</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>23.63655772744621</v>
+        <v>26.52093248252334</v>
       </c>
       <c r="C4" t="n">
-        <v>96.70313061601506</v>
+        <v>74.18969226222723</v>
       </c>
       <c r="D4" t="n">
-        <v>102.331490204462</v>
+        <v>100.8510146664578</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>30.9495963763807</v>
+        <v>37.28186906877263</v>
       </c>
       <c r="C5" t="n">
-        <v>100.8745766113598</v>
+        <v>71.71666979522951</v>
       </c>
       <c r="D5" t="n">
-        <v>65.75255249193013</v>
+        <v>65.50711556586843</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>27.81389420901639</v>
+        <v>34.97868895460962</v>
       </c>
       <c r="C6" t="n">
-        <v>103.97002712285</v>
+        <v>72.2114706381699</v>
       </c>
       <c r="D6" t="n">
-        <v>32.36233132279187</v>
+        <v>32.08056973167303</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>18.92416874706152</v>
+        <v>24.73316991308989</v>
       </c>
       <c r="C7" t="n">
-        <v>85.09887275181777</v>
+        <v>58.26967149016093</v>
       </c>
       <c r="D7" t="n">
-        <v>28.98511922018283</v>
+        <v>29.52409870981433</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.6814150222053</v>
+        <v>13.85246010692249</v>
       </c>
       <c r="C8" t="n">
-        <v>60.66709938393165</v>
+        <v>42.55876297909923</v>
       </c>
       <c r="D8" t="n">
-        <v>27.20422888467911</v>
+        <v>27.37112599440107</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.657812019574366</v>
+        <v>6.767186925373262</v>
       </c>
       <c r="C9" t="n">
-        <v>39.04999668412111</v>
+        <v>32.61562223048752</v>
       </c>
       <c r="D9" t="n">
-        <v>27.62343515439249</v>
+        <v>28.39999758845172</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3.701188845010476</v>
+        <v>4.128249096357838</v>
       </c>
       <c r="C10" t="n">
-        <v>29.89421759431538</v>
+        <v>28.32833000604172</v>
       </c>
       <c r="D10" t="n">
-        <v>29.04009709162065</v>
+        <v>28.47068342315751</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.020837685967435</v>
+        <v>3.198534020436107</v>
       </c>
       <c r="C11" t="n">
-        <v>27.00984283923824</v>
+        <v>27.54293184264426</v>
       </c>
       <c r="D11" t="n">
-        <v>28.43141351498762</v>
+        <v>29.31989518733098</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.386628669023996</v>
+        <v>2.603594911662541</v>
       </c>
       <c r="C12" t="n">
-        <v>24.95111790343269</v>
+        <v>25.81898287398687</v>
       </c>
       <c r="D12" t="n">
-        <v>27.12078032981814</v>
+        <v>27.33774657245668</v>
       </c>
     </row>
     <row r="13">
@@ -1870,7 +1870,7 @@
         <v>1.560978849752429</v>
       </c>
       <c r="C13" t="n">
-        <v>23.41468274628643</v>
+        <v>23.93500902953724</v>
       </c>
       <c r="D13" t="n">
         <v>26.01631416254048</v>
@@ -1884,10 +1884,10 @@
         <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>20.89551813718911</v>
+        <v>21.20280516861837</v>
       </c>
       <c r="D14" t="n">
-        <v>23.66110142005238</v>
+        <v>24.89024954576939</v>
       </c>
     </row>
     <row r="15">
@@ -1898,7 +1898,7 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>18.63357142660446</v>
+        <v>18.99190933865455</v>
       </c>
       <c r="D15" t="n">
         <v>22.93362637120549</v>
@@ -1912,7 +1912,7 @@
         <v>0.4133157834879072</v>
       </c>
       <c r="C16" t="n">
-        <v>16.94594712300419</v>
+        <v>17.3592629064921</v>
       </c>
       <c r="D16" t="n">
         <v>20.66578917439536</v>
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>16.05550195525234</v>
+        <v>16.52772260099505</v>
       </c>
       <c r="D17" t="n">
-        <v>18.41660518396592</v>
+        <v>17.9443845382232</v>
       </c>
     </row>
     <row r="18">
@@ -1940,7 +1940,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>16.58662746324986</v>
+        <v>16.05157496443535</v>
       </c>
       <c r="D18" t="n">
         <v>13.9113649691773</v>
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.193044444838127</v>
+        <v>5.029493488856409</v>
       </c>
       <c r="C2" t="n">
-        <v>2.282563412373834</v>
+        <v>3.549999698556466</v>
       </c>
       <c r="D2" t="n">
-        <v>17.0824100538945</v>
+        <v>12.33565990386117</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>23.89573912136737</v>
+        <v>28.53940576245478</v>
       </c>
       <c r="C3" t="n">
-        <v>28.84865628929252</v>
+        <v>35.41163969218245</v>
       </c>
       <c r="D3" t="n">
-        <v>77.27827053978768</v>
+        <v>68.41799750896023</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>32.65980087717864</v>
+        <v>37.6755498981756</v>
       </c>
       <c r="C4" t="n">
-        <v>99.90657337497241</v>
+        <v>88.53498971668159</v>
       </c>
       <c r="D4" t="n">
-        <v>115.7578718077414</v>
+        <v>113.6264975418216</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>34.65569395991241</v>
+        <v>41.08614142272902</v>
       </c>
       <c r="C5" t="n">
-        <v>139.5554361586841</v>
+        <v>104.9979169691964</v>
       </c>
       <c r="D5" t="n">
-        <v>81.36234098945442</v>
+        <v>82.02502068982102</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>33.40887437551896</v>
+        <v>42.38499363544755</v>
       </c>
       <c r="C6" t="n">
-        <v>131.0996431820063</v>
+        <v>92.86057010159307</v>
       </c>
       <c r="D6" t="n">
-        <v>40.13090090649688</v>
+        <v>40.57366912111219</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>18.02586959767568</v>
+        <v>24.07441720354028</v>
       </c>
       <c r="C7" t="n">
-        <v>112.347280283188</v>
+        <v>78.27179921648545</v>
       </c>
       <c r="D7" t="n">
-        <v>31.68001666834032</v>
+        <v>32.15910954801276</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.012443924985718</v>
+        <v>11.59934912567606</v>
       </c>
       <c r="C8" t="n">
-        <v>79.94371555681776</v>
+        <v>56.24432597629976</v>
       </c>
       <c r="D8" t="n">
-        <v>28.37250865273282</v>
+        <v>29.12354564648163</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.548437113775471</v>
+        <v>5.324999547834698</v>
       </c>
       <c r="C9" t="n">
-        <v>44.81874619427537</v>
+        <v>39.04999668412111</v>
       </c>
       <c r="D9" t="n">
-        <v>28.6218725696115</v>
+        <v>29.28749751309084</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.135301256736813</v>
+        <v>2.420008090968388</v>
       </c>
       <c r="C10" t="n">
-        <v>32.74128593663113</v>
+        <v>32.02951885105219</v>
       </c>
       <c r="D10" t="n">
-        <v>30.17892442854695</v>
+        <v>30.03657101143117</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.776963344686726</v>
+        <v>1.954659679155399</v>
       </c>
       <c r="C11" t="n">
-        <v>29.852984190737</v>
+        <v>31.09685853201771</v>
       </c>
       <c r="D11" t="n">
-        <v>29.49759152179966</v>
+        <v>30.20837685967435</v>
       </c>
     </row>
     <row r="12">
@@ -2167,10 +2167,10 @@
         <v>1.084831213192725</v>
       </c>
       <c r="C12" t="n">
-        <v>21.69662426385451</v>
+        <v>22.56448923440869</v>
       </c>
       <c r="D12" t="n">
-        <v>28.63954402828795</v>
+        <v>28.8565102709265</v>
       </c>
     </row>
     <row r="13">
@@ -2181,10 +2181,10 @@
         <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>17.17076734727672</v>
+        <v>17.43093048890212</v>
       </c>
       <c r="D13" t="n">
-        <v>25.23582473766426</v>
+        <v>26.27647730416588</v>
       </c>
     </row>
     <row r="14">
@@ -2195,7 +2195,7 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>15.36435157146258</v>
+        <v>15.67163860289184</v>
       </c>
       <c r="D14" t="n">
         <v>19.0517959486136</v>
@@ -2209,7 +2209,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>14.33351648200343</v>
+        <v>14.69185439405351</v>
       </c>
       <c r="D15" t="n">
         <v>17.5585576904542</v>
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>13.63942085510094</v>
+        <v>14.05273663858884</v>
       </c>
       <c r="D16" t="n">
-        <v>15.70599977254047</v>
+        <v>15.29268398905256</v>
       </c>
     </row>
     <row r="17">
@@ -2237,7 +2237,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>14.16661937228147</v>
+        <v>13.69439872653876</v>
       </c>
       <c r="D17" t="n">
         <v>11.8055161435679</v>
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.541564879845745</v>
+        <v>5.816855147662351</v>
       </c>
       <c r="C2" t="n">
-        <v>5.148284961070273</v>
+        <v>3.265292864324891</v>
       </c>
       <c r="D2" t="n">
-        <v>23.28214680621311</v>
+        <v>16.12226079914112</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.98209186161208</v>
+        <v>22.86981277042945</v>
       </c>
       <c r="C3" t="n">
-        <v>18.12797135891735</v>
+        <v>23.10543221944868</v>
       </c>
       <c r="D3" t="n">
-        <v>73.1303864893449</v>
+        <v>63.22946089201582</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>39.44956799974958</v>
+        <v>46.43077592464865</v>
       </c>
       <c r="C4" t="n">
-        <v>85.39536055850031</v>
+        <v>89.40285468723579</v>
       </c>
       <c r="D4" t="n">
-        <v>126.9507773838593</v>
+        <v>121.2713669147915</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>41.57701527485243</v>
+        <v>49.06284151973436</v>
       </c>
       <c r="C5" t="n">
-        <v>161.8656527376929</v>
+        <v>135.3830084156352</v>
       </c>
       <c r="D5" t="n">
-        <v>101.9299553934251</v>
+        <v>100.9972950743906</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>40.09064925062275</v>
+        <v>49.71079500453725</v>
       </c>
       <c r="C6" t="n">
-        <v>176.1009944492716</v>
+        <v>130.8581332467616</v>
       </c>
       <c r="D6" t="n">
-        <v>53.89696721544566</v>
+        <v>55.74854338565514</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>26.76931465169778</v>
+        <v>35.69241953559704</v>
       </c>
       <c r="C7" t="n">
-        <v>149.8362981175567</v>
+        <v>106.5382791171596</v>
       </c>
       <c r="D7" t="n">
-        <v>35.45287309576081</v>
+        <v>35.93196597543326</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>13.18487166803466</v>
+        <v>17.35729941108361</v>
       </c>
       <c r="C8" t="n">
-        <v>112.1548577331556</v>
+        <v>79.52647278251287</v>
       </c>
       <c r="D8" t="n">
-        <v>30.45872252425729</v>
+        <v>30.95941385342316</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.101561981893925</v>
+        <v>7.654686850012379</v>
       </c>
       <c r="C9" t="n">
-        <v>68.67030666895162</v>
+        <v>53.69374544066654</v>
       </c>
       <c r="D9" t="n">
-        <v>29.39843500367073</v>
+        <v>30.17499743772996</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.704714925199962</v>
+        <v>3.131775176547325</v>
       </c>
       <c r="C10" t="n">
-        <v>41.99425804915732</v>
+        <v>39.28954312395736</v>
       </c>
       <c r="D10" t="n">
-        <v>30.7483380970101</v>
+        <v>30.89069151412589</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.776963344686726</v>
+        <v>1.954659679155399</v>
       </c>
       <c r="C11" t="n">
-        <v>33.7623035490478</v>
+        <v>34.65078522139116</v>
       </c>
       <c r="D11" t="n">
-        <v>30.03068052520567</v>
+        <v>30.74146586308036</v>
       </c>
     </row>
     <row r="12">
@@ -2478,10 +2478,10 @@
         <v>1.084831213192725</v>
       </c>
       <c r="C12" t="n">
-        <v>26.25291535926396</v>
+        <v>27.55471281509523</v>
       </c>
       <c r="D12" t="n">
-        <v>29.07347651356504</v>
+        <v>29.29044275620359</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>19.51223562190536</v>
+        <v>20.29272504678157</v>
       </c>
       <c r="D13" t="n">
-        <v>25.49598787928967</v>
+        <v>26.79680358741669</v>
       </c>
     </row>
     <row r="14">
@@ -2520,7 +2520,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>15.76686813020377</v>
+        <v>16.12520604225386</v>
       </c>
       <c r="D15" t="n">
         <v>17.5585576904542</v>
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
+        <v>15.70599977254047</v>
+      </c>
+      <c r="D16" t="n">
         <v>14.87936820556466</v>
-      </c>
-      <c r="D16" t="n">
-        <v>15.29268398905256</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>15.11106066376691</v>
+        <v>14.63884001802419</v>
       </c>
       <c r="D17" t="n">
-        <v>11.33329549782518</v>
+        <v>10.86107485208246</v>
       </c>
     </row>
     <row r="18">
@@ -2562,7 +2562,7 @@
         <v>3.21031499288707</v>
       </c>
       <c r="C18" t="n">
-        <v>35.31346492175777</v>
+        <v>34.77841242294325</v>
       </c>
       <c r="D18" t="n">
         <v>6.955682484588652</v>
@@ -2576,7 +2576,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>35.50686921949439</v>
+        <v>36.10868056219768</v>
       </c>
       <c r="D19" t="n">
         <v>4.212679398923063</v>
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.66249977391735</v>
+        <v>3.347759671481624</v>
       </c>
       <c r="C2" t="n">
-        <v>2.384665173615502</v>
+        <v>1.442187377538564</v>
       </c>
       <c r="D2" t="n">
-        <v>16.09379011571796</v>
+        <v>11.00833700771949</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.19316761802514</v>
+        <v>23.61594102565702</v>
       </c>
       <c r="C3" t="n">
-        <v>20.16509784522949</v>
+        <v>19.75767254796706</v>
       </c>
       <c r="D3" t="n">
-        <v>76.21798301920113</v>
+        <v>63.69579105153306</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>43.71231653158923</v>
+        <v>52.17399999449249</v>
       </c>
       <c r="C4" t="n">
-        <v>78.95018688012</v>
+        <v>86.27598824920969</v>
       </c>
       <c r="D4" t="n">
-        <v>135.2465454847449</v>
+        <v>129.1204398102448</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>43.54051068334605</v>
+        <v>52.44987109938586</v>
       </c>
       <c r="C5" t="n">
-        <v>184.9612674800991</v>
+        <v>161.0802545742954</v>
       </c>
       <c r="D5" t="n">
-        <v>110.4466167277662</v>
+        <v>109.2439757900639</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>33.2881194078966</v>
+        <v>43.75354993516761</v>
       </c>
       <c r="C6" t="n">
-        <v>214.0985575944402</v>
+        <v>165.1927957073853</v>
       </c>
       <c r="D6" t="n">
-        <v>53.13218575383738</v>
+        <v>54.82275530055039</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.683558444063037</v>
+        <v>11.49822911213864</v>
       </c>
       <c r="C7" t="n">
-        <v>154.9266599640764</v>
+        <v>111.0297748640888</v>
       </c>
       <c r="D7" t="n">
-        <v>35.57264631567892</v>
+        <v>36.11162580531042</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.172427743048944</v>
+        <v>5.257258956241669</v>
       </c>
       <c r="C8" t="n">
-        <v>85.78511439708629</v>
+        <v>66.00780689503429</v>
       </c>
       <c r="D8" t="n">
-        <v>31.96079651175491</v>
+        <v>32.62838495064274</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.885937339858122</v>
+        <v>2.218749811597791</v>
       </c>
       <c r="C9" t="n">
-        <v>32.06093477758807</v>
+        <v>29.95312245657017</v>
       </c>
       <c r="D9" t="n">
-        <v>32.39374724932775</v>
+        <v>32.72655972106742</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.281180754042088</v>
+        <v>1.423534171157875</v>
       </c>
       <c r="C10" t="n">
-        <v>26.47773558353648</v>
+        <v>27.18950266911542</v>
       </c>
       <c r="D10" t="n">
-        <v>23.48831382410494</v>
+        <v>24.05772749256809</v>
       </c>
     </row>
     <row r="11">
@@ -2775,10 +2775,10 @@
         <v>0.7107853378746906</v>
       </c>
       <c r="C11" t="n">
-        <v>20.96816746730337</v>
+        <v>22.0343454741154</v>
       </c>
       <c r="D11" t="n">
-        <v>23.27821981539612</v>
+        <v>23.45591614986479</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>15.83853571261379</v>
+        <v>16.48943444052943</v>
       </c>
       <c r="D12" t="n">
-        <v>20.82875929330033</v>
+        <v>21.69662426385451</v>
       </c>
     </row>
     <row r="13">
@@ -2817,7 +2817,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>13.21334235145782</v>
+        <v>13.52062938288707</v>
       </c>
       <c r="D14" t="n">
         <v>14.74977750860408</v>
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
+        <v>13.25850274585317</v>
+      </c>
+      <c r="D15" t="n">
         <v>12.541826921753</v>
-      </c>
-      <c r="D15" t="n">
-        <v>12.90016483380309</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>12.81278928812512</v>
+        <v>12.39947350463721</v>
       </c>
       <c r="D16" t="n">
-        <v>9.506263020221864</v>
+        <v>9.092947236733956</v>
       </c>
     </row>
     <row r="17">
@@ -2859,7 +2859,7 @@
         <v>2.361103228713579</v>
       </c>
       <c r="C17" t="n">
-        <v>30.22212132753381</v>
+        <v>29.7499006817911</v>
       </c>
       <c r="D17" t="n">
         <v>5.66664774891259</v>
@@ -2873,7 +2873,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>30.49799243242716</v>
+        <v>31.03304493124168</v>
       </c>
       <c r="D18" t="n">
         <v>3.21031499288707</v>
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.516620276612075</v>
+        <v>4.389393985687489</v>
       </c>
       <c r="C2" t="n">
-        <v>4.505240214788612</v>
+        <v>4.995132319207771</v>
       </c>
       <c r="D2" t="n">
-        <v>16.46685424333175</v>
+        <v>11.13203721845458</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.28442909679109</v>
+        <v>17.5585576904542</v>
       </c>
       <c r="C3" t="n">
-        <v>14.53968349989526</v>
+        <v>12.02640937702343</v>
       </c>
       <c r="D3" t="n">
-        <v>71.6724911485384</v>
+        <v>58.06546796767761</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>40.45782289201105</v>
+        <v>49.53211692236432</v>
       </c>
       <c r="C4" t="n">
-        <v>64.56660126519998</v>
+        <v>67.54031506136356</v>
       </c>
       <c r="D4" t="n">
-        <v>141.3981765995553</v>
+        <v>131.4943057591135</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>53.43161880363267</v>
+        <v>64.45173678380311</v>
       </c>
       <c r="C5" t="n">
-        <v>167.6088768075367</v>
+        <v>161.595672119025</v>
       </c>
       <c r="D5" t="n">
-        <v>130.0570271200962</v>
+        <v>129.6643280383975</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>43.91455655866408</v>
+        <v>55.30577517103983</v>
       </c>
       <c r="C6" t="n">
-        <v>252.6998955777206</v>
+        <v>209.8318820717836</v>
       </c>
       <c r="D6" t="n">
-        <v>71.3661858648134</v>
+        <v>71.96996070292518</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>19.04394196697963</v>
+        <v>26.11056194214817</v>
       </c>
       <c r="C7" t="n">
-        <v>225.2335400560075</v>
+        <v>171.2158178729395</v>
       </c>
       <c r="D7" t="n">
-        <v>40.72289477215769</v>
+        <v>42.27994663109313</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.674501730546564</v>
+        <v>7.510369937488099</v>
       </c>
       <c r="C8" t="n">
-        <v>135.8542473136736</v>
+        <v>101.9741340401162</v>
       </c>
       <c r="D8" t="n">
-        <v>33.96356182841841</v>
+        <v>34.63115026730623</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.32968730217768</v>
+        <v>2.884374755077128</v>
       </c>
       <c r="C9" t="n">
-        <v>60.23905738488002</v>
+        <v>51.14218315732908</v>
       </c>
       <c r="D9" t="n">
-        <v>33.61405964570653</v>
+        <v>33.72499713628642</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.281180754042088</v>
+        <v>1.565887588273662</v>
       </c>
       <c r="C10" t="n">
         <v>31.60245859970483</v>
       </c>
       <c r="D10" t="n">
-        <v>24.62714116103124</v>
+        <v>25.62361508084176</v>
       </c>
     </row>
     <row r="11">
@@ -3086,10 +3086,10 @@
         <v>0.5330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>24.6997904911455</v>
+        <v>25.9436648324262</v>
       </c>
       <c r="D11" t="n">
-        <v>23.98900515327081</v>
+        <v>24.16670148773948</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>18.22516438163779</v>
+        <v>19.09302935219197</v>
       </c>
       <c r="D12" t="n">
-        <v>21.26269177857742</v>
+        <v>22.34752299177014</v>
       </c>
     </row>
     <row r="13">
@@ -3114,7 +3114,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>16.1301147807751</v>
+        <v>16.3902779224005</v>
       </c>
       <c r="D13" t="n">
         <v>16.3902779224005</v>
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>14.13520344574558</v>
+        <v>14.44249047717483</v>
       </c>
       <c r="D14" t="n">
-        <v>14.74977750860408</v>
+        <v>14.44249047717483</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>13.61684065790326</v>
+        <v>14.33351648200343</v>
       </c>
       <c r="D15" t="n">
-        <v>12.18348900970292</v>
+        <v>11.82515109765283</v>
       </c>
     </row>
     <row r="16">
@@ -3156,7 +3156,7 @@
         <v>1.653263133951629</v>
       </c>
       <c r="C16" t="n">
-        <v>24.38563122578652</v>
+        <v>23.55899965881071</v>
       </c>
       <c r="D16" t="n">
         <v>8.266315669758143</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.344413517741383</v>
+        <v>3.307508015607504</v>
       </c>
       <c r="C2" t="n">
-        <v>2.68998870963626</v>
+        <v>3.639338739642926</v>
       </c>
       <c r="D2" t="n">
-        <v>12.09414996861646</v>
+        <v>9.130253649495335</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>13.45976102522377</v>
+        <v>16.69461971071701</v>
       </c>
       <c r="C3" t="n">
-        <v>16.24301576676348</v>
+        <v>15.82086425393735</v>
       </c>
       <c r="D3" t="n">
-        <v>69.0512247781994</v>
+        <v>54.50172380126168</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>36.34822700203391</v>
+        <v>44.47807974090174</v>
       </c>
       <c r="C4" t="n">
-        <v>53.41198384954772</v>
+        <v>52.05913551309561</v>
       </c>
       <c r="D4" t="n">
-        <v>144.4867548771158</v>
+        <v>131.5581193598896</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>57.70222131710629</v>
+        <v>70.29313562407164</v>
       </c>
       <c r="C5" t="n">
-        <v>154.2816517223863</v>
+        <v>151.9500009248001</v>
       </c>
       <c r="D5" t="n">
-        <v>144.9305048394354</v>
+        <v>143.5806017460961</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>52.327152636355</v>
+        <v>65.97246397768143</v>
       </c>
       <c r="C6" t="n">
-        <v>270.3301208505848</v>
+        <v>237.0822530985623</v>
       </c>
       <c r="D6" t="n">
-        <v>84.16621243278331</v>
+        <v>85.97753694711868</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>17.90609637775757</v>
+        <v>26.35010838198439</v>
       </c>
       <c r="C7" t="n">
-        <v>278.9518291892802</v>
+        <v>221.520570238546</v>
       </c>
       <c r="D7" t="n">
-        <v>45.8132566186774</v>
+        <v>48.38838084691679</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.673119072214817</v>
+        <v>6.175193059712437</v>
       </c>
       <c r="C8" t="n">
-        <v>179.1640472865217</v>
+        <v>137.1059756365883</v>
       </c>
       <c r="D8" t="n">
-        <v>35.88287859022092</v>
+        <v>36.38356991938679</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.774999849278233</v>
+        <v>2.218749811597791</v>
       </c>
       <c r="C9" t="n">
-        <v>72.33124385808797</v>
+        <v>64.23280704575605</v>
       </c>
       <c r="D9" t="n">
-        <v>33.28124717396686</v>
+        <v>33.72499713628642</v>
       </c>
     </row>
     <row r="10">
@@ -3383,10 +3383,10 @@
         <v>0.5694136684631501</v>
       </c>
       <c r="C10" t="n">
-        <v>32.74128593663113</v>
+        <v>33.59540643932586</v>
       </c>
       <c r="D10" t="n">
-        <v>25.19655482949439</v>
+        <v>26.05067533218912</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>24.34439782220815</v>
+        <v>25.58827216348886</v>
       </c>
       <c r="D11" t="n">
-        <v>24.16670148773948</v>
+        <v>24.6997904911455</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>17.7912318963607</v>
+        <v>18.65909686691488</v>
       </c>
       <c r="D12" t="n">
-        <v>20.17786056538469</v>
+        <v>20.82875929330033</v>
       </c>
     </row>
     <row r="13">
@@ -3425,7 +3425,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>11.70734137314322</v>
+        <v>11.96750451476862</v>
       </c>
       <c r="D13" t="n">
         <v>16.65044106402591</v>
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.36962016288231</v>
+        <v>11.98419422574081</v>
       </c>
       <c r="D14" t="n">
-        <v>11.67690719431156</v>
+        <v>11.06233313145306</v>
       </c>
     </row>
     <row r="15">
@@ -3453,7 +3453,7 @@
         <v>1.075013736150257</v>
       </c>
       <c r="C15" t="n">
-        <v>20.42526098685489</v>
+        <v>19.70858516275472</v>
       </c>
       <c r="D15" t="n">
         <v>6.808420328951629</v>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.999640147101506</v>
+        <v>6.053456344385832</v>
       </c>
       <c r="C2" t="n">
-        <v>7.527059648460295</v>
+        <v>10.49880994921539</v>
       </c>
       <c r="D2" t="n">
-        <v>16.47372647726148</v>
+        <v>12.8815116274224</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>10.78449853115121</v>
+        <v>13.96536109291088</v>
       </c>
       <c r="C3" t="n">
-        <v>13.52357462599981</v>
+        <v>14.88329519638165</v>
       </c>
       <c r="D3" t="n">
-        <v>64.08358139471055</v>
+        <v>49.78933482087699</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>31.15379989886403</v>
+        <v>38.67104207028186</v>
       </c>
       <c r="C4" t="n">
-        <v>46.9540474510122</v>
+        <v>45.93302983859552</v>
       </c>
       <c r="D4" t="n">
-        <v>143.7465171081137</v>
+        <v>129.1076770900895</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>57.08862900195204</v>
+        <v>69.0904946863693</v>
       </c>
       <c r="C5" t="n">
-        <v>130.7687942056752</v>
+        <v>127.3572209334175</v>
       </c>
       <c r="D5" t="n">
-        <v>159.6567204031376</v>
+        <v>154.9688751153591</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>62.26931163726245</v>
+        <v>78.24921901928779</v>
       </c>
       <c r="C6" t="n">
-        <v>261.1527433112856</v>
+        <v>239.9401206656247</v>
       </c>
       <c r="D6" t="n">
-        <v>103.6882655317311</v>
+        <v>104.0907820904723</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>33.0574086973986</v>
+        <v>45.63359678880023</v>
       </c>
       <c r="C7" t="n">
-        <v>325.9029313971797</v>
+        <v>274.1010137825967</v>
       </c>
       <c r="D7" t="n">
-        <v>55.45500082208532</v>
+        <v>58.74876436983337</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.262789589568655</v>
+        <v>13.76901155206151</v>
       </c>
       <c r="C8" t="n">
-        <v>256.771203307232</v>
+        <v>203.9482680802324</v>
       </c>
       <c r="D8" t="n">
-        <v>38.80357801035517</v>
+        <v>40.3056519978528</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.662499773917349</v>
+        <v>3.439062207976575</v>
       </c>
       <c r="C9" t="n">
-        <v>127.4671766762931</v>
+        <v>106.3890534661141</v>
       </c>
       <c r="D9" t="n">
-        <v>34.39062207976576</v>
+        <v>34.94530953266521</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.7117670855789376</v>
+        <v>0.8541205026947251</v>
       </c>
       <c r="C10" t="n">
-        <v>52.10135066437823</v>
+        <v>49.68134257340984</v>
       </c>
       <c r="D10" t="n">
-        <v>26.76244241776806</v>
+        <v>27.3318560862312</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>28.96450251839364</v>
+        <v>30.74146586308036</v>
       </c>
       <c r="D11" t="n">
-        <v>24.34439782220815</v>
+        <v>25.23287949455151</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>21.04572553593887</v>
+        <v>22.1305567491316</v>
       </c>
       <c r="D12" t="n">
-        <v>20.61179305066178</v>
+        <v>21.26269177857742</v>
       </c>
     </row>
     <row r="13">
@@ -3736,7 +3736,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.78864650614645</v>
+        <v>14.30897278939726</v>
       </c>
       <c r="D13" t="n">
         <v>16.91060420565131</v>
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.98419422574081</v>
+        <v>12.59876828859932</v>
       </c>
       <c r="D14" t="n">
-        <v>11.98419422574081</v>
+        <v>11.36962016288231</v>
       </c>
     </row>
     <row r="15">
@@ -3764,10 +3764,10 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>21.14193681095506</v>
+        <v>19.70858516275472</v>
       </c>
       <c r="D15" t="n">
-        <v>6.450082416901544</v>
+        <v>6.808420328951629</v>
       </c>
     </row>
     <row r="16">
@@ -3778,7 +3778,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>29.34542062764141</v>
+        <v>30.17205219461722</v>
       </c>
       <c r="D16" t="n">
         <v>3.306526267903257</v>
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.070726892434775</v>
+        <v>6.895795874629596</v>
       </c>
       <c r="C2" t="n">
-        <v>5.752059799182062</v>
+        <v>3.523492510541802</v>
       </c>
       <c r="D2" t="n">
-        <v>13.39987441526472</v>
+        <v>10.31424138081699</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.829396883639308</v>
+        <v>4.188135706316893</v>
       </c>
       <c r="C2" t="n">
-        <v>4.215624642035804</v>
+        <v>5.710826395603696</v>
       </c>
       <c r="D2" t="n">
-        <v>12.12556589515235</v>
+        <v>9.377654070965532</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.78021168743573</v>
+        <v>19.72331137831842</v>
       </c>
       <c r="C3" t="n">
-        <v>20.45471341798229</v>
+        <v>25.72178985126643</v>
       </c>
       <c r="D3" t="n">
-        <v>70.50421138048469</v>
+        <v>55.29203070318036</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>43.31667220677777</v>
+        <v>52.95252592396021</v>
       </c>
       <c r="C4" t="n">
-        <v>69.35262132340317</v>
+        <v>67.7317558636917</v>
       </c>
       <c r="D4" t="n">
-        <v>147.4604686732794</v>
+        <v>135.0678674025719</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>37.18369429834795</v>
+        <v>47.27115195948392</v>
       </c>
       <c r="C5" t="n">
-        <v>209.8976591679681</v>
+        <v>197.1840263979719</v>
       </c>
       <c r="D5" t="n">
-        <v>147.4585051778709</v>
+        <v>143.5315143608837</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>20.52834449580081</v>
+        <v>28.33716573537994</v>
       </c>
       <c r="C6" t="n">
-        <v>268.398041368627</v>
+        <v>234.626902090241</v>
       </c>
       <c r="D6" t="n">
-        <v>82.19388129495147</v>
+        <v>85.29325879725866</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>6.108434215823654</v>
+        <v>9.102764713776425</v>
       </c>
       <c r="C7" t="n">
-        <v>180.5581290265521</v>
+        <v>143.4284308519377</v>
       </c>
       <c r="D7" t="n">
-        <v>34.85400699617026</v>
+        <v>36.35117224514665</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.835868206941535</v>
+        <v>2.336559536107409</v>
       </c>
       <c r="C8" t="n">
-        <v>93.96307277346222</v>
+        <v>78.35819301445918</v>
       </c>
       <c r="D8" t="n">
-        <v>25.2849121228766</v>
+        <v>25.70215489718149</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.4437499623195582</v>
+        <v>0.5546874528994477</v>
       </c>
       <c r="C9" t="n">
-        <v>39.71562162760046</v>
+        <v>37.94062177832222</v>
       </c>
       <c r="D9" t="n">
-        <v>20.41249826669968</v>
+        <v>20.85624822901923</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>22.63419332141022</v>
+        <v>24.05772749256809</v>
       </c>
       <c r="D10" t="n">
-        <v>19.07535789351553</v>
+        <v>19.78712497909446</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>16.8811517745239</v>
+        <v>17.59193711239859</v>
       </c>
       <c r="D11" t="n">
-        <v>16.52575910558656</v>
+        <v>17.05884810899257</v>
       </c>
     </row>
     <row r="12">
@@ -4344,7 +4344,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>11.0652783745658</v>
+        <v>11.49921085984289</v>
       </c>
       <c r="D12" t="n">
         <v>13.66887328622834</v>
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>9.886199381765381</v>
+        <v>10.40652566501619</v>
       </c>
       <c r="D13" t="n">
-        <v>9.886199381765381</v>
+        <v>9.365873098514571</v>
       </c>
     </row>
     <row r="14">
@@ -4372,10 +4372,10 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>17.51536079146734</v>
+        <v>16.28621266575034</v>
       </c>
       <c r="D14" t="n">
-        <v>5.223879534297279</v>
+        <v>5.53116656572653</v>
       </c>
     </row>
     <row r="15">
@@ -4386,7 +4386,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>24.72531593145592</v>
+        <v>25.44199175555609</v>
       </c>
       <c r="D15" t="n">
         <v>2.5083653843506</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.685300955293279</v>
+        <v>6.838854507783281</v>
       </c>
       <c r="C2" t="n">
-        <v>5.721625620350411</v>
+        <v>2.426880324898115</v>
       </c>
       <c r="D2" t="n">
-        <v>14.5279025274443</v>
+        <v>15.19745446174062</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>10.77468105410875</v>
+        <v>14.64276700884118</v>
       </c>
       <c r="C3" t="n">
-        <v>14.49059611468292</v>
+        <v>8.874999246391166</v>
       </c>
       <c r="D3" t="n">
-        <v>14.39242134425824</v>
+        <v>11.80060740504666</v>
       </c>
     </row>
     <row r="4">
@@ -4543,7 +4543,7 @@
         <v>1.008254892261474</v>
       </c>
       <c r="C4" t="n">
-        <v>1.493238258159399</v>
+        <v>1.454950097693773</v>
       </c>
       <c r="D4" t="n">
         <v>19.62906359871073</v>
@@ -4554,10 +4554,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>4.736932672990861</v>
+        <v>4.68784528777852</v>
       </c>
       <c r="C5" t="n">
-        <v>9.35114688295087</v>
+        <v>9.424777960769381</v>
       </c>
       <c r="D5" t="n">
         <v>28.49522711576368</v>
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>8.050331174823848</v>
+        <v>8.130834486572086</v>
       </c>
       <c r="C6" t="n">
         <v>18.47551004622073</v>
       </c>
       <c r="D6" t="n">
-        <v>32.8453511932813</v>
+        <v>32.52333794628834</v>
       </c>
     </row>
     <row r="7">
@@ -4588,7 +4588,7 @@
         <v>20.9603134856694</v>
       </c>
       <c r="D7" t="n">
-        <v>32.21899615797182</v>
+        <v>32.69808903764427</v>
       </c>
     </row>
     <row r="8">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.39784357311192</v>
+        <v>13.39844272309265</v>
       </c>
       <c r="C21" t="n">
-        <v>70.14165164746828</v>
+        <v>70.144788373838</v>
       </c>
       <c r="D21" t="n">
-        <v>1.576216890954343</v>
+        <v>1.576287379187371</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.993749660876024</v>
+        <v>4.5553093477052</v>
       </c>
       <c r="C2" t="n">
-        <v>3.149446635223768</v>
+        <v>3.636393496530185</v>
       </c>
       <c r="D2" t="n">
-        <v>20.86213871524472</v>
+        <v>19.53088882828605</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.09575361112645</v>
+        <v>20.06201433628357</v>
       </c>
       <c r="C3" t="n">
-        <v>19.38460842035327</v>
+        <v>9.252972112526187</v>
       </c>
       <c r="D3" t="n">
-        <v>23.11524969649115</v>
+        <v>21.71135047941821</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>12.59680479319082</v>
+        <v>16.96165508627214</v>
       </c>
       <c r="C4" t="n">
-        <v>22.62830283518473</v>
+        <v>14.28148385367835</v>
       </c>
       <c r="D4" t="n">
-        <v>22.61554011502952</v>
+        <v>21.24992905842221</v>
       </c>
     </row>
     <row r="5">
@@ -4865,10 +4865,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3.092505268377454</v>
+        <v>3.067961575771283</v>
       </c>
       <c r="C5" t="n">
-        <v>5.424156065963628</v>
+        <v>5.399612373357458</v>
       </c>
       <c r="D5" t="n">
         <v>29.10881943091793</v>
@@ -4882,10 +4882,10 @@
         <v>7.446556336712058</v>
       </c>
       <c r="C6" t="n">
-        <v>16.50317890838889</v>
+        <v>16.54343056426301</v>
       </c>
       <c r="D6" t="n">
-        <v>35.01894061048373</v>
+        <v>34.77743067523902</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.462084373530759</v>
+        <v>9.521970983489814</v>
       </c>
       <c r="C7" t="n">
         <v>24.49362347325367</v>
       </c>
       <c r="D7" t="n">
-        <v>34.97378021608837</v>
+        <v>35.27321326588365</v>
       </c>
     </row>
     <row r="8">
@@ -4913,7 +4913,7 @@
         <v>25.61870634232051</v>
       </c>
       <c r="D8" t="n">
-        <v>36.63391558396972</v>
+        <v>36.80081269369168</v>
       </c>
     </row>
     <row r="9">
@@ -4924,7 +4924,7 @@
         <v>9.318749208710722</v>
       </c>
       <c r="C9" t="n">
-        <v>25.73749781453438</v>
+        <v>25.5156228333746</v>
       </c>
       <c r="D9" t="n">
         <v>40.27030908049991</v>
@@ -4938,7 +4938,7 @@
         <v>8.968265278294615</v>
       </c>
       <c r="C10" t="n">
-        <v>27.04714925199963</v>
+        <v>27.3318560862312</v>
       </c>
       <c r="D10" t="n">
         <v>50.1084028247572</v>
@@ -4949,7 +4949,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>7.640942382152923</v>
+        <v>7.463246047684251</v>
       </c>
       <c r="C11" t="n">
         <v>29.49759152179966</v>
@@ -4983,7 +4983,7 @@
         <v>26.79680358741669</v>
       </c>
       <c r="D13" t="n">
-        <v>44.74806035956962</v>
+        <v>44.22773407631881</v>
       </c>
     </row>
     <row r="14">
@@ -4997,7 +4997,7 @@
         <v>25.50482360862789</v>
       </c>
       <c r="D14" t="n">
-        <v>44.86390658867074</v>
+        <v>45.47848065152925</v>
       </c>
     </row>
     <row r="15">
@@ -5022,7 +5022,7 @@
         <v>5.373105185342793</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>29.34542062764141</v>
       </c>
       <c r="D16" t="n">
         <v>40.5049467818149</v>
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.44158554459253</v>
+        <v>15.44333786451974</v>
       </c>
       <c r="C21" t="n">
-        <v>86.14779303825304</v>
+        <v>86.15756913889959</v>
       </c>
       <c r="D21" t="n">
-        <v>3.250860114651058</v>
+        <v>3.251229024109418</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.911683764346792</v>
+        <v>5.442809272344316</v>
       </c>
       <c r="C2" t="n">
-        <v>6.265513848503144</v>
+        <v>2.724349879284899</v>
       </c>
       <c r="D2" t="n">
-        <v>19.91082518982956</v>
+        <v>18.57073957353267</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.8194815956056</v>
+        <v>17.82362957060084</v>
       </c>
       <c r="C3" t="n">
-        <v>15.06000978314607</v>
+        <v>12.22275891787279</v>
       </c>
       <c r="D3" t="n">
-        <v>34.43970946497811</v>
+        <v>32.29459073119883</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>23.04947260030661</v>
+        <v>29.29044275620359</v>
       </c>
       <c r="C4" t="n">
-        <v>37.87975342065894</v>
+        <v>19.37380919560656</v>
       </c>
       <c r="D4" t="n">
-        <v>29.12452739418588</v>
+        <v>27.35050929261189</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>11.43736075447534</v>
+        <v>14.84893402673301</v>
       </c>
       <c r="C5" t="n">
-        <v>26.08994524035899</v>
+        <v>17.54874021341174</v>
       </c>
       <c r="D5" t="n">
-        <v>30.55689729468198</v>
+        <v>30.06602344255857</v>
       </c>
     </row>
     <row r="6">
@@ -5196,7 +5196,7 @@
         <v>12.19625172985813</v>
       </c>
       <c r="D6" t="n">
-        <v>36.8302651248191</v>
+        <v>36.6290068454485</v>
       </c>
     </row>
     <row r="7">
@@ -5210,7 +5210,7 @@
         <v>24.49362347325367</v>
       </c>
       <c r="D7" t="n">
-        <v>37.24947139453248</v>
+        <v>37.42913122440964</v>
       </c>
     </row>
     <row r="8">
@@ -5221,10 +5221,10 @@
         <v>10.34762080276138</v>
       </c>
       <c r="C8" t="n">
-        <v>29.87458264023044</v>
+        <v>29.6242369756475</v>
       </c>
       <c r="D8" t="n">
-        <v>38.38633523605029</v>
+        <v>38.55323234577224</v>
       </c>
     </row>
     <row r="9">
@@ -5235,10 +5235,10 @@
         <v>10.09531164276995</v>
       </c>
       <c r="C9" t="n">
-        <v>29.50937249425062</v>
+        <v>29.7312474754104</v>
       </c>
       <c r="D9" t="n">
-        <v>41.15780900513902</v>
+        <v>41.26874649571891</v>
       </c>
     </row>
     <row r="10">
@@ -5246,7 +5246,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.537678946757763</v>
+        <v>9.395325529641976</v>
       </c>
       <c r="C10" t="n">
         <v>29.89421759431538</v>
@@ -5263,7 +5263,7 @@
         <v>8.351727720027615</v>
       </c>
       <c r="C11" t="n">
-        <v>31.27455486648638</v>
+        <v>31.45225120095506</v>
       </c>
       <c r="D11" t="n">
         <v>49.75497365122833</v>
@@ -5274,7 +5274,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6.725953521794898</v>
+        <v>6.508987279156352</v>
       </c>
       <c r="C12" t="n">
         <v>32.11100391050467</v>
@@ -5291,10 +5291,10 @@
         <v>5.463425974133501</v>
       </c>
       <c r="C13" t="n">
-        <v>30.17892442854696</v>
+        <v>29.91876128692155</v>
       </c>
       <c r="D13" t="n">
-        <v>45.52854978444583</v>
+        <v>45.00822350119503</v>
       </c>
     </row>
     <row r="14">
@@ -5305,10 +5305,10 @@
         <v>4.609305471438775</v>
       </c>
       <c r="C14" t="n">
-        <v>27.65583282863265</v>
+        <v>27.9631198600619</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>45.7857676829585</v>
       </c>
     </row>
     <row r="15">
@@ -5322,7 +5322,7 @@
         <v>27.5920192278566</v>
       </c>
       <c r="D15" t="n">
-        <v>43.00054944601029</v>
+        <v>43.35888735806038</v>
       </c>
     </row>
     <row r="16">
@@ -5333,7 +5333,7 @@
         <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>29.34542062764141</v>
+        <v>29.75873641112932</v>
       </c>
       <c r="D16" t="n">
         <v>40.91826256530281</v>
@@ -5361,7 +5361,7 @@
         <v>5.350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>35.31346492175777</v>
       </c>
       <c r="D18" t="n">
         <v>31.56809743005619</v>
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.73727282947326</v>
+        <v>16.74164367801552</v>
       </c>
       <c r="C21" t="n">
-        <v>102.0973642597869</v>
+        <v>102.1240264358947</v>
       </c>
       <c r="D21" t="n">
-        <v>5.021181848841977</v>
+        <v>5.022493103404656</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.525276079501049</v>
+        <v>6.620906517440489</v>
       </c>
       <c r="C2" t="n">
-        <v>8.1102177847829</v>
+        <v>6.546293691917731</v>
       </c>
       <c r="D2" t="n">
-        <v>22.15019170321653</v>
+        <v>17.78435966243097</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.92394776288327</v>
+        <v>18.49612674800991</v>
       </c>
       <c r="C3" t="n">
-        <v>20.4988920646734</v>
+        <v>11.25573742918968</v>
       </c>
       <c r="D3" t="n">
-        <v>41.91080949429634</v>
+        <v>39.22572952318131</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>26.0231863964702</v>
+        <v>32.02166486941822</v>
       </c>
       <c r="C4" t="n">
-        <v>37.77765165941726</v>
+        <v>25.75516927321083</v>
       </c>
       <c r="D4" t="n">
-        <v>38.97734735400687</v>
+        <v>36.57795596482766</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>23.26742059064941</v>
+        <v>29.59969328304134</v>
       </c>
       <c r="C5" t="n">
-        <v>50.21639507222437</v>
+        <v>27.41530464109218</v>
       </c>
       <c r="D5" t="n">
-        <v>34.26299487821369</v>
+        <v>33.25670348136071</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>10.70694046251572</v>
+        <v>13.20254312671111</v>
       </c>
       <c r="C6" t="n">
-        <v>27.6126359296458</v>
+        <v>20.64909946342317</v>
       </c>
       <c r="D6" t="n">
-        <v>38.60133798328035</v>
+        <v>37.91705983342032</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.683558444063037</v>
+        <v>8.623671834103982</v>
       </c>
       <c r="C7" t="n">
-        <v>21.02020009562846</v>
+        <v>21.19985992550562</v>
       </c>
       <c r="D7" t="n">
-        <v>39.40538935305847</v>
+        <v>40.00425545264903</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.76486357706628</v>
+        <v>10.84831213192725</v>
       </c>
       <c r="C8" t="n">
-        <v>31.87734795689393</v>
+        <v>31.46010518258904</v>
       </c>
       <c r="D8" t="n">
-        <v>40.22220344299182</v>
+        <v>40.38910055271378</v>
       </c>
     </row>
     <row r="9">
@@ -5549,7 +5549,7 @@
         <v>34.27968458918587</v>
       </c>
       <c r="D9" t="n">
-        <v>41.82343394861835</v>
+        <v>41.93437143919824</v>
       </c>
     </row>
     <row r="10">
@@ -5557,10 +5557,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.964739198105127</v>
+        <v>10.10709261522091</v>
       </c>
       <c r="C10" t="n">
-        <v>33.16834618797849</v>
+        <v>33.59540643932586</v>
       </c>
       <c r="D10" t="n">
         <v>49.25428232206248</v>
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>9.062513057902304</v>
+        <v>8.884816723433632</v>
       </c>
       <c r="C11" t="n">
-        <v>33.7623035490478</v>
+        <v>33.93999988351647</v>
       </c>
       <c r="D11" t="n">
-        <v>50.82115165804038</v>
+        <v>50.46575898910303</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>7.376852249710534</v>
+        <v>7.159886007071988</v>
       </c>
       <c r="C12" t="n">
-        <v>34.49763257952867</v>
+        <v>34.28066633689012</v>
       </c>
       <c r="D12" t="n">
-        <v>46.86470840992573</v>
+        <v>47.29864089520282</v>
       </c>
     </row>
     <row r="13">
@@ -5602,10 +5602,10 @@
         <v>5.723589115758904</v>
       </c>
       <c r="C13" t="n">
-        <v>33.04071898642641</v>
+        <v>33.30088212805181</v>
       </c>
       <c r="D13" t="n">
-        <v>46.30903920932205</v>
+        <v>45.78871292607123</v>
       </c>
     </row>
     <row r="14">
@@ -5619,7 +5619,7 @@
         <v>30.72870314292517</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>45.7857676829585</v>
       </c>
     </row>
     <row r="15">
@@ -5633,7 +5633,7 @@
         <v>29.02537087605695</v>
       </c>
       <c r="D15" t="n">
-        <v>43.71722527011046</v>
+        <v>44.07556318216055</v>
       </c>
     </row>
     <row r="16">
@@ -5644,7 +5644,7 @@
         <v>4.546473618366978</v>
       </c>
       <c r="C16" t="n">
-        <v>29.75873641112932</v>
+        <v>30.17205219461722</v>
       </c>
       <c r="D16" t="n">
         <v>40.91826256530281</v>
@@ -5672,7 +5672,7 @@
         <v>4.815472489330605</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>35.31346492175777</v>
       </c>
       <c r="D18" t="n">
         <v>32.1031499288707</v>
@@ -5700,7 +5700,7 @@
         <v>4.707480241863455</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>39.67733346713483</v>
       </c>
       <c r="D20" t="n">
         <v>16.13993225781756</v>
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.06777698724869</v>
+        <v>18.07754203991971</v>
       </c>
       <c r="C21" t="n">
-        <v>117.8707355834796</v>
+        <v>117.9344409270953</v>
       </c>
       <c r="D21" t="n">
-        <v>6.882962661809025</v>
+        <v>6.886682681874176</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.522731747015809</v>
+        <v>6.453027660014286</v>
       </c>
       <c r="C2" t="n">
-        <v>10.73148415512189</v>
+        <v>7.40532293313369</v>
       </c>
       <c r="D2" t="n">
-        <v>21.09579466885546</v>
+        <v>24.09896089614645</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.78650308428871</v>
+        <v>18.6973850273805</v>
       </c>
       <c r="C3" t="n">
-        <v>25.32909076956771</v>
+        <v>18.62866268808323</v>
       </c>
       <c r="D3" t="n">
-        <v>46.49557127312895</v>
+        <v>42.11697651218817</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>21.05848825609408</v>
+        <v>24.84901614219102</v>
       </c>
       <c r="C4" t="n">
-        <v>38.12224510360789</v>
+        <v>22.53896379409827</v>
       </c>
       <c r="D4" t="n">
-        <v>43.77613013236527</v>
+        <v>41.03214529899544</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>19.1440802328128</v>
+        <v>24.02827506144069</v>
       </c>
       <c r="C5" t="n">
-        <v>45.3076565509903</v>
+        <v>28.76520773443155</v>
       </c>
       <c r="D5" t="n">
-        <v>32.93763547748049</v>
+        <v>31.6122760767473</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>11.67298020349458</v>
+        <v>14.93336432929824</v>
       </c>
       <c r="C6" t="n">
-        <v>36.99127174831558</v>
+        <v>22.21891404251382</v>
       </c>
       <c r="D6" t="n">
-        <v>31.35603992593888</v>
+        <v>30.71201343195298</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.389794896314989</v>
+        <v>6.108434215823654</v>
       </c>
       <c r="C7" t="n">
-        <v>19.82246789644735</v>
+        <v>16.64847756861741</v>
       </c>
       <c r="D7" t="n">
-        <v>31.20092378866788</v>
+        <v>31.4404702285041</v>
       </c>
     </row>
     <row r="8">
@@ -5843,10 +5843,10 @@
         <v>4.840016181936775</v>
       </c>
       <c r="C8" t="n">
-        <v>18.52557917913731</v>
+        <v>18.60902773399829</v>
       </c>
       <c r="D8" t="n">
-        <v>30.20837685967435</v>
+        <v>30.12492830481337</v>
       </c>
     </row>
     <row r="9">
@@ -5857,10 +5857,10 @@
         <v>4.881249585515139</v>
       </c>
       <c r="C9" t="n">
-        <v>22.2984356065578</v>
+        <v>21.96562313481813</v>
       </c>
       <c r="D9" t="n">
-        <v>29.84218496599028</v>
+        <v>30.28593492830985</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.270602513473626</v>
+        <v>4.412955930589413</v>
       </c>
       <c r="C10" t="n">
-        <v>21.49536598448391</v>
+        <v>21.6377194015997</v>
       </c>
       <c r="D10" t="n">
-        <v>33.73775985644164</v>
+        <v>33.45305302221006</v>
       </c>
     </row>
     <row r="11">
@@ -5885,10 +5885,10 @@
         <v>3.731623023842126</v>
       </c>
       <c r="C11" t="n">
-        <v>20.25738212942868</v>
+        <v>20.61277479836603</v>
       </c>
       <c r="D11" t="n">
-        <v>34.47308888692249</v>
+        <v>34.65078522139116</v>
       </c>
     </row>
     <row r="12">
@@ -5899,10 +5899,10 @@
         <v>3.037527396939631</v>
       </c>
       <c r="C12" t="n">
-        <v>20.17786056538469</v>
+        <v>19.96089432274615</v>
       </c>
       <c r="D12" t="n">
-        <v>32.11100391050467</v>
+        <v>32.32797015314322</v>
       </c>
     </row>
     <row r="13">
@@ -5913,10 +5913,10 @@
         <v>2.341468274628643</v>
       </c>
       <c r="C13" t="n">
-        <v>18.99190933865455</v>
+        <v>19.25207248027995</v>
       </c>
       <c r="D13" t="n">
-        <v>30.43908757017236</v>
+        <v>30.17892442854696</v>
       </c>
     </row>
     <row r="14">
@@ -5944,7 +5944,7 @@
         <v>16.12520604225386</v>
       </c>
       <c r="D15" t="n">
-        <v>27.95035713990669</v>
+        <v>28.30869505195678</v>
       </c>
     </row>
     <row r="16">
@@ -5972,7 +5972,7 @@
         <v>16.52772260099505</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>23.61103228713579</v>
       </c>
     </row>
     <row r="18">
@@ -5983,7 +5983,7 @@
         <v>1.070104997629023</v>
       </c>
       <c r="C18" t="n">
-        <v>17.12167996206437</v>
+        <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
         <v>20.33199495495144</v>
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.064049429535341</v>
+        <v>7.071076494962521</v>
       </c>
       <c r="C21" t="n">
-        <v>66.22546340189382</v>
+        <v>67.17522670214395</v>
       </c>
       <c r="D21" t="n">
-        <v>5.298037072151506</v>
+        <v>5.303307371221891</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.822344723260333</v>
+        <v>5.683337459884785</v>
       </c>
       <c r="C2" t="n">
-        <v>7.03618579633689</v>
+        <v>5.529203070318036</v>
       </c>
       <c r="D2" t="n">
-        <v>26.24015263910875</v>
+        <v>23.67680938332033</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.41053477129119</v>
+        <v>21.51990967709008</v>
       </c>
       <c r="C3" t="n">
-        <v>36.22158154818607</v>
+        <v>25.51071409485337</v>
       </c>
       <c r="D3" t="n">
-        <v>53.37762267989908</v>
+        <v>52.73948667213865</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>27.14630577012855</v>
+        <v>32.31520743298801</v>
       </c>
       <c r="C4" t="n">
-        <v>54.35642514103315</v>
+        <v>38.22434686484957</v>
       </c>
       <c r="D4" t="n">
-        <v>58.72127543411447</v>
+        <v>54.24156065963627</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>26.77716863333176</v>
+        <v>32.44676162535709</v>
       </c>
       <c r="C5" t="n">
-        <v>61.01561981893928</v>
+        <v>36.96280106489242</v>
       </c>
       <c r="D5" t="n">
-        <v>42.26423866782519</v>
+        <v>39.85895679242051</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>20.00507296943726</v>
+        <v>25.60005313593983</v>
       </c>
       <c r="C6" t="n">
-        <v>58.00263611460582</v>
+        <v>36.30699359845555</v>
       </c>
       <c r="D6" t="n">
-        <v>34.93843729873549</v>
+        <v>34.49566908412018</v>
       </c>
     </row>
     <row r="7">
@@ -6137,10 +6137,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>10.4801567428347</v>
+        <v>12.93550775115597</v>
       </c>
       <c r="C7" t="n">
-        <v>39.58504918293564</v>
+        <v>26.29022177202533</v>
       </c>
       <c r="D7" t="n">
         <v>33.89582123682538</v>
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.674501730546564</v>
+        <v>6.175193059712437</v>
       </c>
       <c r="C8" t="n">
-        <v>23.53249247079604</v>
+        <v>21.19593293468863</v>
       </c>
       <c r="D8" t="n">
-        <v>32.29459073119883</v>
+        <v>32.04424506661589</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.103124566674919</v>
+        <v>5.214062057254808</v>
       </c>
       <c r="C9" t="n">
-        <v>23.51874800293658</v>
+        <v>23.40781051235669</v>
       </c>
       <c r="D9" t="n">
-        <v>31.06249736236907</v>
+        <v>31.72812230584841</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.697662764820988</v>
+        <v>4.840016181936776</v>
       </c>
       <c r="C10" t="n">
         <v>25.0542014123786</v>
       </c>
       <c r="D10" t="n">
-        <v>34.16482010778901</v>
+        <v>34.02246669067321</v>
       </c>
     </row>
     <row r="11">
@@ -6196,10 +6196,10 @@
         <v>4.08701569277947</v>
       </c>
       <c r="C11" t="n">
-        <v>23.45591614986479</v>
+        <v>23.81130881880213</v>
       </c>
       <c r="D11" t="n">
-        <v>35.36157055926586</v>
+        <v>35.00617789032851</v>
       </c>
     </row>
     <row r="12">
@@ -6213,7 +6213,7 @@
         <v>22.34752299177014</v>
       </c>
       <c r="D12" t="n">
-        <v>32.97886888105885</v>
+        <v>33.62976760897449</v>
       </c>
     </row>
     <row r="13">
@@ -6227,7 +6227,7 @@
         <v>21.33337761328319</v>
       </c>
       <c r="D13" t="n">
-        <v>31.21957699504857</v>
+        <v>30.95941385342317</v>
       </c>
     </row>
     <row r="14">
@@ -6241,7 +6241,7 @@
         <v>19.66637001147211</v>
       </c>
       <c r="D14" t="n">
-        <v>30.11412908006666</v>
+        <v>29.80684204863741</v>
       </c>
     </row>
     <row r="15">
@@ -6255,7 +6255,7 @@
         <v>17.91689560250429</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>28.66703296400686</v>
       </c>
     </row>
     <row r="16">
@@ -6283,7 +6283,7 @@
         <v>16.99994324673777</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>23.61103228713579</v>
       </c>
     </row>
     <row r="18">
@@ -6297,7 +6297,7 @@
         <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -6325,7 +6325,7 @@
         <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>10.08745766113597</v>
       </c>
     </row>
     <row r="21">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.289964333827093</v>
+        <v>7.301712651111476</v>
       </c>
       <c r="C21" t="n">
-        <v>76.54462550518447</v>
+        <v>77.58069691805943</v>
       </c>
       <c r="D21" t="n">
-        <v>6.378718792098706</v>
+        <v>6.388998569722541</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.923464736797754</v>
+        <v>4.977460860531329</v>
       </c>
       <c r="C2" t="n">
-        <v>3.978041697608075</v>
+        <v>4.137084825696059</v>
       </c>
       <c r="D2" t="n">
-        <v>23.44315342970958</v>
+        <v>23.07107104980004</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.33904711533042</v>
+        <v>20.57743188101315</v>
       </c>
       <c r="C3" t="n">
-        <v>30.79251674370121</v>
+        <v>23.04161861867264</v>
       </c>
       <c r="D3" t="n">
-        <v>61.98264130762237</v>
+        <v>59.8817012205342</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>34.62525978108076</v>
+        <v>38.07119422298706</v>
       </c>
       <c r="C4" t="n">
-        <v>76.15515116612933</v>
+        <v>53.51408561078939</v>
       </c>
       <c r="D4" t="n">
-        <v>71.73924999242718</v>
+        <v>69.28880772262713</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>34.45934441906305</v>
+        <v>42.04334543436966</v>
       </c>
       <c r="C5" t="n">
-        <v>83.96397240570847</v>
+        <v>57.23589115758906</v>
       </c>
       <c r="D5" t="n">
-        <v>54.53608497091033</v>
+        <v>50.63363784652926</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>29.22270216461057</v>
+        <v>36.34724525432967</v>
       </c>
       <c r="C6" t="n">
-        <v>79.9397885660008</v>
+        <v>49.3887817575443</v>
       </c>
       <c r="D6" t="n">
-        <v>40.69442408873454</v>
+        <v>39.92964262712628</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>17.78632315783946</v>
+        <v>22.75691178444107</v>
       </c>
       <c r="C7" t="n">
-        <v>63.89901282631214</v>
+        <v>41.44153409166636</v>
       </c>
       <c r="D7" t="n">
-        <v>36.35117224514665</v>
+        <v>36.77037851486003</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.92899537012474</v>
+        <v>10.6814150222053</v>
       </c>
       <c r="C8" t="n">
-        <v>39.8884092235479</v>
+        <v>29.29044275620359</v>
       </c>
       <c r="D8" t="n">
-        <v>34.54770171244525</v>
+        <v>34.04701038327938</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.657812019574366</v>
+        <v>5.990624491314035</v>
       </c>
       <c r="C9" t="n">
-        <v>27.29062268265283</v>
+        <v>25.73749781453438</v>
       </c>
       <c r="D9" t="n">
-        <v>32.39374724932775</v>
+        <v>33.28124717396686</v>
       </c>
     </row>
     <row r="10">
@@ -6490,10 +6490,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.982369599052563</v>
+        <v>5.267076433284139</v>
       </c>
       <c r="C10" t="n">
-        <v>27.47420950334699</v>
+        <v>27.18950266911542</v>
       </c>
       <c r="D10" t="n">
         <v>34.73423377625215</v>
@@ -6507,10 +6507,10 @@
         <v>4.442408361716816</v>
       </c>
       <c r="C11" t="n">
-        <v>27.00984283923824</v>
+        <v>27.36523550817559</v>
       </c>
       <c r="D11" t="n">
-        <v>36.07235589714055</v>
+        <v>35.36157055926586</v>
       </c>
     </row>
     <row r="12">
@@ -6521,10 +6521,10 @@
         <v>3.471459882216721</v>
       </c>
       <c r="C12" t="n">
-        <v>24.73415166079414</v>
+        <v>25.38505038870978</v>
       </c>
       <c r="D12" t="n">
-        <v>33.62976760897449</v>
+        <v>34.71459882216721</v>
       </c>
     </row>
     <row r="13">
@@ -6552,7 +6552,7 @@
         <v>21.81737923147687</v>
       </c>
       <c r="D14" t="n">
-        <v>30.72870314292517</v>
+        <v>30.11412908006666</v>
       </c>
     </row>
     <row r="15">
@@ -6566,7 +6566,7 @@
         <v>19.70858516275472</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>29.02537087605695</v>
       </c>
     </row>
     <row r="16">
@@ -6580,7 +6580,7 @@
         <v>17.77257868998001</v>
       </c>
       <c r="D16" t="n">
-        <v>27.27884171020187</v>
+        <v>26.86552592671396</v>
       </c>
     </row>
     <row r="17">
@@ -6594,7 +6594,7 @@
         <v>17.47216389248049</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>24.0832529328785</v>
       </c>
     </row>
     <row r="18">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.503105839764496</v>
+        <v>7.522082220326986</v>
       </c>
       <c r="C21" t="n">
-        <v>86.2857171572917</v>
+        <v>87.4442058113012</v>
       </c>
       <c r="D21" t="n">
-        <v>7.503105839764496</v>
+        <v>7.522082220326986</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_surface_area_iteration_24_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_24_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497622078869</v>
+        <v>10.84497616835291</v>
       </c>
       <c r="C21" t="n">
-        <v>37.78907155364685</v>
+        <v>37.78907137093557</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.668611244321084</v>
+        <v>5.796238445873168</v>
       </c>
       <c r="C2" t="n">
-        <v>4.716315971201677</v>
+        <v>9.348201639838129</v>
       </c>
       <c r="D2" t="n">
-        <v>19.57801271808989</v>
+        <v>18.77003435749477</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.67284133477433</v>
+        <v>18.08379271222625</v>
       </c>
       <c r="C3" t="n">
-        <v>18.94282195344221</v>
+        <v>42.08261534253953</v>
       </c>
       <c r="D3" t="n">
-        <v>64.09339887175302</v>
+        <v>46.55938487390498</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>39.38575439897354</v>
+        <v>39.09221183540375</v>
       </c>
       <c r="C4" t="n">
-        <v>55.37744275344983</v>
+        <v>96.66484245554945</v>
       </c>
       <c r="D4" t="n">
-        <v>82.26849412047422</v>
+        <v>57.25356261626548</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>50.04458922398117</v>
+        <v>52.79348279587224</v>
       </c>
       <c r="C5" t="n">
-        <v>80.57694282605698</v>
+        <v>133.198619773686</v>
       </c>
       <c r="D5" t="n">
-        <v>64.15721247252907</v>
+        <v>46.01942363656924</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>47.77871552257953</v>
+        <v>49.87180162803373</v>
       </c>
       <c r="C6" t="n">
-        <v>71.88945739117695</v>
+        <v>148.5286101755</v>
       </c>
       <c r="D6" t="n">
-        <v>46.41015922285948</v>
+        <v>39.04410619789565</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>33.65627479698915</v>
+        <v>34.01559445674349</v>
       </c>
       <c r="C7" t="n">
-        <v>57.31148573081605</v>
+        <v>143.0691111921834</v>
       </c>
       <c r="D7" t="n">
-        <v>40.36357511240336</v>
+        <v>37.36924461445059</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>18.19178495969339</v>
+        <v>16.68971097219578</v>
       </c>
       <c r="C8" t="n">
-        <v>43.47669708257</v>
+        <v>105.3955247894163</v>
       </c>
       <c r="D8" t="n">
-        <v>36.55046702910875</v>
+        <v>35.63253292563798</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.542186774651494</v>
+        <v>7.765624340592267</v>
       </c>
       <c r="C9" t="n">
-        <v>32.06093477758807</v>
+        <v>56.79999517690344</v>
       </c>
       <c r="D9" t="n">
-        <v>34.39062207976576</v>
+        <v>33.83593462686631</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.694136684631501</v>
+        <v>5.409429850399925</v>
       </c>
       <c r="C10" t="n">
-        <v>29.75186417719959</v>
+        <v>32.59893251951534</v>
       </c>
       <c r="D10" t="n">
-        <v>35.58835427894688</v>
+        <v>34.73423377625215</v>
       </c>
     </row>
     <row r="11">
@@ -906,10 +906,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.797801030654161</v>
+        <v>4.620104696185489</v>
       </c>
       <c r="C11" t="n">
-        <v>29.852984190737</v>
+        <v>28.96450251839364</v>
       </c>
       <c r="D11" t="n">
         <v>35.7169632282032</v>
@@ -920,13 +920,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.905392367493811</v>
+        <v>3.688426124855267</v>
       </c>
       <c r="C12" t="n">
-        <v>28.63954402828795</v>
+        <v>27.33774657245668</v>
       </c>
       <c r="D12" t="n">
-        <v>35.58246379272139</v>
+        <v>35.1485313074443</v>
       </c>
     </row>
     <row r="13">
@@ -937,10 +937,10 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>26.27647730416588</v>
+        <v>25.23582473766426</v>
       </c>
       <c r="D13" t="n">
-        <v>32.5203927031756</v>
+        <v>32.26022956155019</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.151009220004762</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>23.96838845148163</v>
+        <v>23.35381438862312</v>
       </c>
       <c r="D14" t="n">
-        <v>30.72870314292517</v>
+        <v>30.42141611149592</v>
       </c>
     </row>
     <row r="15">
@@ -965,10 +965,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>21.85861263505523</v>
+        <v>20.78359889890498</v>
       </c>
       <c r="D15" t="n">
-        <v>29.38370878810703</v>
+        <v>29.02537087605695</v>
       </c>
     </row>
     <row r="16">
@@ -979,10 +979,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>19.42584182393164</v>
+        <v>19.01252604044373</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>26.45221014322606</v>
       </c>
     </row>
     <row r="17">
@@ -993,7 +993,7 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>18.41660518396592</v>
+        <v>17.9443845382232</v>
       </c>
       <c r="D17" t="n">
         <v>24.55547357862122</v>
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.730355042985162</v>
+        <v>7.661111408484733</v>
       </c>
       <c r="C21" t="n">
-        <v>96.62943803731453</v>
+        <v>92.89097582787738</v>
       </c>
       <c r="D21" t="n">
-        <v>8.696649423358307</v>
+        <v>7.661111408484733</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.162831250184728</v>
+        <v>8.695339416513999</v>
       </c>
       <c r="C2" t="n">
-        <v>7.215845626214056</v>
+        <v>9.58774807967435</v>
       </c>
       <c r="D2" t="n">
-        <v>18.16625951938298</v>
+        <v>17.24636192050372</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.10971906316416</v>
+        <v>18.51576170209485</v>
       </c>
       <c r="C3" t="n">
-        <v>18.54521413322225</v>
+        <v>38.95574890451343</v>
       </c>
       <c r="D3" t="n">
-        <v>64.54991155422778</v>
+        <v>49.55371537185776</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>37.31819373382976</v>
+        <v>36.3354642818787</v>
       </c>
       <c r="C4" t="n">
-        <v>50.56589725493621</v>
+        <v>100.5191839424224</v>
       </c>
       <c r="D4" t="n">
-        <v>93.55073873767856</v>
+        <v>64.75804206752811</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>54.5606286635165</v>
+        <v>55.68963852340033</v>
       </c>
       <c r="C5" t="n">
-        <v>91.81795403968295</v>
+        <v>152.4163310843173</v>
       </c>
       <c r="D5" t="n">
-        <v>78.44164156932015</v>
+        <v>54.46245389309182</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>58.32464936159877</v>
+        <v>59.08943082320704</v>
       </c>
       <c r="C6" t="n">
-        <v>99.34108669732626</v>
+        <v>175.8594845140269</v>
       </c>
       <c r="D6" t="n">
-        <v>55.34602682691394</v>
+        <v>43.39128503230054</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>45.21439051908685</v>
+        <v>45.09461729916874</v>
       </c>
       <c r="C7" t="n">
-        <v>81.08646988456105</v>
+        <v>176.6056127692545</v>
       </c>
       <c r="D7" t="n">
-        <v>44.01665831990574</v>
+        <v>40.00425545264903</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>27.45457454926205</v>
+        <v>25.45180923259856</v>
       </c>
       <c r="C8" t="n">
-        <v>60.16640805476577</v>
+        <v>142.9473744768568</v>
       </c>
       <c r="D8" t="n">
-        <v>39.22082078466007</v>
+        <v>37.1346069131356</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>13.31249886958674</v>
+        <v>11.75937400146829</v>
       </c>
       <c r="C9" t="n">
-        <v>43.04374634499714</v>
+        <v>90.19217984145018</v>
       </c>
       <c r="D9" t="n">
-        <v>35.72187196672443</v>
+        <v>35.27812200440487</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6.975317438673588</v>
+        <v>6.26355035309465</v>
       </c>
       <c r="C10" t="n">
-        <v>34.59188035913637</v>
+        <v>47.54604131667303</v>
       </c>
       <c r="D10" t="n">
-        <v>36.44247478164161</v>
+        <v>35.01894061048373</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>5.153193699591506</v>
+        <v>4.797801030654161</v>
       </c>
       <c r="C11" t="n">
-        <v>32.51842920776709</v>
+        <v>33.22921454564179</v>
       </c>
       <c r="D11" t="n">
-        <v>36.07235589714055</v>
+        <v>36.25005223160922</v>
       </c>
     </row>
     <row r="12">
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4.122358610132356</v>
+        <v>3.905392367493811</v>
       </c>
       <c r="C12" t="n">
-        <v>31.67707142522758</v>
+        <v>29.72437524148068</v>
       </c>
       <c r="D12" t="n">
-        <v>36.23336252063703</v>
+        <v>35.36549755008285</v>
       </c>
     </row>
     <row r="13">
@@ -1245,10 +1245,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.121957699504857</v>
+        <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>29.13827186204534</v>
+        <v>27.3171298706675</v>
       </c>
       <c r="D13" t="n">
         <v>33.04071898642641</v>
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.151009220004762</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>26.11939767148639</v>
+        <v>25.19753657719863</v>
       </c>
       <c r="D14" t="n">
-        <v>31.34327720578367</v>
+        <v>30.42141611149592</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>23.65030219530566</v>
+        <v>22.57528845915541</v>
       </c>
       <c r="D15" t="n">
-        <v>29.74204670015712</v>
+        <v>29.38370878810703</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>21.07910495788326</v>
+        <v>20.25247339090745</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>26.45221014322606</v>
       </c>
     </row>
     <row r="17">
@@ -1304,7 +1304,7 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>19.36104647545135</v>
+        <v>18.41660518396592</v>
       </c>
       <c r="D17" t="n">
         <v>24.55547357862122</v>
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.925883625523781</v>
+        <v>7.832657011222283</v>
       </c>
       <c r="C21" t="n">
-        <v>106.0086934913806</v>
+        <v>100.8454590194869</v>
       </c>
       <c r="D21" t="n">
-        <v>9.907354531904726</v>
+        <v>8.811739137625068</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>9.534733703645022</v>
+        <v>8.613854357061514</v>
       </c>
       <c r="C2" t="n">
-        <v>12.36805757810132</v>
+        <v>16.95576460004666</v>
       </c>
       <c r="D2" t="n">
-        <v>19.52598008976481</v>
+        <v>26.21757244191107</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21.35301256736813</v>
+        <v>22.61455836732528</v>
       </c>
       <c r="C3" t="n">
-        <v>23.21833320543707</v>
+        <v>37.80710409054467</v>
       </c>
       <c r="D3" t="n">
-        <v>63.78414834491527</v>
+        <v>50.78090000216627</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>36.42480332296516</v>
+        <v>34.88051418418493</v>
       </c>
       <c r="C4" t="n">
-        <v>47.92401418280805</v>
+        <v>97.77519910905259</v>
       </c>
       <c r="D4" t="n">
-        <v>102.8164735703599</v>
+        <v>72.00726711568656</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>55.19876467127693</v>
+        <v>54.78152189697203</v>
       </c>
       <c r="C5" t="n">
-        <v>92.40700266223104</v>
+        <v>164.2463909204914</v>
       </c>
       <c r="D5" t="n">
-        <v>90.88529372064848</v>
+        <v>61.67829951930587</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>66.17372225705202</v>
+        <v>65.24793417194728</v>
       </c>
       <c r="C6" t="n">
-        <v>120.0304378166235</v>
+        <v>203.5123720995468</v>
       </c>
       <c r="D6" t="n">
-        <v>65.85170901005907</v>
+        <v>48.98626519880311</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>56.35329997147116</v>
+        <v>55.51488743204438</v>
       </c>
       <c r="C7" t="n">
-        <v>109.6523828350305</v>
+        <v>207.2675570682908</v>
       </c>
       <c r="D7" t="n">
-        <v>48.74770050667112</v>
+        <v>42.27994663109313</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>37.38495257771854</v>
+        <v>34.38080460272329</v>
       </c>
       <c r="C8" t="n">
-        <v>82.86441497695203</v>
+        <v>179.8316357254095</v>
       </c>
       <c r="D8" t="n">
-        <v>42.05807164993335</v>
+        <v>39.05392367493811</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>19.96874830438012</v>
+        <v>17.08437354930299</v>
       </c>
       <c r="C9" t="n">
-        <v>57.79843259212245</v>
+        <v>125.4703018458551</v>
       </c>
       <c r="D9" t="n">
-        <v>37.16405934426299</v>
+        <v>36.16562192904399</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.537678946757763</v>
+        <v>8.114144775599888</v>
       </c>
       <c r="C10" t="n">
-        <v>42.84837855185204</v>
+        <v>71.46141539212533</v>
       </c>
       <c r="D10" t="n">
-        <v>37.29659528433633</v>
+        <v>35.44600086183109</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>5.686282702997524</v>
+        <v>5.153193699591506</v>
       </c>
       <c r="C11" t="n">
-        <v>36.25005223160922</v>
+        <v>41.5809422656694</v>
       </c>
       <c r="D11" t="n">
-        <v>36.42774856607789</v>
+        <v>36.60544490054656</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4.339324852770901</v>
+        <v>4.122358610132356</v>
       </c>
       <c r="C12" t="n">
-        <v>34.49763257952867</v>
+        <v>32.76190263842031</v>
       </c>
       <c r="D12" t="n">
-        <v>36.66729500591412</v>
+        <v>35.58246379272139</v>
       </c>
     </row>
     <row r="13">
@@ -1556,10 +1556,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.382120841130262</v>
+        <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>31.73990327829938</v>
+        <v>29.65859814529614</v>
       </c>
       <c r="D13" t="n">
         <v>33.56104526967722</v>
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.151009220004762</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>28.88498095434966</v>
+        <v>26.73397173434489</v>
       </c>
       <c r="D14" t="n">
-        <v>31.65056423721292</v>
+        <v>30.42141611149592</v>
       </c>
     </row>
     <row r="15">
@@ -1587,10 +1587,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>25.44199175555609</v>
+        <v>24.00864010735575</v>
       </c>
       <c r="D15" t="n">
-        <v>29.74204670015712</v>
+        <v>29.38370878810703</v>
       </c>
     </row>
     <row r="16">
@@ -1601,10 +1601,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>22.7323680918349</v>
+        <v>21.49242074137117</v>
       </c>
       <c r="D16" t="n">
-        <v>27.27884171020187</v>
+        <v>26.45221014322606</v>
       </c>
     </row>
     <row r="17">
@@ -1615,7 +1615,7 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>20.30548776693678</v>
+        <v>19.36104647545135</v>
       </c>
       <c r="D17" t="n">
         <v>24.55547357862122</v>
@@ -1629,7 +1629,7 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>19.26188995732242</v>
+        <v>18.72683745850791</v>
       </c>
       <c r="D18" t="n">
         <v>20.86704745376595</v>
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8.107836240710899</v>
+        <v>7.987453498880665</v>
       </c>
       <c r="C21" t="n">
-        <v>114.5231869000414</v>
+        <v>107.830622234889</v>
       </c>
       <c r="D21" t="n">
-        <v>11.14827483097748</v>
+        <v>9.984316873600832</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8.44008501340983</v>
+        <v>7.978663592413827</v>
       </c>
       <c r="C2" t="n">
-        <v>8.014006509766713</v>
+        <v>11.93608858823272</v>
       </c>
       <c r="D2" t="n">
-        <v>15.83166347868406</v>
+        <v>21.46100481483527</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>26.12430641000763</v>
+        <v>25.2996383384403</v>
       </c>
       <c r="C3" t="n">
-        <v>38.58759351542088</v>
+        <v>60.67691686097411</v>
       </c>
       <c r="D3" t="n">
-        <v>71.56449890107125</v>
+        <v>54.81588306662066</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>26.52093248252334</v>
+        <v>26.31672896004</v>
       </c>
       <c r="C4" t="n">
-        <v>74.18969226222723</v>
+        <v>133.6129173048782</v>
       </c>
       <c r="D4" t="n">
-        <v>100.8510146664578</v>
+        <v>69.17394324123026</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>37.28186906877263</v>
+        <v>36.74190783143688</v>
       </c>
       <c r="C5" t="n">
-        <v>71.71666979522951</v>
+        <v>121.5894531709675</v>
       </c>
       <c r="D5" t="n">
-        <v>65.50711556586843</v>
+        <v>45.84761778832605</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>34.97868895460962</v>
+        <v>34.45541742824607</v>
       </c>
       <c r="C6" t="n">
-        <v>72.2114706381699</v>
+        <v>136.4933650691383</v>
       </c>
       <c r="D6" t="n">
-        <v>32.08056973167303</v>
+        <v>27.81389420901639</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>24.73316991308989</v>
+        <v>22.75691178444107</v>
       </c>
       <c r="C7" t="n">
-        <v>58.26967149016093</v>
+        <v>126.420633623566</v>
       </c>
       <c r="D7" t="n">
-        <v>29.52409870981433</v>
+        <v>27.42806736124739</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>13.85246010692249</v>
+        <v>11.849694790259</v>
       </c>
       <c r="C8" t="n">
-        <v>42.55876297909923</v>
+        <v>92.46099878596459</v>
       </c>
       <c r="D8" t="n">
-        <v>27.37112599440107</v>
+        <v>26.62008900065226</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.767186925373262</v>
+        <v>5.768749510154256</v>
       </c>
       <c r="C9" t="n">
-        <v>32.61562223048752</v>
+        <v>54.47030787472577</v>
       </c>
       <c r="D9" t="n">
-        <v>28.39999758845172</v>
+        <v>27.06874770149305</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.128249096357838</v>
+        <v>3.701188845010476</v>
       </c>
       <c r="C10" t="n">
-        <v>28.32833000604172</v>
+        <v>32.59893251951534</v>
       </c>
       <c r="D10" t="n">
-        <v>28.47068342315751</v>
+        <v>28.61303684027329</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.198534020436107</v>
+        <v>3.020837685967435</v>
       </c>
       <c r="C11" t="n">
-        <v>27.54293184264426</v>
+        <v>26.12136116689488</v>
       </c>
       <c r="D11" t="n">
-        <v>29.31989518733098</v>
+        <v>28.43141351498762</v>
       </c>
     </row>
     <row r="12">
@@ -1853,10 +1853,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.603594911662541</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C12" t="n">
-        <v>25.81898287398687</v>
+        <v>24.0832529328785</v>
       </c>
       <c r="D12" t="n">
         <v>27.33774657245668</v>
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1.560978849752429</v>
+        <v>1.300815708127024</v>
       </c>
       <c r="C13" t="n">
-        <v>23.93500902953724</v>
+        <v>22.11386703815941</v>
       </c>
       <c r="D13" t="n">
-        <v>26.01631416254048</v>
+        <v>25.23582473766426</v>
       </c>
     </row>
     <row r="14">
@@ -1884,10 +1884,10 @@
         <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>21.20280516861837</v>
+        <v>19.97365704290136</v>
       </c>
       <c r="D14" t="n">
-        <v>24.89024954576939</v>
+        <v>24.58296251434014</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>18.99190933865455</v>
+        <v>17.91689560250429</v>
       </c>
       <c r="D15" t="n">
-        <v>22.93362637120549</v>
+        <v>22.21695054710532</v>
       </c>
     </row>
     <row r="16">
@@ -1912,7 +1912,7 @@
         <v>0.4133157834879072</v>
       </c>
       <c r="C16" t="n">
-        <v>17.3592629064921</v>
+        <v>16.53263133951629</v>
       </c>
       <c r="D16" t="n">
         <v>20.66578917439536</v>
@@ -1926,7 +1926,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>16.52772260099505</v>
+        <v>16.05550195525234</v>
       </c>
       <c r="D17" t="n">
         <v>17.9443845382232</v>
@@ -1968,10 +1968,10 @@
         <v>5.37997741927252</v>
       </c>
       <c r="C20" t="n">
-        <v>75.31968386981528</v>
+        <v>72.62969516017901</v>
       </c>
       <c r="D20" t="n">
-        <v>7.397468951499714</v>
+        <v>6.724971774090649</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.029493488856409</v>
+        <v>4.944081438586937</v>
       </c>
       <c r="C2" t="n">
-        <v>3.549999698556466</v>
+        <v>5.282784396552087</v>
       </c>
       <c r="D2" t="n">
-        <v>12.33565990386117</v>
+        <v>15.62549646079223</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>28.53940576245478</v>
+        <v>26.8851608807989</v>
       </c>
       <c r="C3" t="n">
-        <v>35.41163969218245</v>
+        <v>54.74225198880215</v>
       </c>
       <c r="D3" t="n">
-        <v>68.41799750896023</v>
+        <v>59.32210502911352</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>37.6755498981756</v>
+        <v>35.53141291210056</v>
       </c>
       <c r="C4" t="n">
-        <v>88.53498971668159</v>
+        <v>146.8478581058294</v>
       </c>
       <c r="D4" t="n">
-        <v>113.6264975418216</v>
+        <v>78.95018688012</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>41.08614142272902</v>
+        <v>40.20256848890689</v>
       </c>
       <c r="C5" t="n">
-        <v>104.9979169691964</v>
+        <v>178.1626646281899</v>
       </c>
       <c r="D5" t="n">
-        <v>82.02502068982102</v>
+        <v>55.37057051952011</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>42.38499363544755</v>
+        <v>40.21140421824511</v>
       </c>
       <c r="C6" t="n">
-        <v>92.86057010159307</v>
+        <v>164.06574934291</v>
       </c>
       <c r="D6" t="n">
-        <v>40.57366912111219</v>
+        <v>32.36233132279187</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>24.07441720354028</v>
+        <v>21.19985992550562</v>
       </c>
       <c r="C7" t="n">
-        <v>78.27179921648545</v>
+        <v>157.0226913126434</v>
       </c>
       <c r="D7" t="n">
-        <v>32.15910954801276</v>
+        <v>29.64387192973244</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>11.59934912567606</v>
+        <v>9.680032363873551</v>
       </c>
       <c r="C8" t="n">
-        <v>56.24432597629976</v>
+        <v>118.2466022380071</v>
       </c>
       <c r="D8" t="n">
-        <v>29.12354564648163</v>
+        <v>27.37112599440107</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.324999547834698</v>
+        <v>4.548437113775471</v>
       </c>
       <c r="C9" t="n">
-        <v>39.04999668412111</v>
+        <v>58.13124506386212</v>
       </c>
       <c r="D9" t="n">
-        <v>29.28749751309084</v>
+        <v>28.28906009787183</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.420008090968388</v>
+        <v>2.135301256736813</v>
       </c>
       <c r="C10" t="n">
-        <v>32.02951885105219</v>
+        <v>34.16482010778901</v>
       </c>
       <c r="D10" t="n">
-        <v>30.03657101143117</v>
+        <v>29.60951076008381</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.954659679155399</v>
+        <v>1.599267010218054</v>
       </c>
       <c r="C11" t="n">
-        <v>31.09685853201771</v>
+        <v>28.78680618392497</v>
       </c>
       <c r="D11" t="n">
-        <v>30.20837685967435</v>
+        <v>29.67528785626833</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>1.084831213192725</v>
+        <v>0.8678649705541803</v>
       </c>
       <c r="C12" t="n">
-        <v>22.56448923440869</v>
+        <v>20.17786056538469</v>
       </c>
       <c r="D12" t="n">
-        <v>28.8565102709265</v>
+        <v>28.20561154301086</v>
       </c>
     </row>
     <row r="13">
@@ -2181,10 +2181,10 @@
         <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>17.43093048890212</v>
+        <v>16.3902779224005</v>
       </c>
       <c r="D13" t="n">
-        <v>26.27647730416588</v>
+        <v>25.75615102091507</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>15.67163860289184</v>
+        <v>15.05706454003333</v>
       </c>
       <c r="D14" t="n">
-        <v>19.0517959486136</v>
+        <v>18.4372218857551</v>
       </c>
     </row>
     <row r="15">
@@ -2209,7 +2209,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>14.69185439405351</v>
+        <v>13.97517856995334</v>
       </c>
       <c r="D15" t="n">
         <v>17.5585576904542</v>
@@ -2223,7 +2223,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>14.05273663858884</v>
+        <v>13.63942085510094</v>
       </c>
       <c r="D16" t="n">
         <v>15.29268398905256</v>
@@ -2265,10 +2265,10 @@
         <v>4.212679398923063</v>
       </c>
       <c r="C19" t="n">
-        <v>65.59743635465912</v>
+        <v>63.19019098384595</v>
       </c>
       <c r="D19" t="n">
-        <v>6.018113427032947</v>
+        <v>5.416302084329653</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.816855147662351</v>
+        <v>4.711407232680442</v>
       </c>
       <c r="C2" t="n">
-        <v>3.265292864324891</v>
+        <v>8.94470333339269</v>
       </c>
       <c r="D2" t="n">
-        <v>16.12226079914112</v>
+        <v>12.97477765932585</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>22.86981277042945</v>
+        <v>21.84879515801277</v>
       </c>
       <c r="C3" t="n">
-        <v>23.10543221944868</v>
+        <v>37.36531762363361</v>
       </c>
       <c r="D3" t="n">
-        <v>63.22946089201582</v>
+        <v>57.88875338091317</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>46.43077592464865</v>
+        <v>42.88273972150068</v>
       </c>
       <c r="C4" t="n">
-        <v>89.40285468723579</v>
+        <v>141.6661937228147</v>
       </c>
       <c r="D4" t="n">
-        <v>121.2713669147915</v>
+        <v>88.82853228025141</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>49.06284151973436</v>
+        <v>46.04396732917541</v>
       </c>
       <c r="C5" t="n">
-        <v>135.3830084156352</v>
+        <v>221.4822820780805</v>
       </c>
       <c r="D5" t="n">
-        <v>100.9972950743906</v>
+        <v>68.50144606382121</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>49.71079500453725</v>
+        <v>46.32965591111124</v>
       </c>
       <c r="C6" t="n">
-        <v>130.8581332467616</v>
+        <v>219.4520278256981</v>
       </c>
       <c r="D6" t="n">
-        <v>55.74854338565514</v>
+        <v>40.33215918586747</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>35.69241953559704</v>
+        <v>31.38058361854505</v>
       </c>
       <c r="C7" t="n">
-        <v>106.5382791171596</v>
+        <v>192.7749974581994</v>
       </c>
       <c r="D7" t="n">
-        <v>35.93196597543326</v>
+        <v>31.85967649821749</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>17.35729941108361</v>
+        <v>14.18625432636641</v>
       </c>
       <c r="C8" t="n">
-        <v>79.52647278251287</v>
+        <v>158.7191513455818</v>
       </c>
       <c r="D8" t="n">
-        <v>30.95941385342316</v>
+        <v>29.12354564648163</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>7.654686850012379</v>
+        <v>6.101561981893925</v>
       </c>
       <c r="C9" t="n">
-        <v>53.69374544066654</v>
+        <v>95.07342942696533</v>
       </c>
       <c r="D9" t="n">
-        <v>30.17499743772996</v>
+        <v>28.84374755077128</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3.131775176547325</v>
+        <v>2.562361508084175</v>
       </c>
       <c r="C10" t="n">
-        <v>39.28954312395736</v>
+        <v>47.54604131667303</v>
       </c>
       <c r="D10" t="n">
-        <v>30.89069151412589</v>
+        <v>30.17892442854695</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.954659679155399</v>
+        <v>1.599267010218054</v>
       </c>
       <c r="C11" t="n">
-        <v>34.65078522139116</v>
+        <v>33.40691088011046</v>
       </c>
       <c r="D11" t="n">
-        <v>30.74146586308036</v>
+        <v>29.852984190737</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>1.084831213192725</v>
+        <v>0.8678649705541803</v>
       </c>
       <c r="C12" t="n">
-        <v>27.55471281509523</v>
+        <v>24.5171854181556</v>
       </c>
       <c r="D12" t="n">
-        <v>29.29044275620359</v>
+        <v>28.8565102709265</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>20.29272504678157</v>
+        <v>18.47158305540374</v>
       </c>
       <c r="D13" t="n">
-        <v>26.79680358741669</v>
+        <v>26.01631416254048</v>
       </c>
     </row>
     <row r="14">
@@ -2506,10 +2506,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>16.90078672860884</v>
+        <v>15.97892563432109</v>
       </c>
       <c r="D14" t="n">
-        <v>19.97365704290136</v>
+        <v>19.0517959486136</v>
       </c>
     </row>
     <row r="15">
@@ -2520,10 +2520,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>16.12520604225386</v>
+        <v>15.76686813020377</v>
       </c>
       <c r="D15" t="n">
-        <v>17.5585576904542</v>
+        <v>17.20021977840412</v>
       </c>
     </row>
     <row r="16">
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>15.70599977254047</v>
+        <v>14.46605242207675</v>
       </c>
       <c r="D16" t="n">
         <v>14.87936820556466</v>
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>36.10868056219768</v>
+        <v>33.09962384868121</v>
       </c>
       <c r="D19" t="n">
-        <v>4.212679398923063</v>
+        <v>3.610868056219768</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.347759671481624</v>
+        <v>2.876520773443155</v>
       </c>
       <c r="C2" t="n">
-        <v>1.442187377538564</v>
+        <v>4.339324852770901</v>
       </c>
       <c r="D2" t="n">
-        <v>11.00833700771949</v>
+        <v>9.042878103817371</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>23.61594102565702</v>
+        <v>21.46591355335651</v>
       </c>
       <c r="C3" t="n">
-        <v>19.75767254796706</v>
+        <v>38.70049450140927</v>
       </c>
       <c r="D3" t="n">
-        <v>63.69579105153306</v>
+        <v>57.31443097392879</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>52.17399999449249</v>
+        <v>47.20930185411637</v>
       </c>
       <c r="C4" t="n">
-        <v>86.27598824920969</v>
+        <v>138.6414290460303</v>
       </c>
       <c r="D4" t="n">
-        <v>129.1204398102448</v>
+        <v>96.39682533229008</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>52.44987109938586</v>
+        <v>48.30198704894308</v>
       </c>
       <c r="C5" t="n">
-        <v>161.0802545742954</v>
+        <v>269.0234146562323</v>
       </c>
       <c r="D5" t="n">
-        <v>109.2439757900639</v>
+        <v>72.25663103256525</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>43.75354993516761</v>
+        <v>37.43403996293088</v>
       </c>
       <c r="C6" t="n">
-        <v>165.1927957073853</v>
+        <v>251.4520942456228</v>
       </c>
       <c r="D6" t="n">
-        <v>54.82275530055039</v>
+        <v>40.01014593887452</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>11.49822911213864</v>
+        <v>9.402197763571703</v>
       </c>
       <c r="C7" t="n">
-        <v>111.0297748640888</v>
+        <v>203.9139069105838</v>
       </c>
       <c r="D7" t="n">
-        <v>36.11162580531042</v>
+        <v>32.39865598784899</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.257258956241669</v>
+        <v>4.172427743048944</v>
       </c>
       <c r="C8" t="n">
-        <v>66.00780689503429</v>
+        <v>115.1590057081509</v>
       </c>
       <c r="D8" t="n">
-        <v>32.62838495064274</v>
+        <v>30.79251674370121</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.218749811597791</v>
+        <v>1.774999849278233</v>
       </c>
       <c r="C9" t="n">
-        <v>29.95312245657017</v>
+        <v>36.27655941962388</v>
       </c>
       <c r="D9" t="n">
-        <v>32.72655972106742</v>
+        <v>31.50624732468863</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.423534171157875</v>
+        <v>1.1388273369263</v>
       </c>
       <c r="C10" t="n">
-        <v>27.18950266911542</v>
+        <v>26.1930287493049</v>
       </c>
       <c r="D10" t="n">
-        <v>24.05772749256809</v>
+        <v>23.34596040698915</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.7107853378746906</v>
+        <v>0.5330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>22.0343454741154</v>
+        <v>19.54659679155399</v>
       </c>
       <c r="D11" t="n">
-        <v>23.45591614986479</v>
+        <v>23.10052348092744</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>16.48943444052943</v>
+        <v>14.97067074205961</v>
       </c>
       <c r="D12" t="n">
-        <v>21.69662426385451</v>
+        <v>21.26269177857742</v>
       </c>
     </row>
     <row r="13">
@@ -2803,10 +2803,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.78864650614645</v>
+        <v>13.00815708127024</v>
       </c>
       <c r="D13" t="n">
-        <v>16.3902779224005</v>
+        <v>15.60978849752428</v>
       </c>
     </row>
     <row r="14">
@@ -2817,10 +2817,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>13.52062938288707</v>
+        <v>13.21334235145782</v>
       </c>
       <c r="D14" t="n">
-        <v>14.74977750860408</v>
+        <v>14.44249047717483</v>
       </c>
     </row>
     <row r="15">
@@ -2831,7 +2831,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>13.25850274585317</v>
+        <v>12.18348900970292</v>
       </c>
       <c r="D15" t="n">
         <v>12.541826921753</v>
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>31.03304493124168</v>
+        <v>28.35778243716912</v>
       </c>
       <c r="D18" t="n">
-        <v>3.21031499288707</v>
+        <v>2.675262494072558</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.389393985687489</v>
+        <v>3.251548396465436</v>
       </c>
       <c r="C2" t="n">
-        <v>4.995132319207771</v>
+        <v>4.021238596594936</v>
       </c>
       <c r="D2" t="n">
-        <v>11.13203721845458</v>
+        <v>11.53062678637879</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.5585576904542</v>
+        <v>15.82577299245858</v>
       </c>
       <c r="C3" t="n">
-        <v>12.02640937702343</v>
+        <v>28.01907947920397</v>
       </c>
       <c r="D3" t="n">
-        <v>58.06546796767761</v>
+        <v>52.00317589395354</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>49.53211692236432</v>
+        <v>44.60570694245383</v>
       </c>
       <c r="C4" t="n">
-        <v>67.54031506136356</v>
+        <v>118.5911956821977</v>
       </c>
       <c r="D4" t="n">
-        <v>131.4943057591135</v>
+        <v>101.5402015548391</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>64.45173678380311</v>
+        <v>57.5304154688631</v>
       </c>
       <c r="C5" t="n">
-        <v>161.595672119025</v>
+        <v>264.949161683608</v>
       </c>
       <c r="D5" t="n">
-        <v>129.6643280383975</v>
+        <v>86.34471058850698</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>55.30577517103983</v>
+        <v>47.89947049020189</v>
       </c>
       <c r="C6" t="n">
-        <v>209.8318820717836</v>
+        <v>328.1717503416941</v>
       </c>
       <c r="D6" t="n">
-        <v>71.96996070292518</v>
+        <v>50.39507315439728</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>26.11056194214817</v>
+        <v>19.76258128648829</v>
       </c>
       <c r="C7" t="n">
-        <v>171.2158178729395</v>
+        <v>272.8433949734565</v>
       </c>
       <c r="D7" t="n">
-        <v>42.27994663109313</v>
+        <v>35.2133266559246</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>7.510369937488099</v>
+        <v>5.757950285407543</v>
       </c>
       <c r="C8" t="n">
-        <v>101.9741340401162</v>
+        <v>175.3254137629166</v>
       </c>
       <c r="D8" t="n">
-        <v>34.63115026730623</v>
+        <v>32.29459073119883</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.884374755077128</v>
+        <v>2.107812321017901</v>
       </c>
       <c r="C9" t="n">
-        <v>51.14218315732908</v>
+        <v>72.77499382040753</v>
       </c>
       <c r="D9" t="n">
-        <v>33.72499713628642</v>
+        <v>32.28280975874785</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.565887588273662</v>
+        <v>1.1388273369263</v>
       </c>
       <c r="C10" t="n">
-        <v>31.60245859970483</v>
+        <v>32.02951885105219</v>
       </c>
       <c r="D10" t="n">
-        <v>25.62361508084176</v>
+        <v>24.62714116103124</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.5330890034060179</v>
+        <v>0.3553926689373453</v>
       </c>
       <c r="C11" t="n">
-        <v>25.9436648324262</v>
+        <v>23.10052348092744</v>
       </c>
       <c r="D11" t="n">
-        <v>24.16670148773948</v>
+        <v>23.98900515327081</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>19.09302935219197</v>
+        <v>17.14033316844506</v>
       </c>
       <c r="D12" t="n">
-        <v>22.34752299177014</v>
+        <v>21.26269177857742</v>
       </c>
     </row>
     <row r="13">
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>16.3902779224005</v>
+        <v>14.82929907264807</v>
       </c>
       <c r="D13" t="n">
-        <v>16.3902779224005</v>
+        <v>15.60978849752428</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>14.44249047717483</v>
+        <v>13.82791641431633</v>
       </c>
       <c r="D14" t="n">
-        <v>14.44249047717483</v>
+        <v>14.13520344574558</v>
       </c>
     </row>
     <row r="15">
@@ -3142,7 +3142,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>14.33351648200343</v>
+        <v>13.25850274585317</v>
       </c>
       <c r="D15" t="n">
         <v>11.82515109765283</v>
@@ -3156,7 +3156,7 @@
         <v>1.653263133951629</v>
       </c>
       <c r="C16" t="n">
-        <v>23.55899965881071</v>
+        <v>23.97231544229862</v>
       </c>
       <c r="D16" t="n">
         <v>8.266315669758143</v>
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>34.94432778496098</v>
+        <v>33.0554452019901</v>
       </c>
       <c r="D17" t="n">
-        <v>4.722206457427158</v>
+        <v>4.249985811684442</v>
       </c>
     </row>
     <row r="18">
@@ -3184,7 +3184,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>1.070104997629023</v>
+        <v>0.5350524988145117</v>
       </c>
       <c r="D18" t="n">
         <v>1.070104997629023</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.307508015607504</v>
+        <v>2.258019719767664</v>
       </c>
       <c r="C2" t="n">
-        <v>3.639338739642926</v>
+        <v>3.445934441906304</v>
       </c>
       <c r="D2" t="n">
-        <v>9.130253649495335</v>
+        <v>8.892670705067609</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.69461971071701</v>
+        <v>13.99972226255952</v>
       </c>
       <c r="C3" t="n">
-        <v>15.82086425393735</v>
+        <v>22.89435646303562</v>
       </c>
       <c r="D3" t="n">
-        <v>54.50172380126168</v>
+        <v>49.88750959130167</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>44.47807974090174</v>
+        <v>39.83244960440584</v>
       </c>
       <c r="C4" t="n">
-        <v>52.05913551309561</v>
+        <v>101.9741340401162</v>
       </c>
       <c r="D4" t="n">
-        <v>131.5581193598896</v>
+        <v>103.6205249401381</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>70.29313562407164</v>
+        <v>62.63550353094652</v>
       </c>
       <c r="C5" t="n">
-        <v>151.9500009248001</v>
+        <v>254.6653544816227</v>
       </c>
       <c r="D5" t="n">
-        <v>143.5806017460961</v>
+        <v>96.87395471655404</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>65.97246397768143</v>
+        <v>55.06426523579511</v>
       </c>
       <c r="C6" t="n">
-        <v>237.0822530985623</v>
+        <v>372.7705850502182</v>
       </c>
       <c r="D6" t="n">
-        <v>85.97753694711868</v>
+        <v>57.7611261793611</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>26.35010838198439</v>
+        <v>17.48689010804419</v>
       </c>
       <c r="C7" t="n">
-        <v>221.520570238546</v>
+        <v>339.9762847375577</v>
       </c>
       <c r="D7" t="n">
-        <v>48.38838084691679</v>
+        <v>38.50709020367265</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>6.175193059712437</v>
+        <v>4.589670517353839</v>
       </c>
       <c r="C8" t="n">
-        <v>137.1059756365883</v>
+        <v>222.5572958142307</v>
       </c>
       <c r="D8" t="n">
-        <v>36.38356991938679</v>
+        <v>33.54631905411351</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.218749811597791</v>
+        <v>1.553124868118454</v>
       </c>
       <c r="C9" t="n">
-        <v>64.23280704575605</v>
+        <v>78.98749329288135</v>
       </c>
       <c r="D9" t="n">
-        <v>33.72499713628642</v>
+        <v>31.94999728700819</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.5694136684631501</v>
+        <v>0.4270602513473625</v>
       </c>
       <c r="C10" t="n">
-        <v>33.59540643932586</v>
+        <v>32.17187226816798</v>
       </c>
       <c r="D10" t="n">
-        <v>26.05067533218912</v>
+        <v>25.19655482949439</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>25.58827216348886</v>
+        <v>22.38973814305275</v>
       </c>
       <c r="D11" t="n">
-        <v>24.6997904911455</v>
+        <v>23.98900515327081</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>18.65909686691488</v>
+        <v>16.27246819789088</v>
       </c>
       <c r="D12" t="n">
-        <v>20.82875929330033</v>
+        <v>19.7439280801076</v>
       </c>
     </row>
     <row r="13">
@@ -3425,10 +3425,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>11.96750451476862</v>
+        <v>11.44717823151781</v>
       </c>
       <c r="D13" t="n">
-        <v>16.65044106402591</v>
+        <v>15.86995163914969</v>
       </c>
     </row>
     <row r="14">
@@ -3439,7 +3439,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.98419422574081</v>
+        <v>11.06233313145306</v>
       </c>
       <c r="D14" t="n">
         <v>11.06233313145306</v>
@@ -3453,7 +3453,7 @@
         <v>1.075013736150257</v>
       </c>
       <c r="C15" t="n">
-        <v>19.70858516275472</v>
+        <v>20.0669230748048</v>
       </c>
       <c r="D15" t="n">
         <v>6.808420328951629</v>
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>29.75873641112932</v>
+        <v>28.10547327717769</v>
       </c>
       <c r="D16" t="n">
-        <v>3.719842051391165</v>
+        <v>3.306526267903257</v>
       </c>
     </row>
     <row r="17">
@@ -3481,7 +3481,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>0.4722206457427158</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
         <v>0.4722206457427158</v>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.053456344385832</v>
+        <v>3.911282853719293</v>
       </c>
       <c r="C2" t="n">
-        <v>10.49880994921539</v>
+        <v>8.162250413107982</v>
       </c>
       <c r="D2" t="n">
-        <v>12.8815116274224</v>
+        <v>9.143998117354792</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>13.96536109291088</v>
+        <v>11.02993545721291</v>
       </c>
       <c r="C3" t="n">
-        <v>14.88329519638165</v>
+        <v>18.53539665617978</v>
       </c>
       <c r="D3" t="n">
-        <v>49.78933482087699</v>
+        <v>46.16668579220626</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>38.67104207028186</v>
+        <v>33.9488356128547</v>
       </c>
       <c r="C4" t="n">
-        <v>45.93302983859552</v>
+        <v>82.72795204606172</v>
       </c>
       <c r="D4" t="n">
-        <v>129.1076770900895</v>
+        <v>103.9651183843287</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>69.0904946863693</v>
+        <v>61.31014413021332</v>
       </c>
       <c r="C5" t="n">
-        <v>127.3572209334175</v>
+        <v>226.8573507588318</v>
       </c>
       <c r="D5" t="n">
-        <v>154.9688751153591</v>
+        <v>105.7587714399877</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>78.24921901928779</v>
+        <v>65.16743086019903</v>
       </c>
       <c r="C6" t="n">
-        <v>239.9401206656247</v>
+        <v>386.1341348004258</v>
       </c>
       <c r="D6" t="n">
-        <v>104.0907820904723</v>
+        <v>69.63536466222628</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>45.63359678880023</v>
+        <v>32.09922293805371</v>
       </c>
       <c r="C7" t="n">
-        <v>274.1010137825967</v>
+        <v>415.5531865058856</v>
       </c>
       <c r="D7" t="n">
-        <v>58.74876436983337</v>
+        <v>43.6573386601514</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>13.76901155206151</v>
+        <v>8.511752595819845</v>
       </c>
       <c r="C8" t="n">
-        <v>203.9482680802324</v>
+        <v>308.342410211317</v>
       </c>
       <c r="D8" t="n">
-        <v>40.3056519978528</v>
+        <v>35.29873870619407</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>3.439062207976575</v>
+        <v>2.32968730217768</v>
       </c>
       <c r="C9" t="n">
-        <v>106.3890534661141</v>
+        <v>145.5499876408151</v>
       </c>
       <c r="D9" t="n">
-        <v>34.94530953266521</v>
+        <v>32.8374972116473</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.8541205026947251</v>
+        <v>0.5694136684631501</v>
       </c>
       <c r="C10" t="n">
-        <v>49.68134257340984</v>
+        <v>51.38958357879929</v>
       </c>
       <c r="D10" t="n">
-        <v>27.3318560862312</v>
+        <v>26.47773558353648</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>30.74146586308036</v>
+        <v>26.83214650476957</v>
       </c>
       <c r="D11" t="n">
-        <v>25.23287949455151</v>
+        <v>24.16670148773948</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>22.1305567491316</v>
+        <v>18.87606310955342</v>
       </c>
       <c r="D12" t="n">
-        <v>21.26269177857742</v>
+        <v>20.17786056538469</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>14.30897278939726</v>
+        <v>13.00815708127024</v>
       </c>
       <c r="D13" t="n">
-        <v>16.91060420565131</v>
+        <v>16.1301147807751</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>12.59876828859932</v>
+        <v>11.67690719431156</v>
       </c>
       <c r="D14" t="n">
-        <v>11.36962016288231</v>
+        <v>11.06233313145306</v>
       </c>
     </row>
     <row r="15">
@@ -3764,10 +3764,10 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>19.70858516275472</v>
+        <v>21.14193681095506</v>
       </c>
       <c r="D15" t="n">
-        <v>6.808420328951629</v>
+        <v>6.450082416901544</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>30.17205219461722</v>
+        <v>26.45221014322606</v>
       </c>
       <c r="D16" t="n">
-        <v>3.306526267903257</v>
+        <v>2.89321048441535</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.895795874629596</v>
+        <v>6.481498343437441</v>
       </c>
       <c r="C2" t="n">
-        <v>3.523492510541802</v>
+        <v>13.95259837275567</v>
       </c>
       <c r="D2" t="n">
-        <v>10.31424138081699</v>
+        <v>5.324017800130453</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.188135706316893</v>
+        <v>2.858849314766712</v>
       </c>
       <c r="C2" t="n">
-        <v>5.710826395603696</v>
+        <v>4.8321622003028</v>
       </c>
       <c r="D2" t="n">
-        <v>9.377654070965532</v>
+        <v>6.802529842726149</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.72331137831842</v>
+        <v>15.2514505854742</v>
       </c>
       <c r="C3" t="n">
-        <v>25.72178985126643</v>
+        <v>25.16219365984575</v>
       </c>
       <c r="D3" t="n">
-        <v>55.29203070318036</v>
+        <v>49.94641445355648</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>52.95252592396021</v>
+        <v>46.5073522455799</v>
       </c>
       <c r="C4" t="n">
-        <v>67.7317558636917</v>
+        <v>121.9605538031728</v>
       </c>
       <c r="D4" t="n">
-        <v>135.0678674025719</v>
+        <v>105.0116614370558</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>47.27115195948392</v>
+        <v>37.28186906877263</v>
       </c>
       <c r="C5" t="n">
-        <v>197.1840263979719</v>
+        <v>333.0579086657305</v>
       </c>
       <c r="D5" t="n">
-        <v>143.5315143608837</v>
+        <v>97.36482856867744</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>28.33716573537994</v>
+        <v>19.92456965768902</v>
       </c>
       <c r="C6" t="n">
-        <v>234.626902090241</v>
+        <v>338.0334060308533</v>
       </c>
       <c r="D6" t="n">
-        <v>85.29325879725866</v>
+        <v>58.72716592033996</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.102764713776425</v>
+        <v>5.629341336151211</v>
       </c>
       <c r="C7" t="n">
-        <v>143.4284308519377</v>
+        <v>216.8494146617397</v>
       </c>
       <c r="D7" t="n">
-        <v>36.35117224514665</v>
+        <v>29.94330497952771</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>2.336559536107409</v>
+        <v>1.585522542358599</v>
       </c>
       <c r="C8" t="n">
-        <v>78.35819301445918</v>
+        <v>107.2313929963579</v>
       </c>
       <c r="D8" t="n">
-        <v>25.70215489718149</v>
+        <v>24.20008090968387</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.5546874528994477</v>
+        <v>0.3328124717396686</v>
       </c>
       <c r="C9" t="n">
-        <v>37.94062177832222</v>
+        <v>39.160934174701</v>
       </c>
       <c r="D9" t="n">
-        <v>20.85624822901923</v>
+        <v>20.1906232855399</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>24.05772749256809</v>
+        <v>20.92595231602077</v>
       </c>
       <c r="D10" t="n">
-        <v>19.78712497909446</v>
+        <v>18.93300447639974</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>17.59193711239859</v>
+        <v>15.10418842983717</v>
       </c>
       <c r="D11" t="n">
-        <v>17.05884810899257</v>
+        <v>16.17036643664921</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>11.49921085984289</v>
+        <v>10.63134588928871</v>
       </c>
       <c r="D12" t="n">
-        <v>13.66887328622834</v>
+        <v>13.0179745583127</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>10.40652566501619</v>
+        <v>9.626036240139976</v>
       </c>
       <c r="D13" t="n">
-        <v>9.365873098514571</v>
+        <v>9.105709956889166</v>
       </c>
     </row>
     <row r="14">
@@ -4372,10 +4372,10 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>16.28621266575034</v>
+        <v>17.51536079146734</v>
       </c>
       <c r="D14" t="n">
-        <v>5.53116656572653</v>
+        <v>5.223879534297279</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>25.44199175555609</v>
+        <v>22.21695054710532</v>
       </c>
       <c r="D15" t="n">
-        <v>2.5083653843506</v>
+        <v>2.150027472300515</v>
       </c>
     </row>
     <row r="16">
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.838854507783281</v>
+        <v>8.153414683769761</v>
       </c>
       <c r="C2" t="n">
-        <v>2.426880324898115</v>
+        <v>6.864379948093698</v>
       </c>
       <c r="D2" t="n">
-        <v>15.19745446174062</v>
+        <v>8.072911372021522</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.64276700884118</v>
+        <v>13.76410281354028</v>
       </c>
       <c r="C3" t="n">
-        <v>8.874999246391166</v>
+        <v>35.15638528907828</v>
       </c>
       <c r="D3" t="n">
-        <v>11.80060740504666</v>
+        <v>7.608544707912781</v>
       </c>
     </row>
     <row r="4">
@@ -4543,7 +4543,7 @@
         <v>1.008254892261474</v>
       </c>
       <c r="C4" t="n">
-        <v>1.454950097693773</v>
+        <v>1.493238258159399</v>
       </c>
       <c r="D4" t="n">
         <v>19.62906359871073</v>
@@ -4554,10 +4554,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>4.68784528777852</v>
+        <v>4.736932672990861</v>
       </c>
       <c r="C5" t="n">
-        <v>9.424777960769381</v>
+        <v>9.35114688295087</v>
       </c>
       <c r="D5" t="n">
         <v>28.49522711576368</v>
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>8.130834486572086</v>
+        <v>8.050331174823848</v>
       </c>
       <c r="C6" t="n">
         <v>18.47551004622073</v>
       </c>
       <c r="D6" t="n">
-        <v>32.52333794628834</v>
+        <v>32.8453511932813</v>
       </c>
     </row>
     <row r="7">
@@ -4588,7 +4588,7 @@
         <v>20.9603134856694</v>
       </c>
       <c r="D7" t="n">
-        <v>32.69808903764427</v>
+        <v>32.21899615797182</v>
       </c>
     </row>
     <row r="8">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.39844272309265</v>
+        <v>13.39758019061155</v>
       </c>
       <c r="C21" t="n">
-        <v>70.144788373838</v>
+        <v>70.14027276261338</v>
       </c>
       <c r="D21" t="n">
-        <v>1.576287379187371</v>
+        <v>1.576185904777829</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.5553093477052</v>
+        <v>5.909139431861552</v>
       </c>
       <c r="C2" t="n">
-        <v>3.636393496530185</v>
+        <v>4.864559874542945</v>
       </c>
       <c r="D2" t="n">
-        <v>19.53088882828605</v>
+        <v>13.23494080095125</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.06201433628357</v>
+        <v>22.37893891830604</v>
       </c>
       <c r="C3" t="n">
-        <v>9.252972112526187</v>
+        <v>29.90894380987908</v>
       </c>
       <c r="D3" t="n">
-        <v>21.71135047941821</v>
+        <v>12.54673566027424</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>16.96165508627214</v>
+        <v>15.97892563432108</v>
       </c>
       <c r="C4" t="n">
-        <v>14.28148385367835</v>
+        <v>54.11393345808419</v>
       </c>
       <c r="D4" t="n">
-        <v>21.24992905842221</v>
+        <v>19.05474119172634</v>
       </c>
     </row>
     <row r="5">
@@ -4868,10 +4868,10 @@
         <v>3.067961575771283</v>
       </c>
       <c r="C5" t="n">
-        <v>5.399612373357458</v>
+        <v>5.473243451175969</v>
       </c>
       <c r="D5" t="n">
-        <v>29.10881943091793</v>
+        <v>29.40334374219198</v>
       </c>
     </row>
     <row r="6">
@@ -4882,10 +4882,10 @@
         <v>7.446556336712058</v>
       </c>
       <c r="C6" t="n">
-        <v>16.54343056426301</v>
+        <v>16.34217228489241</v>
       </c>
       <c r="D6" t="n">
-        <v>34.77743067523902</v>
+        <v>34.57617239586842</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.521970983489814</v>
+        <v>9.462084373530759</v>
       </c>
       <c r="C7" t="n">
         <v>24.49362347325367</v>
       </c>
       <c r="D7" t="n">
-        <v>35.27321326588365</v>
+        <v>34.97378021608837</v>
       </c>
     </row>
     <row r="8">
@@ -4913,7 +4913,7 @@
         <v>25.61870634232051</v>
       </c>
       <c r="D8" t="n">
-        <v>36.80081269369168</v>
+        <v>36.63391558396972</v>
       </c>
     </row>
     <row r="9">
@@ -4921,10 +4921,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.318749208710722</v>
+        <v>9.429686699290611</v>
       </c>
       <c r="C9" t="n">
-        <v>25.5156228333746</v>
+        <v>25.73749781453438</v>
       </c>
       <c r="D9" t="n">
         <v>40.27030908049991</v>
@@ -4935,7 +4935,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.968265278294615</v>
+        <v>8.825911861178826</v>
       </c>
       <c r="C10" t="n">
         <v>27.3318560862312</v>
@@ -4949,10 +4949,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>7.463246047684251</v>
+        <v>7.640942382152923</v>
       </c>
       <c r="C11" t="n">
-        <v>29.49759152179966</v>
+        <v>29.14219885286231</v>
       </c>
       <c r="D11" t="n">
         <v>47.97801030654161</v>
@@ -4983,7 +4983,7 @@
         <v>26.79680358741669</v>
       </c>
       <c r="D13" t="n">
-        <v>44.22773407631881</v>
+        <v>44.74806035956962</v>
       </c>
     </row>
     <row r="14">
@@ -4997,7 +4997,7 @@
         <v>25.50482360862789</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>44.86390658867074</v>
       </c>
     </row>
     <row r="15">
@@ -5005,7 +5005,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.0167307687012</v>
+        <v>4.658392856651115</v>
       </c>
       <c r="C15" t="n">
         <v>26.51700549170635</v>
@@ -5025,7 +5025,7 @@
         <v>29.34542062764141</v>
       </c>
       <c r="D16" t="n">
-        <v>40.5049467818149</v>
+        <v>40.91826256530281</v>
       </c>
     </row>
     <row r="17">
@@ -5036,10 +5036,10 @@
         <v>5.66664774891259</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>31.63878326476196</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>36.36098972218912</v>
       </c>
     </row>
     <row r="18">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.44333786451974</v>
+        <v>15.43861732497823</v>
       </c>
       <c r="C21" t="n">
-        <v>86.15756913889959</v>
+        <v>86.131233497247</v>
       </c>
       <c r="D21" t="n">
-        <v>3.251229024109418</v>
+        <v>3.250235226311207</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.442809272344316</v>
+        <v>7.199155915241861</v>
       </c>
       <c r="C2" t="n">
-        <v>2.724349879284899</v>
+        <v>6.550220682734719</v>
       </c>
       <c r="D2" t="n">
-        <v>18.57073957353267</v>
+        <v>14.79395615529518</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.82362957060084</v>
+        <v>21.30392518215579</v>
       </c>
       <c r="C3" t="n">
-        <v>12.22275891787279</v>
+        <v>23.34105166846792</v>
       </c>
       <c r="D3" t="n">
-        <v>32.29459073119883</v>
+        <v>20.21909396896306</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>29.29044275620359</v>
+        <v>31.49839334305466</v>
       </c>
       <c r="C4" t="n">
-        <v>19.37380919560656</v>
+        <v>65.62590703808229</v>
       </c>
       <c r="D4" t="n">
-        <v>27.35050929261189</v>
+        <v>21.07125097624929</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>14.84893402673301</v>
+        <v>13.81809893727386</v>
       </c>
       <c r="C5" t="n">
-        <v>17.54874021341174</v>
+        <v>59.29756133650736</v>
       </c>
       <c r="D5" t="n">
-        <v>30.06602344255857</v>
+        <v>29.52606220522283</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>5.916993413495527</v>
+        <v>5.957245069369646</v>
       </c>
       <c r="C6" t="n">
-        <v>12.19625172985813</v>
+        <v>12.23650338573225</v>
       </c>
       <c r="D6" t="n">
-        <v>36.6290068454485</v>
+        <v>36.54850353370026</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.581857593448868</v>
+        <v>9.462084373530759</v>
       </c>
       <c r="C7" t="n">
-        <v>24.49362347325367</v>
+        <v>24.37385025333556</v>
       </c>
       <c r="D7" t="n">
-        <v>37.42913122440964</v>
+        <v>37.4890178343687</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.34762080276138</v>
+        <v>10.43106935762236</v>
       </c>
       <c r="C8" t="n">
-        <v>29.6242369756475</v>
+        <v>29.54078842078653</v>
       </c>
       <c r="D8" t="n">
-        <v>38.55323234577224</v>
+        <v>37.88564390688441</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.09531164276995</v>
+        <v>9.984374152190059</v>
       </c>
       <c r="C9" t="n">
         <v>29.7312474754104</v>
       </c>
       <c r="D9" t="n">
-        <v>41.26874649571891</v>
+        <v>41.15780900513902</v>
       </c>
     </row>
     <row r="10">
@@ -5263,7 +5263,7 @@
         <v>8.351727720027615</v>
       </c>
       <c r="C11" t="n">
-        <v>31.45225120095506</v>
+        <v>31.27455486648638</v>
       </c>
       <c r="D11" t="n">
         <v>49.75497365122833</v>
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6.508987279156352</v>
+        <v>6.725953521794898</v>
       </c>
       <c r="C12" t="n">
-        <v>32.11100391050467</v>
+        <v>31.67707142522758</v>
       </c>
       <c r="D12" t="n">
-        <v>45.77987719673301</v>
+        <v>46.2138096820101</v>
       </c>
     </row>
     <row r="13">
@@ -5291,7 +5291,7 @@
         <v>5.463425974133501</v>
       </c>
       <c r="C13" t="n">
-        <v>29.91876128692155</v>
+        <v>30.17892442854696</v>
       </c>
       <c r="D13" t="n">
         <v>45.00822350119503</v>
@@ -5308,7 +5308,7 @@
         <v>27.9631198600619</v>
       </c>
       <c r="D14" t="n">
-        <v>45.7857676829585</v>
+        <v>45.47848065152925</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.658392856651115</v>
+        <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
         <v>27.5920192278566</v>
       </c>
       <c r="D15" t="n">
-        <v>43.35888735806038</v>
+        <v>43.00054944601029</v>
       </c>
     </row>
     <row r="16">
@@ -5333,10 +5333,10 @@
         <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>29.75873641112932</v>
+        <v>29.34542062764141</v>
       </c>
       <c r="D16" t="n">
-        <v>40.91826256530281</v>
+        <v>41.33157834879071</v>
       </c>
     </row>
     <row r="17">
@@ -5350,7 +5350,7 @@
         <v>32.11100391050468</v>
       </c>
       <c r="D17" t="n">
-        <v>37.30543101367455</v>
+        <v>36.83321036793183</v>
       </c>
     </row>
     <row r="18">
@@ -5361,7 +5361,7 @@
         <v>5.350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>35.31346492175777</v>
+        <v>34.77841242294325</v>
       </c>
       <c r="D18" t="n">
         <v>31.56809743005619</v>
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.74164367801552</v>
+        <v>16.72765148336432</v>
       </c>
       <c r="C21" t="n">
-        <v>102.1240264358947</v>
+        <v>102.0386740485223</v>
       </c>
       <c r="D21" t="n">
-        <v>5.022493103404656</v>
+        <v>4.18191287084108</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.620906517440489</v>
+        <v>6.58360010467911</v>
       </c>
       <c r="C2" t="n">
-        <v>6.546293691917731</v>
+        <v>10.83751290718054</v>
       </c>
       <c r="D2" t="n">
-        <v>17.78435966243097</v>
+        <v>17.19727453529138</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.49612674800991</v>
+        <v>23.04652735719387</v>
       </c>
       <c r="C3" t="n">
-        <v>11.25573742918968</v>
+        <v>24.48969648243668</v>
       </c>
       <c r="D3" t="n">
-        <v>39.22572952318131</v>
+        <v>26.96370069713865</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>32.02166486941822</v>
+        <v>36.46309148343079</v>
       </c>
       <c r="C4" t="n">
-        <v>25.75516927321083</v>
+        <v>61.01856506205201</v>
       </c>
       <c r="D4" t="n">
-        <v>36.57795596482766</v>
+        <v>26.16357631817749</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>29.59969328304134</v>
+        <v>30.48326621686347</v>
       </c>
       <c r="C5" t="n">
-        <v>27.41530464109218</v>
+        <v>92.72607066611126</v>
       </c>
       <c r="D5" t="n">
-        <v>33.25670348136071</v>
+        <v>30.23782929080177</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>13.20254312671111</v>
+        <v>12.19625172985813</v>
       </c>
       <c r="C6" t="n">
-        <v>20.64909946342317</v>
+        <v>54.54099370943156</v>
       </c>
       <c r="D6" t="n">
-        <v>37.91705983342032</v>
+        <v>38.07806645691679</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.623671834103982</v>
+        <v>8.683558444063037</v>
       </c>
       <c r="C7" t="n">
-        <v>21.19985992550562</v>
+        <v>21.08008670558751</v>
       </c>
       <c r="D7" t="n">
-        <v>40.00425545264903</v>
+        <v>39.88448223273092</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.84831213192725</v>
+        <v>10.6814150222053</v>
       </c>
       <c r="C8" t="n">
-        <v>31.46010518258904</v>
+        <v>31.62700229231099</v>
       </c>
       <c r="D8" t="n">
-        <v>40.38910055271378</v>
+        <v>39.30426933952106</v>
       </c>
     </row>
     <row r="9">
@@ -5546,10 +5546,10 @@
         <v>10.76093658624928</v>
       </c>
       <c r="C9" t="n">
-        <v>34.27968458918587</v>
+        <v>34.05780960802609</v>
       </c>
       <c r="D9" t="n">
-        <v>41.93437143919824</v>
+        <v>42.15624642035802</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>10.10709261522091</v>
+        <v>9.82238578098934</v>
       </c>
       <c r="C10" t="n">
-        <v>33.59540643932586</v>
+        <v>33.16834618797849</v>
       </c>
       <c r="D10" t="n">
-        <v>49.25428232206248</v>
+        <v>48.68486865359933</v>
       </c>
     </row>
     <row r="11">
@@ -5574,10 +5574,10 @@
         <v>8.884816723433632</v>
       </c>
       <c r="C11" t="n">
-        <v>33.93999988351647</v>
+        <v>33.7623035490478</v>
       </c>
       <c r="D11" t="n">
-        <v>50.46575898910303</v>
+        <v>50.82115165804038</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>7.159886007071988</v>
+        <v>7.376852249710534</v>
       </c>
       <c r="C12" t="n">
         <v>34.28066633689012</v>
       </c>
       <c r="D12" t="n">
-        <v>47.29864089520282</v>
+        <v>47.08167465256428</v>
       </c>
     </row>
     <row r="13">
@@ -5602,7 +5602,7 @@
         <v>5.723589115758904</v>
       </c>
       <c r="C13" t="n">
-        <v>33.30088212805181</v>
+        <v>32.780555844801</v>
       </c>
       <c r="D13" t="n">
         <v>45.78871292607123</v>
@@ -5630,10 +5630,10 @@
         <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>29.02537087605695</v>
+        <v>29.38370878810703</v>
       </c>
       <c r="D15" t="n">
-        <v>44.07556318216055</v>
+        <v>43.00054944601029</v>
       </c>
     </row>
     <row r="16">
@@ -5644,10 +5644,10 @@
         <v>4.546473618366978</v>
       </c>
       <c r="C16" t="n">
-        <v>30.17205219461722</v>
+        <v>29.75873641112932</v>
       </c>
       <c r="D16" t="n">
-        <v>40.91826256530281</v>
+        <v>41.74489413227862</v>
       </c>
     </row>
     <row r="17">
@@ -5658,10 +5658,10 @@
         <v>4.722206457427158</v>
       </c>
       <c r="C17" t="n">
-        <v>32.58322455624739</v>
+        <v>32.11100391050468</v>
       </c>
       <c r="D17" t="n">
-        <v>37.77765165941727</v>
+        <v>36.83321036793183</v>
       </c>
     </row>
     <row r="18">
@@ -5672,7 +5672,7 @@
         <v>4.815472489330605</v>
       </c>
       <c r="C18" t="n">
-        <v>35.31346492175777</v>
+        <v>34.77841242294325</v>
       </c>
       <c r="D18" t="n">
         <v>32.1031499288707</v>
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.07754203991971</v>
+        <v>18.04570652137758</v>
       </c>
       <c r="C21" t="n">
-        <v>117.9344409270953</v>
+        <v>117.7267520680347</v>
       </c>
       <c r="D21" t="n">
-        <v>6.886682681874176</v>
+        <v>6.01523550712586</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.453027660014286</v>
+        <v>6.528622233241289</v>
       </c>
       <c r="C2" t="n">
-        <v>7.40532293313369</v>
+        <v>10.66178006812036</v>
       </c>
       <c r="D2" t="n">
-        <v>24.09896089614645</v>
+        <v>16.24007052365074</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.6973850273805</v>
+        <v>20.16018910670825</v>
       </c>
       <c r="C3" t="n">
-        <v>18.62866268808323</v>
+        <v>32.27004703859266</v>
       </c>
       <c r="D3" t="n">
-        <v>42.11697651218817</v>
+        <v>32.01970137400972</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>24.84901614219102</v>
+        <v>29.48188355853172</v>
       </c>
       <c r="C4" t="n">
-        <v>22.53896379409827</v>
+        <v>51.08916878129977</v>
       </c>
       <c r="D4" t="n">
-        <v>41.03214529899544</v>
+        <v>29.11176467403067</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>24.02827506144069</v>
+        <v>25.94268308472197</v>
       </c>
       <c r="C5" t="n">
-        <v>28.76520773443155</v>
+        <v>76.0118160013093</v>
       </c>
       <c r="D5" t="n">
-        <v>31.6122760767473</v>
+        <v>26.31083847381452</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>14.93336432929824</v>
+        <v>14.57109942643116</v>
       </c>
       <c r="C6" t="n">
-        <v>22.21891404251382</v>
+        <v>69.19259644761097</v>
       </c>
       <c r="D6" t="n">
-        <v>30.71201343195298</v>
+        <v>30.47050349670826</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>6.108434215823654</v>
+        <v>5.749114556069321</v>
       </c>
       <c r="C7" t="n">
-        <v>16.64847756861741</v>
+        <v>31.62013005838127</v>
       </c>
       <c r="D7" t="n">
-        <v>31.4404702285041</v>
+        <v>31.26081039862693</v>
       </c>
     </row>
     <row r="8">
@@ -5846,7 +5846,7 @@
         <v>18.60902773399829</v>
       </c>
       <c r="D8" t="n">
-        <v>30.12492830481337</v>
+        <v>29.37389131106456</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.881249585515139</v>
+        <v>4.77031209493525</v>
       </c>
       <c r="C9" t="n">
-        <v>21.96562313481813</v>
+        <v>21.74374815365835</v>
       </c>
       <c r="D9" t="n">
-        <v>30.28593492830985</v>
+        <v>30.17499743772996</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.412955930589413</v>
+        <v>4.270602513473626</v>
       </c>
       <c r="C10" t="n">
-        <v>21.6377194015997</v>
+        <v>21.35301256736813</v>
       </c>
       <c r="D10" t="n">
-        <v>33.45305302221006</v>
+        <v>33.16834618797849</v>
       </c>
     </row>
     <row r="11">
@@ -5885,7 +5885,7 @@
         <v>3.731623023842126</v>
       </c>
       <c r="C11" t="n">
-        <v>20.61277479836603</v>
+        <v>20.25738212942868</v>
       </c>
       <c r="D11" t="n">
         <v>34.65078522139116</v>
@@ -5902,7 +5902,7 @@
         <v>19.96089432274615</v>
       </c>
       <c r="D12" t="n">
-        <v>32.32797015314322</v>
+        <v>31.89403766786613</v>
       </c>
     </row>
     <row r="13">
@@ -5913,10 +5913,10 @@
         <v>2.341468274628643</v>
       </c>
       <c r="C13" t="n">
-        <v>19.25207248027995</v>
+        <v>18.99190933865455</v>
       </c>
       <c r="D13" t="n">
-        <v>30.17892442854696</v>
+        <v>30.43908757017236</v>
       </c>
     </row>
     <row r="14">
@@ -5927,10 +5927,10 @@
         <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>17.51536079146734</v>
+        <v>17.20807376003809</v>
       </c>
       <c r="D14" t="n">
-        <v>29.80684204863741</v>
+        <v>29.49955501720816</v>
       </c>
     </row>
     <row r="15">
@@ -5944,7 +5944,7 @@
         <v>16.12520604225386</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>27.95035713990669</v>
       </c>
     </row>
     <row r="16">
@@ -5983,7 +5983,7 @@
         <v>1.070104997629023</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>17.12167996206437</v>
       </c>
       <c r="D18" t="n">
         <v>20.33199495495144</v>
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.071076494962521</v>
+        <v>7.049020076605427</v>
       </c>
       <c r="C21" t="n">
-        <v>67.17522670214395</v>
+        <v>66.08456321817587</v>
       </c>
       <c r="D21" t="n">
-        <v>5.303307371221891</v>
+        <v>4.405637547878392</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.683337459884785</v>
+        <v>5.6479945425319</v>
       </c>
       <c r="C2" t="n">
-        <v>5.529203070318036</v>
+        <v>11.81238837749762</v>
       </c>
       <c r="D2" t="n">
-        <v>23.67680938332033</v>
+        <v>13.96830633602362</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21.51990967709008</v>
+        <v>21.81934272688536</v>
       </c>
       <c r="C3" t="n">
-        <v>25.51071409485337</v>
+        <v>38.32743037379548</v>
       </c>
       <c r="D3" t="n">
-        <v>52.73948667213865</v>
+        <v>37.92491381505428</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>32.31520743298801</v>
+        <v>35.77390459504952</v>
       </c>
       <c r="C4" t="n">
-        <v>38.22434686484957</v>
+        <v>69.86313012961152</v>
       </c>
       <c r="D4" t="n">
-        <v>54.24156065963627</v>
+        <v>38.84972015245478</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>32.44676162535709</v>
+        <v>36.37375244234433</v>
       </c>
       <c r="C5" t="n">
-        <v>36.96280106489242</v>
+        <v>87.44917675578465</v>
       </c>
       <c r="D5" t="n">
-        <v>39.85895679242051</v>
+        <v>31.48955761371645</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>25.60005313593983</v>
+        <v>26.3648345975481</v>
       </c>
       <c r="C6" t="n">
-        <v>36.30699359845555</v>
+        <v>99.74360325606746</v>
       </c>
       <c r="D6" t="n">
-        <v>34.49566908412018</v>
+        <v>32.4428346345401</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>12.93550775115597</v>
+        <v>12.27675504160636</v>
       </c>
       <c r="C7" t="n">
-        <v>26.29022177202533</v>
+        <v>71.44472568115313</v>
       </c>
       <c r="D7" t="n">
-        <v>33.89582123682538</v>
+        <v>33.23706852727577</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>6.175193059712437</v>
+        <v>5.841398840268521</v>
       </c>
       <c r="C8" t="n">
-        <v>21.19593293468863</v>
+        <v>32.29459073119883</v>
       </c>
       <c r="D8" t="n">
-        <v>32.04424506661589</v>
+        <v>31.71045084717197</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.214062057254808</v>
+        <v>5.103124566674919</v>
       </c>
       <c r="C9" t="n">
-        <v>23.40781051235669</v>
+        <v>23.18593553119691</v>
       </c>
       <c r="D9" t="n">
-        <v>31.72812230584841</v>
+        <v>31.39530983410874</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.840016181936776</v>
+        <v>4.697662764820988</v>
       </c>
       <c r="C10" t="n">
-        <v>25.0542014123786</v>
+        <v>24.34243432679967</v>
       </c>
       <c r="D10" t="n">
-        <v>34.02246669067321</v>
+        <v>33.31069960509428</v>
       </c>
     </row>
     <row r="11">
@@ -6196,10 +6196,10 @@
         <v>4.08701569277947</v>
       </c>
       <c r="C11" t="n">
-        <v>23.81130881880213</v>
+        <v>23.27821981539612</v>
       </c>
       <c r="D11" t="n">
-        <v>35.00617789032851</v>
+        <v>35.36157055926586</v>
       </c>
     </row>
     <row r="12">
@@ -6210,10 +6210,10 @@
         <v>3.254493639578176</v>
       </c>
       <c r="C12" t="n">
-        <v>22.34752299177014</v>
+        <v>22.1305567491316</v>
       </c>
       <c r="D12" t="n">
-        <v>33.62976760897449</v>
+        <v>33.1958351236974</v>
       </c>
     </row>
     <row r="13">
@@ -6224,7 +6224,7 @@
         <v>2.601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>21.33337761328319</v>
+        <v>21.07321447165778</v>
       </c>
       <c r="D13" t="n">
         <v>30.95941385342317</v>
@@ -6238,10 +6238,10 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>19.66637001147211</v>
+        <v>19.35908298004286</v>
       </c>
       <c r="D14" t="n">
-        <v>29.80684204863741</v>
+        <v>30.11412908006666</v>
       </c>
     </row>
     <row r="15">
@@ -6252,10 +6252,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>17.91689560250429</v>
+        <v>17.5585576904542</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>28.30869505195678</v>
       </c>
     </row>
     <row r="16">
@@ -6269,7 +6269,7 @@
         <v>16.53263133951629</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>26.45221014322606</v>
       </c>
     </row>
     <row r="17">
@@ -6283,7 +6283,7 @@
         <v>16.99994324673777</v>
       </c>
       <c r="D17" t="n">
-        <v>23.61103228713579</v>
+        <v>24.0832529328785</v>
       </c>
     </row>
     <row r="18">
@@ -6294,7 +6294,7 @@
         <v>1.070104997629023</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>17.12167996206437</v>
       </c>
       <c r="D18" t="n">
         <v>20.86704745376595</v>
@@ -6311,7 +6311,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>15.64709491028566</v>
       </c>
     </row>
     <row r="20">
@@ -6325,7 +6325,7 @@
         <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
-        <v>10.08745766113597</v>
+        <v>10.75995483854504</v>
       </c>
     </row>
     <row r="21">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.301712651111476</v>
+        <v>7.268019813039549</v>
       </c>
       <c r="C21" t="n">
-        <v>77.58069691805943</v>
+        <v>75.40570556028534</v>
       </c>
       <c r="D21" t="n">
-        <v>6.388998569722541</v>
+        <v>5.451014859779662</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.977460860531329</v>
+        <v>4.716315971201677</v>
       </c>
       <c r="C2" t="n">
-        <v>4.137084825696059</v>
+        <v>10.73050240741764</v>
       </c>
       <c r="D2" t="n">
-        <v>23.07107104980004</v>
+        <v>20.60492081673206</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.57743188101315</v>
+        <v>20.50870954171587</v>
       </c>
       <c r="C3" t="n">
-        <v>23.04161861867264</v>
+        <v>42.85819602889451</v>
       </c>
       <c r="D3" t="n">
-        <v>59.8817012205342</v>
+        <v>40.30074325933157</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>38.07119422298706</v>
+        <v>39.34746623850791</v>
       </c>
       <c r="C4" t="n">
-        <v>53.51408561078939</v>
+        <v>84.98695351353363</v>
       </c>
       <c r="D4" t="n">
-        <v>69.28880772262713</v>
+        <v>49.13647259755286</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>42.04334543436966</v>
+        <v>46.01942363656924</v>
       </c>
       <c r="C5" t="n">
-        <v>57.23589115758906</v>
+        <v>110.8393158094649</v>
       </c>
       <c r="D5" t="n">
-        <v>50.63363784652926</v>
+        <v>38.41087892865646</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>36.34724525432967</v>
+        <v>38.44033135978387</v>
       </c>
       <c r="C6" t="n">
-        <v>49.3887817575443</v>
+        <v>120.2719477518683</v>
       </c>
       <c r="D6" t="n">
-        <v>39.92964262712628</v>
+        <v>34.97868895460962</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>22.75691178444107</v>
+        <v>22.51736534460484</v>
       </c>
       <c r="C7" t="n">
-        <v>41.44153409166636</v>
+        <v>111.329207913884</v>
       </c>
       <c r="D7" t="n">
-        <v>36.77037851486003</v>
+        <v>35.51275970571987</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.6814150222053</v>
+        <v>9.763480918734528</v>
       </c>
       <c r="C8" t="n">
-        <v>29.29044275620359</v>
+        <v>65.84090978531233</v>
       </c>
       <c r="D8" t="n">
-        <v>34.04701038327938</v>
+        <v>33.46287049925253</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.990624491314035</v>
+        <v>5.768749510154256</v>
       </c>
       <c r="C9" t="n">
-        <v>25.73749781453438</v>
+        <v>32.61562223048752</v>
       </c>
       <c r="D9" t="n">
-        <v>33.28124717396686</v>
+        <v>32.8374972116473</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.267076433284139</v>
+        <v>4.982369599052563</v>
       </c>
       <c r="C10" t="n">
-        <v>27.18950266911542</v>
+        <v>26.47773558353648</v>
       </c>
       <c r="D10" t="n">
-        <v>34.73423377625215</v>
+        <v>34.02246669067321</v>
       </c>
     </row>
     <row r="11">
@@ -6507,10 +6507,10 @@
         <v>4.442408361716816</v>
       </c>
       <c r="C11" t="n">
-        <v>27.36523550817559</v>
+        <v>26.29905750136355</v>
       </c>
       <c r="D11" t="n">
-        <v>35.36157055926586</v>
+        <v>35.53926689373453</v>
       </c>
     </row>
     <row r="12">
@@ -6521,10 +6521,10 @@
         <v>3.471459882216721</v>
       </c>
       <c r="C12" t="n">
-        <v>25.38505038870978</v>
+        <v>24.73415166079414</v>
       </c>
       <c r="D12" t="n">
-        <v>34.71459882216721</v>
+        <v>34.28066633689012</v>
       </c>
     </row>
     <row r="13">
@@ -6535,10 +6535,10 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>23.67484588791184</v>
+        <v>22.89435646303562</v>
       </c>
       <c r="D13" t="n">
-        <v>32.00006641992479</v>
+        <v>31.47974013667398</v>
       </c>
     </row>
     <row r="14">
@@ -6549,10 +6549,10 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>21.81737923147687</v>
+        <v>21.51009220004762</v>
       </c>
       <c r="D14" t="n">
-        <v>30.11412908006666</v>
+        <v>30.42141611149592</v>
       </c>
     </row>
     <row r="15">
@@ -6563,10 +6563,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>19.70858516275472</v>
+        <v>19.35024725070463</v>
       </c>
       <c r="D15" t="n">
-        <v>29.02537087605695</v>
+        <v>28.66703296400686</v>
       </c>
     </row>
     <row r="16">
@@ -6580,7 +6580,7 @@
         <v>17.77257868998001</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>26.45221014322606</v>
       </c>
     </row>
     <row r="17">
@@ -6594,7 +6594,7 @@
         <v>17.47216389248049</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>24.55547357862122</v>
       </c>
     </row>
     <row r="18">
@@ -6605,7 +6605,7 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
         <v>20.86704745376595</v>
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.522082220326986</v>
+        <v>7.472814648280793</v>
       </c>
       <c r="C21" t="n">
-        <v>87.4442058113012</v>
+        <v>84.06916479315893</v>
       </c>
       <c r="D21" t="n">
-        <v>7.522082220326986</v>
+        <v>6.538712817245695</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_surface_area_iteration_24_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_24_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497616835291</v>
+        <v>10.84497645389941</v>
       </c>
       <c r="C21" t="n">
-        <v>37.78907137093557</v>
+        <v>37.78907236591584</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.796238445873168</v>
+        <v>0.8119053514121122</v>
       </c>
       <c r="C2" t="n">
-        <v>9.348201639838129</v>
+        <v>3.590251354430586</v>
       </c>
       <c r="D2" t="n">
-        <v>18.77003435749477</v>
+        <v>10.34467555964864</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.08379271222625</v>
+        <v>6.567892141411162</v>
       </c>
       <c r="C3" t="n">
-        <v>42.08261534253953</v>
+        <v>50.24584750335175</v>
       </c>
       <c r="D3" t="n">
-        <v>46.55938487390498</v>
+        <v>63.76942212935157</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>39.09221183540375</v>
+        <v>11.09080381487622</v>
       </c>
       <c r="C4" t="n">
-        <v>96.66484245554945</v>
+        <v>144.3591276755637</v>
       </c>
       <c r="D4" t="n">
-        <v>57.25356261626548</v>
+        <v>82.26849412047422</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>52.79348279587224</v>
+        <v>10.4801567428347</v>
       </c>
       <c r="C5" t="n">
-        <v>133.198619773686</v>
+        <v>124.6819584393449</v>
       </c>
       <c r="D5" t="n">
-        <v>46.01942363656924</v>
+        <v>50.82998738737862</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>49.87180162803373</v>
+        <v>8.010079518949729</v>
       </c>
       <c r="C6" t="n">
-        <v>148.5286101755</v>
+        <v>77.88695411642071</v>
       </c>
       <c r="D6" t="n">
-        <v>39.04410619789565</v>
+        <v>30.30949687321178</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>34.01559445674349</v>
+        <v>5.629341336151211</v>
       </c>
       <c r="C7" t="n">
-        <v>143.0691111921834</v>
+        <v>45.21439051908685</v>
       </c>
       <c r="D7" t="n">
-        <v>37.36924461445059</v>
+        <v>29.10489244010094</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>16.68971097219578</v>
+        <v>6.091744504851458</v>
       </c>
       <c r="C8" t="n">
-        <v>105.3955247894163</v>
+        <v>29.95803119509142</v>
       </c>
       <c r="D8" t="n">
-        <v>35.63253292563798</v>
+        <v>31.12631096314512</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>7.765624340592267</v>
+        <v>5.879687000734146</v>
       </c>
       <c r="C9" t="n">
-        <v>56.79999517690344</v>
+        <v>31.28437234352885</v>
       </c>
       <c r="D9" t="n">
-        <v>33.83593462686631</v>
+        <v>34.94530953266521</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.409429850399925</v>
+        <v>3.4164820107789</v>
       </c>
       <c r="C10" t="n">
-        <v>32.59893251951534</v>
+        <v>30.32127784566274</v>
       </c>
       <c r="D10" t="n">
-        <v>34.73423377625215</v>
+        <v>38.29306920414684</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.620104696185489</v>
+        <v>2.665445017030089</v>
       </c>
       <c r="C11" t="n">
-        <v>28.96450251839364</v>
+        <v>31.45225120095506</v>
       </c>
       <c r="D11" t="n">
-        <v>35.7169632282032</v>
+        <v>37.6716229073586</v>
       </c>
     </row>
     <row r="12">
@@ -920,13 +920,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.688426124855267</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C12" t="n">
-        <v>27.33774657245668</v>
+        <v>23.86628669023996</v>
       </c>
       <c r="D12" t="n">
-        <v>35.1485313074443</v>
+        <v>37.96909246174538</v>
       </c>
     </row>
     <row r="13">
@@ -934,13 +934,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>1.821141991377834</v>
       </c>
       <c r="C13" t="n">
-        <v>25.23582473766426</v>
+        <v>20.03256190515617</v>
       </c>
       <c r="D13" t="n">
-        <v>32.26022956155019</v>
+        <v>35.90251354430586</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>23.35381438862312</v>
+        <v>19.97365704290136</v>
       </c>
       <c r="D14" t="n">
-        <v>30.42141611149592</v>
+        <v>27.3485457972034</v>
       </c>
     </row>
     <row r="15">
@@ -968,7 +968,7 @@
         <v>20.78359889890498</v>
       </c>
       <c r="D15" t="n">
-        <v>29.02537087605695</v>
+        <v>25.80032966760617</v>
       </c>
     </row>
     <row r="16">
@@ -976,13 +976,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>1.653263133951629</v>
       </c>
       <c r="C16" t="n">
-        <v>19.01252604044373</v>
+        <v>22.7323680918349</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>21.90573652485908</v>
       </c>
     </row>
     <row r="17">
@@ -990,13 +990,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
-        <v>17.9443845382232</v>
+        <v>24.55547357862122</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>18.41660518396592</v>
       </c>
     </row>
     <row r="18">
@@ -1004,13 +1004,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>1.605157496443535</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>26.75262494072559</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>11.23610247510475</v>
       </c>
     </row>
     <row r="19">
@@ -1018,13 +1018,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>10.83260416865931</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>85.45721066386785</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>3.009056713516474</v>
       </c>
     </row>
     <row r="20">
@@ -1035,10 +1035,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.661111408484733</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>92.89097582787738</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>7.661111408484733</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8.695339416513999</v>
+        <v>0.9287333282174827</v>
       </c>
       <c r="C2" t="n">
-        <v>9.58774807967435</v>
+        <v>12.22668590868978</v>
       </c>
       <c r="D2" t="n">
-        <v>17.24636192050372</v>
+        <v>12.57226110058465</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.51576170209485</v>
+        <v>4.599487994396307</v>
       </c>
       <c r="C3" t="n">
-        <v>38.95574890451343</v>
+        <v>29.4082524807132</v>
       </c>
       <c r="D3" t="n">
-        <v>49.55371537185776</v>
+        <v>57.44696691400211</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>36.3354642818787</v>
+        <v>11.93314334511998</v>
       </c>
       <c r="C4" t="n">
-        <v>100.5191839424224</v>
+        <v>135.3614099661417</v>
       </c>
       <c r="D4" t="n">
-        <v>64.75804206752811</v>
+        <v>94.99292611521713</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>55.68963852340033</v>
+        <v>13.71992416684918</v>
       </c>
       <c r="C5" t="n">
-        <v>152.4163310843173</v>
+        <v>199.8838325846506</v>
       </c>
       <c r="D5" t="n">
-        <v>54.46245389309182</v>
+        <v>67.83876636345461</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>59.08943082320704</v>
+        <v>10.90819874188631</v>
       </c>
       <c r="C6" t="n">
-        <v>175.8594845140269</v>
+        <v>139.7940008508161</v>
       </c>
       <c r="D6" t="n">
-        <v>43.39128503230054</v>
+        <v>38.52083467153211</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>45.09461729916874</v>
+        <v>7.485826244881928</v>
       </c>
       <c r="C7" t="n">
-        <v>176.6056127692545</v>
+        <v>78.87066531607601</v>
       </c>
       <c r="D7" t="n">
-        <v>40.00425545264903</v>
+        <v>31.56024344842221</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>25.45180923259856</v>
+        <v>6.425538724295373</v>
       </c>
       <c r="C8" t="n">
-        <v>142.9473744768568</v>
+        <v>44.81187396034566</v>
       </c>
       <c r="D8" t="n">
-        <v>37.1346069131356</v>
+        <v>32.04424506661589</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>11.75937400146829</v>
+        <v>6.212499472473814</v>
       </c>
       <c r="C9" t="n">
-        <v>90.19217984145018</v>
+        <v>35.38905949498476</v>
       </c>
       <c r="D9" t="n">
-        <v>35.27812200440487</v>
+        <v>35.38905949498476</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6.26355035309465</v>
+        <v>4.128249096357838</v>
       </c>
       <c r="C10" t="n">
-        <v>47.54604131667303</v>
+        <v>34.44952694202058</v>
       </c>
       <c r="D10" t="n">
-        <v>35.01894061048373</v>
+        <v>39.00483628972578</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.797801030654161</v>
+        <v>2.843141351498762</v>
       </c>
       <c r="C11" t="n">
-        <v>33.22921454564179</v>
+        <v>34.11769621798515</v>
       </c>
       <c r="D11" t="n">
-        <v>36.25005223160922</v>
+        <v>38.56010457970196</v>
       </c>
     </row>
     <row r="12">
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.905392367493811</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C12" t="n">
-        <v>29.72437524148068</v>
+        <v>28.8565102709265</v>
       </c>
       <c r="D12" t="n">
-        <v>35.36549755008285</v>
+        <v>38.40302494702248</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>1.560978849752429</v>
       </c>
       <c r="C13" t="n">
-        <v>27.3171298706675</v>
+        <v>22.37403017978481</v>
       </c>
       <c r="D13" t="n">
-        <v>33.04071898642641</v>
+        <v>36.68300296918207</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>1.229148125717007</v>
       </c>
       <c r="C14" t="n">
-        <v>25.19753657719863</v>
+        <v>21.51009220004762</v>
       </c>
       <c r="D14" t="n">
-        <v>30.42141611149592</v>
+        <v>28.88498095434966</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>22.57528845915541</v>
+        <v>22.93362637120549</v>
       </c>
       <c r="D15" t="n">
-        <v>29.38370878810703</v>
+        <v>25.44199175555609</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>20.25247339090745</v>
+        <v>25.21226279276234</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>21.49242074137117</v>
       </c>
     </row>
     <row r="17">
@@ -1301,13 +1301,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
-        <v>18.41660518396592</v>
+        <v>26.9165768073348</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>17.47216389248049</v>
       </c>
     </row>
     <row r="18">
@@ -1315,13 +1315,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>8.560839981032187</v>
       </c>
       <c r="C18" t="n">
-        <v>18.72683745850791</v>
+        <v>51.36503988619312</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>9.095892479846698</v>
       </c>
     </row>
     <row r="19">
@@ -1332,10 +1332,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>46.33947338815369</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>1.805434028109884</v>
       </c>
     </row>
     <row r="20">
@@ -1346,10 +1346,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.832657011222283</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>100.8454590194869</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>8.811739137625068</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8.613854357061514</v>
+        <v>0.5006913291658733</v>
       </c>
       <c r="C2" t="n">
-        <v>16.95576460004666</v>
+        <v>5.231733515931253</v>
       </c>
       <c r="D2" t="n">
-        <v>26.21757244191107</v>
+        <v>8.608945618540281</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>22.61455836732528</v>
+        <v>4.437499623195583</v>
       </c>
       <c r="C3" t="n">
-        <v>37.80710409054467</v>
+        <v>40.20747722742812</v>
       </c>
       <c r="D3" t="n">
-        <v>50.78090000216627</v>
+        <v>56.62229884243479</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>34.88051418418493</v>
+        <v>13.12007631955437</v>
       </c>
       <c r="C4" t="n">
-        <v>97.77519910905259</v>
+        <v>123.4793175016426</v>
       </c>
       <c r="D4" t="n">
-        <v>72.00726711568656</v>
+        <v>102.3953038052381</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>54.78152189697203</v>
+        <v>13.76901155206152</v>
       </c>
       <c r="C5" t="n">
-        <v>164.2463909204914</v>
+        <v>240.9945176999858</v>
       </c>
       <c r="D5" t="n">
-        <v>61.67829951930587</v>
+        <v>76.18362184955249</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>65.24793417194728</v>
+        <v>9.378635818669782</v>
       </c>
       <c r="C6" t="n">
-        <v>203.5123720995468</v>
+        <v>181.615471304026</v>
       </c>
       <c r="D6" t="n">
-        <v>48.98626519880311</v>
+        <v>38.7220929509027</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>55.51488743204438</v>
+        <v>4.251949307092936</v>
       </c>
       <c r="C7" t="n">
-        <v>207.2675570682908</v>
+        <v>76.11588125795946</v>
       </c>
       <c r="D7" t="n">
-        <v>42.27994663109313</v>
+        <v>33.23706852727577</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>34.38080460272329</v>
+        <v>4.255876297909922</v>
       </c>
       <c r="C8" t="n">
-        <v>179.8316357254095</v>
+        <v>41.39048321104552</v>
       </c>
       <c r="D8" t="n">
-        <v>39.05392367493811</v>
+        <v>36.13322425480386</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>17.08437354930299</v>
+        <v>2.884374755077128</v>
       </c>
       <c r="C9" t="n">
-        <v>125.4703018458551</v>
+        <v>26.29218526743382</v>
       </c>
       <c r="D9" t="n">
-        <v>36.16562192904399</v>
+        <v>40.49218406165969</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.114144775599888</v>
+        <v>1.992947839621025</v>
       </c>
       <c r="C10" t="n">
-        <v>71.46141539212533</v>
+        <v>26.76244241776806</v>
       </c>
       <c r="D10" t="n">
-        <v>35.44600086183109</v>
+        <v>30.17892442854695</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>5.153193699591506</v>
+        <v>1.599267010218054</v>
       </c>
       <c r="C11" t="n">
-        <v>41.5809422656694</v>
+        <v>23.10052348092744</v>
       </c>
       <c r="D11" t="n">
-        <v>36.60544490054656</v>
+        <v>30.74146586308036</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4.122358610132356</v>
+        <v>1.084831213192725</v>
       </c>
       <c r="C12" t="n">
-        <v>32.76190263842031</v>
+        <v>18.22516438163779</v>
       </c>
       <c r="D12" t="n">
-        <v>35.58246379272139</v>
+        <v>29.94134148411922</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>0.7804894248762143</v>
       </c>
       <c r="C13" t="n">
-        <v>29.65859814529614</v>
+        <v>17.69109363052753</v>
       </c>
       <c r="D13" t="n">
-        <v>33.56104526967722</v>
+        <v>23.93500902953724</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>26.73397173434489</v>
+        <v>19.0517959486136</v>
       </c>
       <c r="D14" t="n">
-        <v>30.42141611149592</v>
+        <v>21.20280516861837</v>
       </c>
     </row>
     <row r="15">
@@ -1584,13 +1584,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>24.00864010735575</v>
+        <v>21.14193681095506</v>
       </c>
       <c r="D15" t="n">
-        <v>29.38370878810703</v>
+        <v>17.91689560250429</v>
       </c>
     </row>
     <row r="16">
@@ -1598,13 +1598,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>0.8266315669758143</v>
       </c>
       <c r="C16" t="n">
-        <v>21.49242074137117</v>
+        <v>22.7323680918349</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>14.87936820556466</v>
       </c>
     </row>
     <row r="17">
@@ -1612,13 +1612,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>6.611089040398022</v>
       </c>
       <c r="C17" t="n">
-        <v>19.36104647545135</v>
+        <v>44.38874069981529</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>7.555530331883453</v>
       </c>
     </row>
     <row r="18">
@@ -1626,13 +1626,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>18.72683745850791</v>
+        <v>40.12893741108837</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>1.070104997629023</v>
       </c>
     </row>
     <row r="19">
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1657,10 +1657,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.987453498880665</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>107.830622234889</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>9.984316873600832</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.978663592413827</v>
+        <v>0.4447317100238051</v>
       </c>
       <c r="C2" t="n">
-        <v>11.93608858823272</v>
+        <v>7.721445693901163</v>
       </c>
       <c r="D2" t="n">
-        <v>21.46100481483527</v>
+        <v>11.90074567087984</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>25.2996383384403</v>
+        <v>3.072870314292516</v>
       </c>
       <c r="C3" t="n">
-        <v>60.67691686097411</v>
+        <v>29.43770491184061</v>
       </c>
       <c r="D3" t="n">
-        <v>54.81588306662066</v>
+        <v>50.7710825251238</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>26.31672896004</v>
+        <v>10.93765117301371</v>
       </c>
       <c r="C4" t="n">
-        <v>133.6129173048782</v>
+        <v>112.4523272875424</v>
       </c>
       <c r="D4" t="n">
-        <v>69.17394324123026</v>
+        <v>107.0154085014236</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>36.74190783143688</v>
+        <v>16.76334205001429</v>
       </c>
       <c r="C5" t="n">
-        <v>121.5894531709675</v>
+        <v>236.5766530308752</v>
       </c>
       <c r="D5" t="n">
-        <v>45.84761778832605</v>
+        <v>94.29686699290615</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>34.45541742824607</v>
+        <v>13.24279478258523</v>
       </c>
       <c r="C6" t="n">
-        <v>136.4933650691383</v>
+        <v>277.9779354666674</v>
       </c>
       <c r="D6" t="n">
-        <v>27.81389420901639</v>
+        <v>50.59633143376788</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>22.75691178444107</v>
+        <v>6.707300315414209</v>
       </c>
       <c r="C7" t="n">
-        <v>126.420633623566</v>
+        <v>161.2147540097772</v>
       </c>
       <c r="D7" t="n">
-        <v>27.42806736124739</v>
+        <v>36.53083207502382</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>11.849694790259</v>
+        <v>4.506221962492859</v>
       </c>
       <c r="C8" t="n">
-        <v>92.46099878596459</v>
+        <v>67.92712365683681</v>
       </c>
       <c r="D8" t="n">
-        <v>26.62008900065226</v>
+        <v>37.30150402285756</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.768749510154256</v>
+        <v>3.217187226816797</v>
       </c>
       <c r="C9" t="n">
-        <v>54.47030787472577</v>
+        <v>36.83124687252333</v>
       </c>
       <c r="D9" t="n">
-        <v>27.06874770149305</v>
+        <v>41.15780900513902</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3.701188845010476</v>
+        <v>2.135301256736813</v>
       </c>
       <c r="C10" t="n">
-        <v>32.59893251951534</v>
+        <v>29.75186417719959</v>
       </c>
       <c r="D10" t="n">
-        <v>28.61303684027329</v>
+        <v>32.02951885105219</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.020837685967435</v>
+        <v>1.421570675749381</v>
       </c>
       <c r="C11" t="n">
-        <v>26.12136116689488</v>
+        <v>26.47675383583222</v>
       </c>
       <c r="D11" t="n">
-        <v>28.43141351498762</v>
+        <v>31.8076438698924</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.169662426385451</v>
+        <v>0.8678649705541803</v>
       </c>
       <c r="C12" t="n">
-        <v>24.0832529328785</v>
+        <v>20.82875929330033</v>
       </c>
       <c r="D12" t="n">
-        <v>27.33774657245668</v>
+        <v>30.59224021203486</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1.300815708127024</v>
+        <v>0.7804894248762143</v>
       </c>
       <c r="C13" t="n">
-        <v>22.11386703815941</v>
+        <v>20.81305133003238</v>
       </c>
       <c r="D13" t="n">
-        <v>25.23582473766426</v>
+        <v>23.93500902953724</v>
       </c>
     </row>
     <row r="14">
@@ -1881,13 +1881,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.921861094287755</v>
+        <v>0.6145740628585034</v>
       </c>
       <c r="C14" t="n">
-        <v>19.97365704290136</v>
+        <v>21.20280516861837</v>
       </c>
       <c r="D14" t="n">
-        <v>24.58296251434014</v>
+        <v>20.89551813718911</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>17.91689560250429</v>
+        <v>23.65030219530566</v>
       </c>
       <c r="D15" t="n">
-        <v>22.21695054710532</v>
+        <v>17.5585576904542</v>
       </c>
     </row>
     <row r="16">
@@ -1909,13 +1909,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0.4133157834879072</v>
+        <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>16.53263133951629</v>
+        <v>37.61173629739955</v>
       </c>
       <c r="D16" t="n">
-        <v>20.66578917439536</v>
+        <v>12.81278928812512</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>16.05550195525234</v>
+        <v>47.6942852200143</v>
       </c>
       <c r="D17" t="n">
-        <v>17.9443845382232</v>
+        <v>4.722206457427158</v>
       </c>
     </row>
     <row r="18">
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>16.05157496443535</v>
+        <v>1.070104997629023</v>
       </c>
       <c r="D18" t="n">
-        <v>13.9113649691773</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1954,10 +1954,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>16.85071759569225</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>9.027170140549421</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1965,13 +1965,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>5.37997741927252</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>72.62969516017901</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>6.724971774090649</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.944081438586937</v>
+        <v>0.2474004214701962</v>
       </c>
       <c r="C2" t="n">
-        <v>5.282784396552087</v>
+        <v>4.280419990516093</v>
       </c>
       <c r="D2" t="n">
-        <v>15.62549646079223</v>
+        <v>8.618763095582748</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>26.8851608807989</v>
+        <v>2.429825568010856</v>
       </c>
       <c r="C3" t="n">
-        <v>54.74225198880215</v>
+        <v>30.08565839664351</v>
       </c>
       <c r="D3" t="n">
-        <v>59.32210502911352</v>
+        <v>49.04320656564941</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>35.53141291210056</v>
+        <v>9.227446672215772</v>
       </c>
       <c r="C4" t="n">
-        <v>146.8478581058294</v>
+        <v>97.48165654548279</v>
       </c>
       <c r="D4" t="n">
-        <v>78.95018688012</v>
+        <v>108.3810195580309</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>40.20256848890689</v>
+        <v>17.62237129123025</v>
       </c>
       <c r="C5" t="n">
-        <v>178.1626646281899</v>
+        <v>232.7232932917065</v>
       </c>
       <c r="D5" t="n">
-        <v>55.37057051952011</v>
+        <v>107.1332182259332</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>40.21140421824511</v>
+        <v>15.8994040702771</v>
       </c>
       <c r="C6" t="n">
-        <v>164.06574934291</v>
+        <v>326.4811807949811</v>
       </c>
       <c r="D6" t="n">
-        <v>32.36233132279187</v>
+        <v>61.42402686390595</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>21.19985992550562</v>
+        <v>7.066619975168541</v>
       </c>
       <c r="C7" t="n">
-        <v>157.0226913126434</v>
+        <v>241.4029247449525</v>
       </c>
       <c r="D7" t="n">
-        <v>29.64387192973244</v>
+        <v>40.00425545264903</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.680032363873551</v>
+        <v>4.172427743048944</v>
       </c>
       <c r="C8" t="n">
-        <v>118.2466022380071</v>
+        <v>104.2272450213626</v>
       </c>
       <c r="D8" t="n">
-        <v>27.37112599440107</v>
+        <v>39.47116644924301</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.548437113775471</v>
+        <v>2.662499773917349</v>
       </c>
       <c r="C9" t="n">
-        <v>58.13124506386212</v>
+        <v>46.03905859065416</v>
       </c>
       <c r="D9" t="n">
-        <v>28.28906009787183</v>
+        <v>40.82499653339935</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.135301256736813</v>
+        <v>1.423534171157875</v>
       </c>
       <c r="C10" t="n">
-        <v>34.16482010778901</v>
+        <v>32.17187226816798</v>
       </c>
       <c r="D10" t="n">
-        <v>29.60951076008381</v>
+        <v>33.16834618797849</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.599267010218054</v>
+        <v>0.5330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>28.78680618392497</v>
+        <v>26.65445017030089</v>
       </c>
       <c r="D11" t="n">
-        <v>29.67528785626833</v>
+        <v>32.87382187670443</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>0.8678649705541803</v>
+        <v>0.4339324852770902</v>
       </c>
       <c r="C12" t="n">
-        <v>20.17786056538469</v>
+        <v>22.56448923440869</v>
       </c>
       <c r="D12" t="n">
-        <v>28.20561154301086</v>
+        <v>29.29044275620359</v>
       </c>
     </row>
     <row r="13">
@@ -2178,13 +2178,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0.5203262832508095</v>
+        <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>16.3902779224005</v>
+        <v>17.43093048890212</v>
       </c>
       <c r="D13" t="n">
-        <v>25.75615102091507</v>
+        <v>23.93500902953724</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>15.05706454003333</v>
+        <v>19.66637001147211</v>
       </c>
       <c r="D14" t="n">
-        <v>18.4372218857551</v>
+        <v>16.59349969717959</v>
       </c>
     </row>
     <row r="15">
@@ -2206,13 +2206,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>3.941717032550943</v>
       </c>
       <c r="C15" t="n">
-        <v>13.97517856995334</v>
+        <v>31.89207417245764</v>
       </c>
       <c r="D15" t="n">
-        <v>17.5585576904542</v>
+        <v>10.75013736150257</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>13.63942085510094</v>
+        <v>40.5049467818149</v>
       </c>
       <c r="D16" t="n">
-        <v>15.29268398905256</v>
+        <v>3.719842051391165</v>
       </c>
     </row>
     <row r="17">
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>13.69439872653876</v>
+        <v>0.4722206457427158</v>
       </c>
       <c r="D17" t="n">
-        <v>11.8055161435679</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>14.44641746799181</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>7.490734983403163</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2262,13 +2262,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>4.212679398923063</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>63.19019098384595</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>5.416302084329653</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.711407232680442</v>
+        <v>0.1806415775814131</v>
       </c>
       <c r="C2" t="n">
-        <v>8.94470333339269</v>
+        <v>8.502916866481625</v>
       </c>
       <c r="D2" t="n">
-        <v>12.97477765932585</v>
+        <v>10.57145927932965</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21.84879515801277</v>
+        <v>1.668971097219578</v>
       </c>
       <c r="C3" t="n">
-        <v>37.36531762363361</v>
+        <v>23.52267499375358</v>
       </c>
       <c r="D3" t="n">
-        <v>57.88875338091317</v>
+        <v>45.06221962492859</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>42.88273972150068</v>
+        <v>7.070546965985528</v>
       </c>
       <c r="C4" t="n">
-        <v>141.6661937228147</v>
+        <v>86.76097161510762</v>
       </c>
       <c r="D4" t="n">
-        <v>88.82853228025141</v>
+        <v>108.023663393685</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>46.04396732917541</v>
+        <v>16.3460992757094</v>
       </c>
       <c r="C5" t="n">
-        <v>221.4822820780805</v>
+        <v>208.3268628411732</v>
       </c>
       <c r="D5" t="n">
-        <v>68.50144606382121</v>
+        <v>118.4478605173777</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>46.32965591111124</v>
+        <v>19.07928488433252</v>
       </c>
       <c r="C6" t="n">
-        <v>219.4520278256981</v>
+        <v>346.2849954850478</v>
       </c>
       <c r="D6" t="n">
-        <v>40.33215918586747</v>
+        <v>75.95487463446298</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>31.38058361854505</v>
+        <v>11.31856928226148</v>
       </c>
       <c r="C7" t="n">
-        <v>192.7749974581994</v>
+        <v>341.8327696462884</v>
       </c>
       <c r="D7" t="n">
-        <v>31.85967649821749</v>
+        <v>46.11268966847268</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>14.18625432636641</v>
+        <v>5.424156065963627</v>
       </c>
       <c r="C8" t="n">
-        <v>158.7191513455818</v>
+        <v>191.5978819608075</v>
       </c>
       <c r="D8" t="n">
-        <v>29.12354564648163</v>
+        <v>40.97324043674063</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.101561981893925</v>
+        <v>3.106249736236907</v>
       </c>
       <c r="C9" t="n">
-        <v>95.07342942696533</v>
+        <v>78.09999336824222</v>
       </c>
       <c r="D9" t="n">
-        <v>28.84374755077128</v>
+        <v>41.60155896745857</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.562361508084175</v>
+        <v>1.70824100538945</v>
       </c>
       <c r="C10" t="n">
-        <v>47.54604131667303</v>
+        <v>40.85543071223102</v>
       </c>
       <c r="D10" t="n">
-        <v>30.17892442854695</v>
+        <v>35.01894061048373</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.599267010218054</v>
+        <v>0.5330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>33.40691088011046</v>
+        <v>30.91916219754903</v>
       </c>
       <c r="D11" t="n">
-        <v>29.852984190737</v>
+        <v>33.05151821117311</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>0.8678649705541803</v>
+        <v>0.4339324852770902</v>
       </c>
       <c r="C12" t="n">
-        <v>24.5171854181556</v>
+        <v>25.38505038870978</v>
       </c>
       <c r="D12" t="n">
-        <v>28.8565102709265</v>
+        <v>29.94134148411922</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>18.47158305540374</v>
+        <v>19.77239876353076</v>
       </c>
       <c r="D13" t="n">
-        <v>26.01631416254048</v>
+        <v>24.45533531278805</v>
       </c>
     </row>
     <row r="14">
@@ -2503,13 +2503,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>15.97892563432109</v>
+        <v>20.28094407433061</v>
       </c>
       <c r="D14" t="n">
-        <v>19.0517959486136</v>
+        <v>17.20807376003809</v>
       </c>
     </row>
     <row r="15">
@@ -2517,13 +2517,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>2.5083653843506</v>
       </c>
       <c r="C15" t="n">
-        <v>15.76686813020377</v>
+        <v>32.96708790860789</v>
       </c>
       <c r="D15" t="n">
-        <v>17.20021977840412</v>
+        <v>10.39179944945249</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>14.46605242207675</v>
+        <v>39.67831521483909</v>
       </c>
       <c r="D16" t="n">
-        <v>14.87936820556466</v>
+        <v>3.306526267903257</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>14.63884001802419</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>10.86107485208246</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2559,13 +2559,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>3.21031499288707</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>6.955682484588652</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>33.09962384868121</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>3.610868056219768</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.876520773443155</v>
+        <v>0.1256637061435917</v>
       </c>
       <c r="C2" t="n">
-        <v>4.339324852770901</v>
+        <v>4.693735774004001</v>
       </c>
       <c r="D2" t="n">
-        <v>9.042878103817371</v>
+        <v>7.695920253590747</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21.46591355335651</v>
+        <v>2.32674205906494</v>
       </c>
       <c r="C3" t="n">
-        <v>38.70049450140927</v>
+        <v>30.18874190558942</v>
       </c>
       <c r="D3" t="n">
-        <v>57.31443097392879</v>
+        <v>49.45554060143307</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>47.20930185411637</v>
+        <v>11.37158365829081</v>
       </c>
       <c r="C4" t="n">
-        <v>138.6414290460303</v>
+        <v>122.1137064450353</v>
       </c>
       <c r="D4" t="n">
-        <v>96.39682533229008</v>
+        <v>111.6610386379195</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>48.30198704894308</v>
+        <v>11.48644813968768</v>
       </c>
       <c r="C5" t="n">
-        <v>269.0234146562323</v>
+        <v>301.3965452037708</v>
       </c>
       <c r="D5" t="n">
-        <v>72.25663103256525</v>
+        <v>108.6549271675158</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>37.43403996293088</v>
+        <v>7.003788122096746</v>
       </c>
       <c r="C6" t="n">
-        <v>251.4520942456228</v>
+        <v>299.7943329504401</v>
       </c>
       <c r="D6" t="n">
-        <v>40.01014593887452</v>
+        <v>64.08063615159783</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.402197763571703</v>
+        <v>3.593196597543325</v>
       </c>
       <c r="C7" t="n">
-        <v>203.9139069105838</v>
+        <v>134.7448724078747</v>
       </c>
       <c r="D7" t="n">
-        <v>32.39865598784899</v>
+        <v>35.09355343600648</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.172427743048944</v>
+        <v>2.086213871524472</v>
       </c>
       <c r="C8" t="n">
-        <v>115.1590057081509</v>
+        <v>57.49605429921444</v>
       </c>
       <c r="D8" t="n">
-        <v>30.79251674370121</v>
+        <v>30.62561963397925</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.774999849278233</v>
+        <v>1.220312396378785</v>
       </c>
       <c r="C9" t="n">
-        <v>36.27655941962388</v>
+        <v>31.17343485294896</v>
       </c>
       <c r="D9" t="n">
-        <v>31.50624732468863</v>
+        <v>26.73593522975338</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.1388273369263</v>
+        <v>0.2847068342315751</v>
       </c>
       <c r="C10" t="n">
-        <v>26.1930287493049</v>
+        <v>24.20008090968388</v>
       </c>
       <c r="D10" t="n">
-        <v>23.34596040698915</v>
+        <v>25.90832191507333</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.5330890034060179</v>
+        <v>0.1776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>19.54659679155399</v>
+        <v>20.25738212942868</v>
       </c>
       <c r="D11" t="n">
-        <v>23.10052348092744</v>
+        <v>23.98900515327081</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>14.97067074205961</v>
+        <v>16.05550195525234</v>
       </c>
       <c r="D12" t="n">
-        <v>21.26269177857742</v>
+        <v>19.96089432274615</v>
       </c>
     </row>
     <row r="13">
@@ -2800,13 +2800,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>13.00815708127024</v>
+        <v>16.65044106402591</v>
       </c>
       <c r="D13" t="n">
-        <v>15.60978849752428</v>
+        <v>14.04880964777186</v>
       </c>
     </row>
     <row r="14">
@@ -2814,13 +2814,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>13.21334235145782</v>
+        <v>27.65583282863265</v>
       </c>
       <c r="D14" t="n">
-        <v>14.44249047717483</v>
+        <v>8.604036880019047</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>12.18348900970292</v>
+        <v>33.68376373270807</v>
       </c>
       <c r="D15" t="n">
-        <v>12.541826921753</v>
+        <v>2.5083653843506</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>12.39947350463721</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>9.092947236733956</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -2856,13 +2856,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2.361103228713579</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>29.7499006817911</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>5.66664774891259</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>28.35778243716912</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>2.675262494072558</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.251548396465436</v>
+        <v>0.09719302272043423</v>
       </c>
       <c r="C2" t="n">
-        <v>4.021238596594936</v>
+        <v>2.491675673378405</v>
       </c>
       <c r="D2" t="n">
-        <v>11.53062678637879</v>
+        <v>5.394703634836223</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.82577299245858</v>
+        <v>1.394081740030471</v>
       </c>
       <c r="C3" t="n">
-        <v>28.01907947920397</v>
+        <v>23.96937019918587</v>
       </c>
       <c r="D3" t="n">
-        <v>52.00317589395354</v>
+        <v>44.48789721794421</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>44.60570694245383</v>
+        <v>7.632106652814704</v>
       </c>
       <c r="C4" t="n">
-        <v>118.5911956821977</v>
+        <v>94.61004451056087</v>
       </c>
       <c r="D4" t="n">
-        <v>101.5402015548391</v>
+        <v>106.4410860944392</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>57.5304154688631</v>
+        <v>10.8973995171396</v>
       </c>
       <c r="C5" t="n">
-        <v>264.949161683608</v>
+        <v>240.3809253848316</v>
       </c>
       <c r="D5" t="n">
-        <v>86.34471058850698</v>
+        <v>109.5875874865502</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>47.89947049020189</v>
+        <v>6.681774875103793</v>
       </c>
       <c r="C6" t="n">
-        <v>328.1717503416941</v>
+        <v>311.8295780568017</v>
       </c>
       <c r="D6" t="n">
-        <v>50.39507315439728</v>
+        <v>67.98504677138737</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>19.76258128648829</v>
+        <v>2.75478405811655</v>
       </c>
       <c r="C7" t="n">
-        <v>272.8433949734565</v>
+        <v>183.4925729145458</v>
       </c>
       <c r="D7" t="n">
-        <v>35.2133266559246</v>
+        <v>33.29695513723482</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.757950285407543</v>
+        <v>1.084831213192726</v>
       </c>
       <c r="C8" t="n">
-        <v>175.3254137629166</v>
+        <v>66.34160111447821</v>
       </c>
       <c r="D8" t="n">
-        <v>32.29459073119883</v>
+        <v>26.53664044579129</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.107812321017901</v>
+        <v>0.3328124717396686</v>
       </c>
       <c r="C9" t="n">
-        <v>72.77499382040753</v>
+        <v>28.73281006019139</v>
       </c>
       <c r="D9" t="n">
-        <v>32.28280975874785</v>
+        <v>21.07812321017901</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.1388273369263</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>32.02951885105219</v>
+        <v>16.94005663677871</v>
       </c>
       <c r="D10" t="n">
-        <v>24.62714116103124</v>
+        <v>19.78712497909446</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.3553926689373453</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>23.10052348092744</v>
+        <v>12.9718324162131</v>
       </c>
       <c r="D11" t="n">
-        <v>23.98900515327081</v>
+        <v>17.41424077792992</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>17.14033316844506</v>
+        <v>11.28224461720434</v>
       </c>
       <c r="D12" t="n">
-        <v>21.26269177857742</v>
+        <v>13.23494080095125</v>
       </c>
     </row>
     <row r="13">
@@ -3111,13 +3111,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>14.82929907264807</v>
+        <v>14.30897278939726</v>
       </c>
       <c r="D13" t="n">
-        <v>15.60978849752428</v>
+        <v>8.325220532012953</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>13.82791641431633</v>
+        <v>15.97892563432109</v>
       </c>
       <c r="D14" t="n">
-        <v>14.13520344574558</v>
+        <v>2.765583282863265</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>13.25850274585317</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>11.82515109765283</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3153,13 +3153,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.653263133951629</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>23.97231544229862</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>8.266315669758143</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>33.0554452019901</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>4.249985811684442</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3184,10 +3184,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>0.5350524988145117</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>1.070104997629023</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.258019719767664</v>
+        <v>0.05988660995905543</v>
       </c>
       <c r="C2" t="n">
-        <v>3.445934441906304</v>
+        <v>9.913688317484292</v>
       </c>
       <c r="D2" t="n">
-        <v>8.892670705067609</v>
+        <v>8.145560702135786</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>13.99972226255952</v>
+        <v>0.8295768100885548</v>
       </c>
       <c r="C3" t="n">
-        <v>22.89435646303562</v>
+        <v>15.93376523992573</v>
       </c>
       <c r="D3" t="n">
-        <v>49.88750959130167</v>
+        <v>38.6906770243668</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>39.83244960440584</v>
+        <v>5.092325341928206</v>
       </c>
       <c r="C4" t="n">
-        <v>101.9741340401162</v>
+        <v>75.58082875914494</v>
       </c>
       <c r="D4" t="n">
-        <v>103.6205249401381</v>
+        <v>104.8840342355037</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>62.63550353094652</v>
+        <v>11.41281706186917</v>
       </c>
       <c r="C5" t="n">
-        <v>254.6653544816227</v>
+        <v>205.6270566544945</v>
       </c>
       <c r="D5" t="n">
-        <v>96.87395471655404</v>
+        <v>122.669375645639</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>55.06426523579511</v>
+        <v>10.465430527271</v>
       </c>
       <c r="C6" t="n">
-        <v>372.7705850502182</v>
+        <v>351.9202273074245</v>
       </c>
       <c r="D6" t="n">
-        <v>57.7611261793611</v>
+        <v>85.29325879725866</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>17.48689010804419</v>
+        <v>5.030475236560656</v>
       </c>
       <c r="C7" t="n">
-        <v>339.9762847375577</v>
+        <v>315.3030014344268</v>
       </c>
       <c r="D7" t="n">
-        <v>38.50709020367265</v>
+        <v>43.5375654402333</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.589670517353839</v>
+        <v>1.835868206941535</v>
       </c>
       <c r="C8" t="n">
-        <v>222.5572958142307</v>
+        <v>152.2936126212865</v>
       </c>
       <c r="D8" t="n">
-        <v>33.54631905411351</v>
+        <v>29.12354564648163</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.553124868118454</v>
+        <v>0.5546874528994477</v>
       </c>
       <c r="C9" t="n">
-        <v>78.98749329288135</v>
+        <v>54.0265579124062</v>
       </c>
       <c r="D9" t="n">
-        <v>31.94999728700819</v>
+        <v>22.74218556887735</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.4270602513473625</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>32.17187226816798</v>
+        <v>25.0542014123786</v>
       </c>
       <c r="D10" t="n">
-        <v>25.19655482949439</v>
+        <v>20.64124548178919</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>22.38973814305275</v>
+        <v>15.81497376771187</v>
       </c>
       <c r="D11" t="n">
-        <v>23.98900515327081</v>
+        <v>17.94732978133594</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>16.27246819789088</v>
+        <v>12.80100831567416</v>
       </c>
       <c r="D12" t="n">
-        <v>19.7439280801076</v>
+        <v>13.88583952886689</v>
       </c>
     </row>
     <row r="13">
@@ -3422,13 +3422,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>11.44717823151781</v>
+        <v>14.30897278939726</v>
       </c>
       <c r="D13" t="n">
-        <v>15.86995163914969</v>
+        <v>8.845546815263763</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.06233313145306</v>
+        <v>16.59349969717959</v>
       </c>
       <c r="D14" t="n">
-        <v>11.06233313145306</v>
+        <v>3.072870314292517</v>
       </c>
     </row>
     <row r="15">
@@ -3450,13 +3450,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.075013736150257</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>20.0669230748048</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="D15" t="n">
-        <v>6.808420328951629</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>28.10547327717769</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>3.306526267903257</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3484,7 +3484,7 @@
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4722206457427158</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.911282853719293</v>
+        <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>8.162250413107982</v>
+        <v>11.85951226730147</v>
       </c>
       <c r="D2" t="n">
-        <v>9.143998117354792</v>
+        <v>19.52401659435632</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>11.02993545721291</v>
+        <v>0.5105088062083415</v>
       </c>
       <c r="C3" t="n">
-        <v>18.53539665617978</v>
+        <v>27.47420950334699</v>
       </c>
       <c r="D3" t="n">
-        <v>46.16668579220626</v>
+        <v>36.36393496530186</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>33.9488356128547</v>
+        <v>3.369358120975053</v>
       </c>
       <c r="C4" t="n">
-        <v>82.72795204606172</v>
+        <v>57.61091878061133</v>
       </c>
       <c r="D4" t="n">
-        <v>103.9651183843287</v>
+        <v>100.9914045881651</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>61.31014413021332</v>
+        <v>9.866564427680446</v>
       </c>
       <c r="C5" t="n">
-        <v>226.8573507588318</v>
+        <v>171.5849550097363</v>
       </c>
       <c r="D5" t="n">
-        <v>105.7587714399877</v>
+        <v>129.885221271853</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>65.16743086019903</v>
+        <v>12.63901994447344</v>
       </c>
       <c r="C6" t="n">
-        <v>386.1341348004258</v>
+        <v>341.8170616830205</v>
       </c>
       <c r="D6" t="n">
-        <v>69.63536466222628</v>
+        <v>101.9171926732699</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>32.09922293805371</v>
+        <v>8.324238784308704</v>
       </c>
       <c r="C7" t="n">
-        <v>415.5531865058856</v>
+        <v>406.9894012817407</v>
       </c>
       <c r="D7" t="n">
-        <v>43.6573386601514</v>
+        <v>55.33522760216722</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.511752595819845</v>
+        <v>3.337942194439155</v>
       </c>
       <c r="C8" t="n">
-        <v>308.342410211317</v>
+        <v>273.1271200599838</v>
       </c>
       <c r="D8" t="n">
-        <v>35.29873870619407</v>
+        <v>32.7952820603647</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.32968730217768</v>
+        <v>0.9984374152190059</v>
       </c>
       <c r="C9" t="n">
-        <v>145.5499876408151</v>
+        <v>113.5999903538069</v>
       </c>
       <c r="D9" t="n">
-        <v>32.8374972116473</v>
+        <v>24.62812290873548</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.5694136684631501</v>
+        <v>0.1423534171157875</v>
       </c>
       <c r="C10" t="n">
-        <v>51.38958357879929</v>
+        <v>41.85190463204153</v>
       </c>
       <c r="D10" t="n">
-        <v>26.47773558353648</v>
+        <v>21.49536598448391</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>26.83214650476957</v>
+        <v>21.32356013624072</v>
       </c>
       <c r="D11" t="n">
-        <v>24.16670148773948</v>
+        <v>18.48041878474196</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>18.87606310955342</v>
+        <v>14.97067074205961</v>
       </c>
       <c r="D12" t="n">
-        <v>20.17786056538469</v>
+        <v>14.53673825678252</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.00815708127024</v>
+        <v>14.56913593102267</v>
       </c>
       <c r="D13" t="n">
-        <v>16.1301147807751</v>
+        <v>9.365873098514571</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.67690719431156</v>
+        <v>16.59349969717959</v>
       </c>
       <c r="D14" t="n">
-        <v>11.06233313145306</v>
+        <v>3.68744437715102</v>
       </c>
     </row>
     <row r="15">
@@ -3761,13 +3761,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0.7166758241001715</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>21.14193681095506</v>
+        <v>7.525096153051802</v>
       </c>
       <c r="D15" t="n">
-        <v>6.450082416901544</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>26.45221014322606</v>
+        <v>0.8266315669758143</v>
       </c>
       <c r="D16" t="n">
-        <v>2.89321048441535</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.481498343437441</v>
+        <v>2.158863201638736</v>
       </c>
       <c r="C2" t="n">
-        <v>13.95259837275567</v>
+        <v>11.42263453891164</v>
       </c>
       <c r="D2" t="n">
-        <v>5.324017800130453</v>
+        <v>12.47801332097696</v>
       </c>
     </row>
     <row r="3">
@@ -3904,13 +3904,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>0.06872233929727672</v>
+        <v>0.07363107781851078</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>4.138066573400306</v>
+        <v>4.196971435655114</v>
       </c>
     </row>
     <row r="4">
@@ -3918,13 +3918,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2.233476027161494</v>
+        <v>2.616357631817749</v>
       </c>
       <c r="C4" t="n">
-        <v>3.994731408580271</v>
+        <v>4.390375733391735</v>
       </c>
       <c r="D4" t="n">
-        <v>23.03670988015141</v>
+        <v>24.32574461582747</v>
       </c>
     </row>
     <row r="5">
@@ -3932,13 +3932,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>6.111379458936396</v>
+        <v>7.706719478337463</v>
       </c>
       <c r="C5" t="n">
-        <v>12.64000169217769</v>
+        <v>14.38260386721577</v>
       </c>
       <c r="D5" t="n">
-        <v>25.47635292520474</v>
+        <v>27.95526587842793</v>
       </c>
     </row>
     <row r="6">
@@ -3946,13 +3946,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.3258013690897</v>
+        <v>10.2641722479004</v>
       </c>
       <c r="C6" t="n">
-        <v>15.8994040702771</v>
+        <v>19.64280806657019</v>
       </c>
       <c r="D6" t="n">
-        <v>31.27553661419064</v>
+        <v>36.14598697495907</v>
       </c>
     </row>
     <row r="7">
@@ -3960,13 +3960,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>7.72537268471815</v>
+        <v>12.0970952117292</v>
       </c>
       <c r="C7" t="n">
-        <v>17.54677671800324</v>
+        <v>23.2360046641135</v>
       </c>
       <c r="D7" t="n">
-        <v>29.70375853969149</v>
+        <v>35.69241953559704</v>
       </c>
     </row>
     <row r="8">
@@ -3974,13 +3974,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.261406931236909</v>
+        <v>14.26970288122739</v>
       </c>
       <c r="C8" t="n">
-        <v>18.52557917913731</v>
+        <v>25.61870634232051</v>
       </c>
       <c r="D8" t="n">
-        <v>35.04839304161113</v>
+        <v>44.31118263117978</v>
       </c>
     </row>
     <row r="9">
@@ -3988,13 +3988,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.320311793491715</v>
+        <v>15.08749871886498</v>
       </c>
       <c r="C9" t="n">
-        <v>20.74531073843935</v>
+        <v>30.7296848906294</v>
       </c>
       <c r="D9" t="n">
-        <v>38.71718421238145</v>
+        <v>49.36718330805084</v>
       </c>
     </row>
     <row r="10">
@@ -4002,13 +4002,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7.544731107136738</v>
+        <v>14.94710879715769</v>
       </c>
       <c r="C10" t="n">
-        <v>24.62714116103124</v>
+        <v>37.72365553568369</v>
       </c>
       <c r="D10" t="n">
-        <v>51.53193699591508</v>
+        <v>69.04140730115694</v>
       </c>
     </row>
     <row r="11">
@@ -4016,13 +4016,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>6.04167537193487</v>
+        <v>12.61643974727576</v>
       </c>
       <c r="C11" t="n">
-        <v>24.34439782220815</v>
+        <v>38.20471191076462</v>
       </c>
       <c r="D11" t="n">
-        <v>43.5356019448248</v>
+        <v>58.10670137125595</v>
       </c>
     </row>
     <row r="12">
@@ -4030,13 +4030,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5.207189823325082</v>
+        <v>11.28224461720434</v>
       </c>
       <c r="C12" t="n">
-        <v>22.56448923440869</v>
+        <v>36.66729500591412</v>
       </c>
       <c r="D12" t="n">
-        <v>42.52538355715483</v>
+        <v>59.44875048296136</v>
       </c>
     </row>
     <row r="13">
@@ -4044,13 +4044,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>4.682936549257286</v>
+        <v>10.926851948267</v>
       </c>
       <c r="C13" t="n">
-        <v>21.853703896534</v>
+        <v>36.94316611080748</v>
       </c>
       <c r="D13" t="n">
-        <v>43.70740779306801</v>
+        <v>60.87817514034472</v>
       </c>
     </row>
     <row r="14">
@@ -4058,13 +4058,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.916592502868027</v>
+        <v>11.67690719431156</v>
       </c>
       <c r="C14" t="n">
-        <v>23.04652735719387</v>
+        <v>39.33274002294421</v>
       </c>
       <c r="D14" t="n">
-        <v>44.55661955724149</v>
+        <v>63.60841550585509</v>
       </c>
     </row>
     <row r="15">
@@ -4072,13 +4072,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.733406592801372</v>
+        <v>13.61684065790326</v>
       </c>
       <c r="C15" t="n">
-        <v>25.80032966760617</v>
+        <v>45.50891483036089</v>
       </c>
       <c r="D15" t="n">
-        <v>41.92553570986004</v>
+        <v>61.27578296056467</v>
       </c>
     </row>
     <row r="16">
@@ -4086,13 +4086,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>6.199736752318607</v>
+        <v>14.87936820556466</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>51.25115715250048</v>
       </c>
       <c r="D16" t="n">
-        <v>40.09163099832699</v>
+        <v>57.864209688307</v>
       </c>
     </row>
     <row r="17">
@@ -4100,13 +4100,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>6.611089040398022</v>
+        <v>16.99994324673777</v>
       </c>
       <c r="C17" t="n">
-        <v>31.16656261901925</v>
+        <v>56.19425684338318</v>
       </c>
       <c r="D17" t="n">
-        <v>35.8887690764464</v>
+        <v>53.8331536146696</v>
       </c>
     </row>
     <row r="18">
@@ -4114,13 +4114,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6.955682484588652</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="C18" t="n">
-        <v>33.70830742531424</v>
+        <v>62.06608986248335</v>
       </c>
       <c r="D18" t="n">
-        <v>30.49799243242716</v>
+        <v>45.47946239923349</v>
       </c>
     </row>
     <row r="19">
@@ -4128,13 +4128,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7.823547455142832</v>
+        <v>20.46158565191202</v>
       </c>
       <c r="C19" t="n">
-        <v>36.10868056219768</v>
+        <v>66.80105904006572</v>
       </c>
       <c r="D19" t="n">
-        <v>22.8688310227252</v>
+        <v>34.9050578767911</v>
       </c>
     </row>
     <row r="20">
@@ -4142,13 +4142,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>7.397468951499714</v>
+        <v>20.84741249968101</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>73.30219233758808</v>
       </c>
       <c r="D20" t="n">
-        <v>13.4499435481813</v>
+        <v>20.17491532227195</v>
       </c>
     </row>
     <row r="21">
@@ -4156,13 +4156,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>11.44977350273866</v>
+        <v>27.41820207255788</v>
       </c>
       <c r="C21" t="n">
-        <v>54.95891281314559</v>
+        <v>99.77179087514119</v>
       </c>
       <c r="D21" t="n">
-        <v>0.763318233515911</v>
+        <v>0.761616724237719</v>
       </c>
     </row>
   </sheetData>
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.858849314766712</v>
+        <v>0.07755806863549802</v>
       </c>
       <c r="C2" t="n">
-        <v>4.8321622003028</v>
+        <v>16.99699800362503</v>
       </c>
       <c r="D2" t="n">
-        <v>6.802529842726149</v>
+        <v>16.94987411382118</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.2514505854742</v>
+        <v>0.2699806186678729</v>
       </c>
       <c r="C3" t="n">
-        <v>25.16219365984575</v>
+        <v>35.85342615909352</v>
       </c>
       <c r="D3" t="n">
-        <v>49.94641445355648</v>
+        <v>41.3855744725243</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>46.5073522455799</v>
+        <v>2.246238747316702</v>
       </c>
       <c r="C4" t="n">
-        <v>121.9605538031728</v>
+        <v>62.37141339850411</v>
       </c>
       <c r="D4" t="n">
-        <v>105.0116614370558</v>
+        <v>96.0139437276338</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>37.28186906877263</v>
+        <v>8.001243789611506</v>
       </c>
       <c r="C5" t="n">
-        <v>333.0579086657305</v>
+        <v>141.2489509485099</v>
       </c>
       <c r="D5" t="n">
-        <v>97.36482856867744</v>
+        <v>135.1866588747858</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>19.92456965768902</v>
+        <v>12.88052987971816</v>
       </c>
       <c r="C6" t="n">
-        <v>338.0334060308533</v>
+        <v>314.4459356886194</v>
       </c>
       <c r="D6" t="n">
-        <v>58.72716592033996</v>
+        <v>114.5159609618692</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.629341336151211</v>
+        <v>10.95924962250714</v>
       </c>
       <c r="C7" t="n">
-        <v>216.8494146617397</v>
+        <v>442.6219342073787</v>
       </c>
       <c r="D7" t="n">
-        <v>29.94330497952771</v>
+        <v>67.97130230352791</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.585522542358599</v>
+        <v>5.507604620824606</v>
       </c>
       <c r="C8" t="n">
-        <v>107.2313929963579</v>
+        <v>385.3654263480004</v>
       </c>
       <c r="D8" t="n">
-        <v>24.20008090968387</v>
+        <v>37.71874679716245</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.3328124717396686</v>
+        <v>1.774999849278233</v>
       </c>
       <c r="C9" t="n">
-        <v>39.160934174701</v>
+        <v>202.904670270618</v>
       </c>
       <c r="D9" t="n">
-        <v>20.1906232855399</v>
+        <v>26.73593522975338</v>
       </c>
     </row>
     <row r="10">
@@ -4313,13 +4313,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>0.4270602513473625</v>
       </c>
       <c r="C10" t="n">
-        <v>20.92595231602077</v>
+        <v>78.43673283079892</v>
       </c>
       <c r="D10" t="n">
-        <v>18.93300447639974</v>
+        <v>22.34948648717864</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>15.10418842983717</v>
+        <v>31.45225120095506</v>
       </c>
       <c r="D11" t="n">
-        <v>16.17036643664921</v>
+        <v>18.8358114536793</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>10.63134588928871</v>
+        <v>18.22516438163779</v>
       </c>
       <c r="D12" t="n">
-        <v>13.0179745583127</v>
+        <v>15.18763698469816</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>9.626036240139976</v>
+        <v>15.34962535589888</v>
       </c>
       <c r="D13" t="n">
-        <v>9.105709956889166</v>
+        <v>9.886199381765381</v>
       </c>
     </row>
     <row r="14">
@@ -4369,13 +4369,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.3072870314292517</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>17.51536079146734</v>
+        <v>16.59349969717959</v>
       </c>
       <c r="D14" t="n">
-        <v>5.223879534297279</v>
+        <v>4.302018440009523</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>22.21695054710532</v>
+        <v>10.75013736150257</v>
       </c>
       <c r="D15" t="n">
-        <v>2.150027472300515</v>
+        <v>0.3583379120500857</v>
       </c>
     </row>
     <row r="16">
@@ -4400,7 +4400,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>2.479894700927443</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8.153414683769761</v>
+        <v>3.30554452019901</v>
       </c>
       <c r="C2" t="n">
-        <v>6.864379948093698</v>
+        <v>7.682175785731292</v>
       </c>
       <c r="D2" t="n">
-        <v>8.072911372021522</v>
+        <v>25.20539055883261</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>13.76410281354028</v>
+        <v>3.583379120500858</v>
       </c>
       <c r="C3" t="n">
-        <v>35.15638528907828</v>
+        <v>22.55074476654924</v>
       </c>
       <c r="D3" t="n">
-        <v>7.608544707912781</v>
+        <v>11.52571804785755</v>
       </c>
     </row>
     <row r="4">
@@ -4540,13 +4540,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.008254892261474</v>
+        <v>0.9189158511750145</v>
       </c>
       <c r="C4" t="n">
-        <v>1.493238258159399</v>
+        <v>1.710204500797944</v>
       </c>
       <c r="D4" t="n">
-        <v>19.62906359871073</v>
+        <v>18.45489334443154</v>
       </c>
     </row>
     <row r="5">
@@ -4554,13 +4554,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>4.736932672990861</v>
+        <v>3.632466505713199</v>
       </c>
       <c r="C5" t="n">
-        <v>9.35114688295087</v>
+        <v>8.197593330460869</v>
       </c>
       <c r="D5" t="n">
-        <v>28.49522711576368</v>
+        <v>24.20008090968388</v>
       </c>
     </row>
     <row r="6">
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>8.050331174823848</v>
+        <v>5.75598678999905</v>
       </c>
       <c r="C6" t="n">
-        <v>18.47551004622073</v>
+        <v>14.49059611468292</v>
       </c>
       <c r="D6" t="n">
-        <v>32.8453511932813</v>
+        <v>28.6591789823729</v>
       </c>
     </row>
     <row r="7">
@@ -4582,13 +4582,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.683558444063037</v>
+        <v>6.108434215823654</v>
       </c>
       <c r="C7" t="n">
-        <v>20.9603134856694</v>
+        <v>16.58859095865835</v>
       </c>
       <c r="D7" t="n">
-        <v>32.21899615797182</v>
+        <v>27.90716024091983</v>
       </c>
     </row>
     <row r="8">
@@ -4596,13 +4596,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.762098260402782</v>
+        <v>6.508987279156353</v>
       </c>
       <c r="C8" t="n">
-        <v>21.69662426385451</v>
+        <v>17.19040230136165</v>
       </c>
       <c r="D8" t="n">
-        <v>35.79943003535994</v>
+        <v>32.04424506661589</v>
       </c>
     </row>
     <row r="9">
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.874999246391162</v>
+        <v>6.656249434793372</v>
       </c>
       <c r="C9" t="n">
-        <v>22.74218556887735</v>
+        <v>18.74843590800133</v>
       </c>
       <c r="D9" t="n">
-        <v>39.2718716652809</v>
+        <v>34.72343455150543</v>
       </c>
     </row>
     <row r="10">
@@ -4624,13 +4624,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.256498192715677</v>
+        <v>6.26355035309465</v>
       </c>
       <c r="C10" t="n">
-        <v>25.62361508084176</v>
+        <v>21.78007281871549</v>
       </c>
       <c r="D10" t="n">
-        <v>50.67781649322036</v>
+        <v>46.12250714551515</v>
       </c>
     </row>
     <row r="11">
@@ -4638,13 +4638,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>6.75246070980956</v>
+        <v>5.330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>27.36523550817559</v>
+        <v>22.7451308119901</v>
       </c>
       <c r="D11" t="n">
-        <v>46.37874329632356</v>
+        <v>41.04785326226338</v>
       </c>
     </row>
     <row r="12">
@@ -4652,13 +4652,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5.641122308602172</v>
+        <v>4.339324852770901</v>
       </c>
       <c r="C12" t="n">
-        <v>25.81898287398687</v>
+        <v>21.69662426385451</v>
       </c>
       <c r="D12" t="n">
-        <v>43.17628228507047</v>
+        <v>39.4878561602152</v>
       </c>
     </row>
     <row r="13">
@@ -4666,13 +4666,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>4.943099690882691</v>
+        <v>3.902447124381071</v>
       </c>
       <c r="C13" t="n">
-        <v>23.93500902953724</v>
+        <v>20.55288818840698</v>
       </c>
       <c r="D13" t="n">
-        <v>44.22773407631881</v>
+        <v>40.06512381031234</v>
       </c>
     </row>
     <row r="14">
@@ -4680,13 +4680,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.994731408580272</v>
       </c>
       <c r="C14" t="n">
-        <v>23.96838845148163</v>
+        <v>21.20280516861837</v>
       </c>
       <c r="D14" t="n">
-        <v>44.86390658867074</v>
+        <v>40.86917518009047</v>
       </c>
     </row>
     <row r="15">
@@ -4694,13 +4694,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.375068680751286</v>
+        <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>26.15866757965626</v>
+        <v>23.29196428325557</v>
       </c>
       <c r="D15" t="n">
-        <v>42.28387362191012</v>
+        <v>39.77550823755952</v>
       </c>
     </row>
     <row r="16">
@@ -4708,13 +4708,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>5.7864209688307</v>
+        <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>26.03889435973815</v>
       </c>
       <c r="D16" t="n">
-        <v>40.5049467818149</v>
+        <v>36.78510473042374</v>
       </c>
     </row>
     <row r="17">
@@ -4722,13 +4722,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>6.138868394655306</v>
+        <v>5.194427103169874</v>
       </c>
       <c r="C17" t="n">
-        <v>31.63878326476196</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>36.36098972218912</v>
+        <v>34.47210713921825</v>
       </c>
     </row>
     <row r="18">
@@ -4736,13 +4736,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6.42062998577414</v>
+        <v>5.885577486959628</v>
       </c>
       <c r="C18" t="n">
-        <v>34.24335992412875</v>
+        <v>31.03304493124168</v>
       </c>
       <c r="D18" t="n">
-        <v>31.03304493124168</v>
+        <v>28.89283493598363</v>
       </c>
     </row>
     <row r="19">
@@ -4750,13 +4750,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7.221736112439537</v>
+        <v>6.018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>33.09962384868121</v>
       </c>
       <c r="D19" t="n">
-        <v>23.47064236542849</v>
+        <v>21.66520833731861</v>
       </c>
     </row>
     <row r="20">
@@ -4767,10 +4767,10 @@
         <v>6.724971774090649</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>14.12244072559037</v>
+        <v>12.77744637077223</v>
       </c>
     </row>
     <row r="21">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.39758019061155</v>
+        <v>11.67775086319653</v>
       </c>
       <c r="C21" t="n">
-        <v>70.14027276261338</v>
+        <v>59.94578776440888</v>
       </c>
       <c r="D21" t="n">
-        <v>1.576185904777829</v>
+        <v>0.7785167242131024</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.909139431861552</v>
+        <v>1.792671307954676</v>
       </c>
       <c r="C2" t="n">
-        <v>4.864559874542945</v>
+        <v>3.914228096832033</v>
       </c>
       <c r="D2" t="n">
-        <v>13.23494080095125</v>
+        <v>21.84977690571701</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>22.37893891830604</v>
+        <v>8.541205026947251</v>
       </c>
       <c r="C3" t="n">
-        <v>29.90894380987908</v>
+        <v>27.5478405811655</v>
       </c>
       <c r="D3" t="n">
-        <v>12.54673566027424</v>
+        <v>30.80724295926491</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>15.97892563432108</v>
+        <v>4.658392856651115</v>
       </c>
       <c r="C4" t="n">
-        <v>54.11393345808419</v>
+        <v>37.19056653227767</v>
       </c>
       <c r="D4" t="n">
-        <v>19.05474119172634</v>
+        <v>20.31825048709199</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3.067961575771283</v>
+        <v>2.454369260617026</v>
       </c>
       <c r="C5" t="n">
-        <v>5.473243451175969</v>
+        <v>5.129631754689585</v>
       </c>
       <c r="D5" t="n">
-        <v>29.40334374219198</v>
+        <v>25.72178985126644</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.446556336712058</v>
+        <v>5.514476854754335</v>
       </c>
       <c r="C6" t="n">
-        <v>16.34217228489241</v>
+        <v>13.68556299720054</v>
       </c>
       <c r="D6" t="n">
-        <v>34.57617239586842</v>
+        <v>30.06798693796707</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.462084373530759</v>
+        <v>6.767186925373263</v>
       </c>
       <c r="C7" t="n">
-        <v>24.49362347325367</v>
+        <v>19.40326162673396</v>
       </c>
       <c r="D7" t="n">
-        <v>34.97378021608837</v>
+        <v>30.48228446915921</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.596583809012571</v>
+        <v>6.926230053461247</v>
       </c>
       <c r="C8" t="n">
-        <v>25.61870634232051</v>
+        <v>20.36144738607885</v>
       </c>
       <c r="D8" t="n">
-        <v>36.63391558396972</v>
+        <v>32.96217917008666</v>
       </c>
     </row>
     <row r="9">
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.429686699290611</v>
+        <v>7.09999939711293</v>
       </c>
       <c r="C9" t="n">
-        <v>25.73749781453438</v>
+        <v>20.85624822901923</v>
       </c>
       <c r="D9" t="n">
-        <v>40.27030908049991</v>
+        <v>35.38905949498476</v>
       </c>
     </row>
     <row r="10">
@@ -4935,13 +4935,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.825911861178826</v>
+        <v>6.690610604442014</v>
       </c>
       <c r="C10" t="n">
-        <v>27.3318560862312</v>
+        <v>22.91890015564179</v>
       </c>
       <c r="D10" t="n">
-        <v>50.1084028247572</v>
+        <v>45.26838664282043</v>
       </c>
     </row>
     <row r="11">
@@ -4949,13 +4949,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>7.640942382152923</v>
+        <v>5.863979037466197</v>
       </c>
       <c r="C11" t="n">
-        <v>29.14219885286231</v>
+        <v>24.87748682561417</v>
       </c>
       <c r="D11" t="n">
-        <v>47.97801030654161</v>
+        <v>43.35790561035613</v>
       </c>
     </row>
     <row r="12">
@@ -4963,13 +4963,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6.075054793879263</v>
+        <v>4.773257338047991</v>
       </c>
       <c r="C12" t="n">
-        <v>29.29044275620359</v>
+        <v>24.5171854181556</v>
       </c>
       <c r="D12" t="n">
-        <v>44.69504598354028</v>
+        <v>40.57268737340794</v>
       </c>
     </row>
     <row r="13">
@@ -4977,13 +4977,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.203262832508096</v>
+        <v>3.902447124381071</v>
       </c>
       <c r="C13" t="n">
-        <v>26.79680358741669</v>
+        <v>22.89435646303562</v>
       </c>
       <c r="D13" t="n">
-        <v>44.74806035956962</v>
+        <v>40.32528695193774</v>
       </c>
     </row>
     <row r="14">
@@ -4991,13 +4991,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>25.50482360862789</v>
+        <v>22.43195329433537</v>
       </c>
       <c r="D14" t="n">
-        <v>44.86390658867074</v>
+        <v>41.17646221151972</v>
       </c>
     </row>
     <row r="15">
@@ -5005,13 +5005,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.658392856651115</v>
+        <v>3.941717032550943</v>
       </c>
       <c r="C15" t="n">
-        <v>26.51700549170635</v>
+        <v>23.65030219530566</v>
       </c>
       <c r="D15" t="n">
-        <v>43.00054944601029</v>
+        <v>40.1338461496096</v>
       </c>
     </row>
     <row r="16">
@@ -5019,13 +5019,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>5.373105185342793</v>
+        <v>4.546473618366978</v>
       </c>
       <c r="C16" t="n">
-        <v>29.34542062764141</v>
+        <v>26.03889435973815</v>
       </c>
       <c r="D16" t="n">
-        <v>40.91826256530281</v>
+        <v>37.19842051391164</v>
       </c>
     </row>
     <row r="17">
@@ -5033,13 +5033,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5.66664774891259</v>
+        <v>4.722206457427158</v>
       </c>
       <c r="C17" t="n">
-        <v>31.63878326476196</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
-        <v>36.36098972218912</v>
+        <v>34.94432778496098</v>
       </c>
     </row>
     <row r="18">
@@ -5047,13 +5047,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>5.885577486959628</v>
+        <v>5.350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>31.56809743005619</v>
+        <v>29.42788743479814</v>
       </c>
     </row>
     <row r="19">
@@ -5061,13 +5061,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>6.619924769736241</v>
+        <v>5.416302084329653</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>33.09962384868121</v>
       </c>
       <c r="D19" t="n">
-        <v>24.07245370813179</v>
+        <v>22.26701968002191</v>
       </c>
     </row>
     <row r="20">
@@ -5078,10 +5078,10 @@
         <v>6.052474596681584</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>14.79493790299943</v>
+        <v>13.4499435481813</v>
       </c>
     </row>
     <row r="21">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.43861732497823</v>
+        <v>13.62735279991251</v>
       </c>
       <c r="C21" t="n">
-        <v>86.131233497247</v>
+        <v>73.74802691717356</v>
       </c>
       <c r="D21" t="n">
-        <v>3.250235226311207</v>
+        <v>1.603217976460295</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.199155915241861</v>
+        <v>1.085812960896972</v>
       </c>
       <c r="C2" t="n">
-        <v>6.550220682734719</v>
+        <v>8.833765842812801</v>
       </c>
       <c r="D2" t="n">
-        <v>14.79395615529518</v>
+        <v>20.9622769810779</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21.30392518215579</v>
+        <v>7.220754364735291</v>
       </c>
       <c r="C3" t="n">
-        <v>23.34105166846792</v>
+        <v>19.75276380944582</v>
       </c>
       <c r="D3" t="n">
-        <v>20.21909396896306</v>
+        <v>41.71445995344698</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>31.49839334305466</v>
+        <v>11.8182788637231</v>
       </c>
       <c r="C4" t="n">
-        <v>65.62590703808229</v>
+        <v>56.90896917207485</v>
       </c>
       <c r="D4" t="n">
-        <v>21.07125097624929</v>
+        <v>31.74088502600363</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>13.81809893727386</v>
+        <v>4.982369599052563</v>
       </c>
       <c r="C5" t="n">
-        <v>59.29756133650736</v>
+        <v>43.245986372072</v>
       </c>
       <c r="D5" t="n">
-        <v>29.52606220522283</v>
+        <v>27.243498792849</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>5.957245069369646</v>
+        <v>4.467933802027235</v>
       </c>
       <c r="C6" t="n">
-        <v>12.23650338573225</v>
+        <v>10.54593383901924</v>
       </c>
       <c r="D6" t="n">
-        <v>36.54850353370026</v>
+        <v>31.95981476405067</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.462084373530759</v>
+        <v>6.94684675525043</v>
       </c>
       <c r="C7" t="n">
-        <v>24.37385025333556</v>
+        <v>19.8823545064064</v>
       </c>
       <c r="D7" t="n">
-        <v>37.4890178343687</v>
+        <v>32.81786225756237</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.43106935762236</v>
+        <v>7.510369937488099</v>
       </c>
       <c r="C8" t="n">
-        <v>29.54078842078653</v>
+        <v>23.86628669023996</v>
       </c>
       <c r="D8" t="n">
-        <v>37.88564390688441</v>
+        <v>33.96356182841841</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.984374152190059</v>
+        <v>7.432811868852599</v>
       </c>
       <c r="C9" t="n">
-        <v>29.7312474754104</v>
+        <v>23.96249796525614</v>
       </c>
       <c r="D9" t="n">
-        <v>41.15780900513902</v>
+        <v>36.49843440078366</v>
       </c>
     </row>
     <row r="10">
@@ -5246,13 +5246,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.395325529641976</v>
+        <v>7.117670855789377</v>
       </c>
       <c r="C10" t="n">
-        <v>29.89421759431538</v>
+        <v>24.76949457814703</v>
       </c>
       <c r="D10" t="n">
-        <v>49.25428232206248</v>
+        <v>44.69897297435728</v>
       </c>
     </row>
     <row r="11">
@@ -5260,13 +5260,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.351727720027615</v>
+        <v>6.397068040872215</v>
       </c>
       <c r="C11" t="n">
-        <v>31.27455486648638</v>
+        <v>26.47675383583222</v>
       </c>
       <c r="D11" t="n">
-        <v>49.75497365122833</v>
+        <v>44.42408361716816</v>
       </c>
     </row>
     <row r="12">
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6.725953521794898</v>
+        <v>5.207189823325082</v>
       </c>
       <c r="C12" t="n">
-        <v>31.67707142522758</v>
+        <v>27.12078032981814</v>
       </c>
       <c r="D12" t="n">
-        <v>46.2138096820101</v>
+        <v>42.09145107187774</v>
       </c>
     </row>
     <row r="13">
@@ -5288,13 +5288,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.463425974133501</v>
+        <v>4.162610266006476</v>
       </c>
       <c r="C13" t="n">
-        <v>30.17892442854696</v>
+        <v>25.49598787928967</v>
       </c>
       <c r="D13" t="n">
-        <v>45.00822350119503</v>
+        <v>41.10577637681396</v>
       </c>
     </row>
     <row r="14">
@@ -5302,13 +5302,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>27.9631198600619</v>
+        <v>24.27567548291088</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>41.48374924294897</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.30005494460103</v>
+        <v>3.583379120500858</v>
       </c>
       <c r="C15" t="n">
-        <v>27.5920192278566</v>
+        <v>24.36697801940583</v>
       </c>
       <c r="D15" t="n">
-        <v>43.00054944601029</v>
+        <v>40.1338461496096</v>
       </c>
     </row>
     <row r="16">
@@ -5330,13 +5330,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4.959789401854886</v>
+        <v>4.133157834879071</v>
       </c>
       <c r="C16" t="n">
-        <v>29.34542062764141</v>
+        <v>26.45221014322606</v>
       </c>
       <c r="D16" t="n">
-        <v>41.33157834879071</v>
+        <v>37.61173629739955</v>
       </c>
     </row>
     <row r="17">
@@ -5344,13 +5344,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5.194427103169874</v>
+        <v>4.249985811684442</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>35.41654843070368</v>
       </c>
     </row>
     <row r="18">
@@ -5358,13 +5358,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>5.350524988145117</v>
+        <v>4.815472489330605</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>31.56809743005619</v>
+        <v>29.42788743479814</v>
       </c>
     </row>
     <row r="19">
@@ -5372,13 +5372,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>6.018113427032947</v>
+        <v>4.814490741626358</v>
       </c>
       <c r="C19" t="n">
-        <v>37.31230324760427</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>24.67426505083508</v>
+        <v>22.8688310227252</v>
       </c>
     </row>
     <row r="20">
@@ -5389,10 +5389,10 @@
         <v>5.37997741927252</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>15.46743508040849</v>
+        <v>14.12244072559037</v>
       </c>
     </row>
     <row r="21">
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.72765148336432</v>
+        <v>14.8365726993297</v>
       </c>
       <c r="C21" t="n">
-        <v>102.0386740485223</v>
+        <v>87.37092811827488</v>
       </c>
       <c r="D21" t="n">
-        <v>4.18191287084108</v>
+        <v>2.47276211655495</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.58360010467911</v>
+        <v>1.273326772408113</v>
       </c>
       <c r="C2" t="n">
         <v>10.83751290718054</v>
       </c>
       <c r="D2" t="n">
-        <v>17.19727453529138</v>
+        <v>20.21320348273758</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>23.04652735719387</v>
+        <v>5.30634634145401</v>
       </c>
       <c r="C3" t="n">
-        <v>24.48969648243668</v>
+        <v>28.61794557879453</v>
       </c>
       <c r="D3" t="n">
-        <v>26.96370069713865</v>
+        <v>48.80267837810894</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>36.46309148343079</v>
+        <v>13.06902543893354</v>
       </c>
       <c r="C4" t="n">
-        <v>61.01856506205201</v>
+        <v>52.56964431930395</v>
       </c>
       <c r="D4" t="n">
-        <v>26.16357631817749</v>
+        <v>45.49909735331843</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>30.48326621686347</v>
+        <v>11.75642875835556</v>
       </c>
       <c r="C5" t="n">
-        <v>92.72607066611126</v>
+        <v>78.56436003235102</v>
       </c>
       <c r="D5" t="n">
-        <v>30.23782929080177</v>
+        <v>32.29949946972007</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>12.19625172985813</v>
+        <v>5.75598678999905</v>
       </c>
       <c r="C6" t="n">
-        <v>54.54099370943156</v>
+        <v>42.18373535607696</v>
       </c>
       <c r="D6" t="n">
-        <v>38.07806645691679</v>
+        <v>33.81139093426016</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.683558444063037</v>
+        <v>6.347980655659875</v>
       </c>
       <c r="C7" t="n">
-        <v>21.08008670558751</v>
+        <v>17.6066633279623</v>
       </c>
       <c r="D7" t="n">
-        <v>39.88448223273092</v>
+        <v>35.03366682604743</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.6814150222053</v>
+        <v>7.927612711792993</v>
       </c>
       <c r="C8" t="n">
-        <v>31.62700229231099</v>
+        <v>25.78560345204247</v>
       </c>
       <c r="D8" t="n">
-        <v>39.30426933952106</v>
+        <v>35.21529015133309</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.76093658624928</v>
+        <v>7.876561831172157</v>
       </c>
       <c r="C9" t="n">
-        <v>34.05780960802609</v>
+        <v>27.73437264497238</v>
       </c>
       <c r="D9" t="n">
-        <v>42.15624642035802</v>
+        <v>37.49687181600267</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.82238578098934</v>
+        <v>7.402377690020952</v>
       </c>
       <c r="C10" t="n">
-        <v>33.16834618797849</v>
+        <v>27.47420950334699</v>
       </c>
       <c r="D10" t="n">
-        <v>48.68486865359933</v>
+        <v>44.55661955724149</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.884816723433632</v>
+        <v>6.75246070980956</v>
       </c>
       <c r="C11" t="n">
-        <v>33.7623035490478</v>
+        <v>28.43141351498762</v>
       </c>
       <c r="D11" t="n">
-        <v>50.82115165804038</v>
+        <v>45.13486895504285</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>7.376852249710534</v>
+        <v>5.641122308602172</v>
       </c>
       <c r="C12" t="n">
-        <v>34.28066633689012</v>
+        <v>29.29044275620359</v>
       </c>
       <c r="D12" t="n">
-        <v>47.08167465256428</v>
+        <v>43.39324852770902</v>
       </c>
     </row>
     <row r="13">
@@ -5599,13 +5599,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.723589115758904</v>
+        <v>4.422773407631881</v>
       </c>
       <c r="C13" t="n">
-        <v>32.780555844801</v>
+        <v>28.35778243716912</v>
       </c>
       <c r="D13" t="n">
-        <v>45.78871292607123</v>
+        <v>41.88626580169016</v>
       </c>
     </row>
     <row r="14">
@@ -5613,13 +5613,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>30.72870314292517</v>
+        <v>26.42668470291564</v>
       </c>
       <c r="D14" t="n">
-        <v>45.7857676829585</v>
+        <v>41.48374924294897</v>
       </c>
     </row>
     <row r="15">
@@ -5627,13 +5627,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.30005494460103</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>29.38370878810703</v>
+        <v>25.80032966760617</v>
       </c>
       <c r="D15" t="n">
-        <v>43.00054944601029</v>
+        <v>40.49218406165969</v>
       </c>
     </row>
     <row r="16">
@@ -5641,13 +5641,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4.546473618366978</v>
+        <v>3.719842051391165</v>
       </c>
       <c r="C16" t="n">
-        <v>29.75873641112932</v>
+        <v>26.86552592671396</v>
       </c>
       <c r="D16" t="n">
-        <v>41.74489413227862</v>
+        <v>38.02505208088746</v>
       </c>
     </row>
     <row r="17">
@@ -5655,13 +5655,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>4.722206457427158</v>
+        <v>3.777765165941727</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>35.41654843070368</v>
       </c>
     </row>
     <row r="18">
@@ -5669,13 +5669,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>4.815472489330605</v>
+        <v>4.280419990516093</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>32.1031499288707</v>
+        <v>29.96293993361265</v>
       </c>
     </row>
     <row r="19">
@@ -5683,13 +5683,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>5.416302084329653</v>
+        <v>4.212679398923063</v>
       </c>
       <c r="C19" t="n">
-        <v>37.31230324760427</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>24.67426505083508</v>
+        <v>23.47064236542849</v>
       </c>
     </row>
     <row r="20">
@@ -5700,10 +5700,10 @@
         <v>4.707480241863455</v>
       </c>
       <c r="C20" t="n">
-        <v>39.67733346713483</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>16.13993225781756</v>
+        <v>14.79493790299943</v>
       </c>
     </row>
     <row r="21">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.04570652137758</v>
+        <v>16.07800921127686</v>
       </c>
       <c r="C21" t="n">
-        <v>117.7267520680347</v>
+        <v>101.5453213343801</v>
       </c>
       <c r="D21" t="n">
-        <v>6.01523550712586</v>
+        <v>3.384844044479339</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.528622233241289</v>
+        <v>1.975276380944582</v>
       </c>
       <c r="C2" t="n">
-        <v>10.66178006812036</v>
+        <v>16.45703676628928</v>
       </c>
       <c r="D2" t="n">
-        <v>16.24007052365074</v>
+        <v>24.34341607450391</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.16018910670825</v>
+        <v>4.786020058203201</v>
       </c>
       <c r="C3" t="n">
-        <v>32.27004703859266</v>
+        <v>36.36393496530186</v>
       </c>
       <c r="D3" t="n">
-        <v>32.01970137400972</v>
+        <v>53.30890034060181</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>29.48188355853172</v>
+        <v>11.63960078155018</v>
       </c>
       <c r="C4" t="n">
-        <v>51.08916878129977</v>
+        <v>63.21375292874787</v>
       </c>
       <c r="D4" t="n">
-        <v>29.11176467403067</v>
+        <v>58.95100439690822</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>25.94268308472197</v>
+        <v>15.70796326794897</v>
       </c>
       <c r="C5" t="n">
-        <v>76.0118160013093</v>
+        <v>87.84187583748337</v>
       </c>
       <c r="D5" t="n">
-        <v>26.31083847381452</v>
+        <v>40.5216364927871</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>14.57109942643116</v>
+        <v>10.90819874188631</v>
       </c>
       <c r="C6" t="n">
-        <v>69.19259644761097</v>
+        <v>85.77627866774809</v>
       </c>
       <c r="D6" t="n">
-        <v>30.47050349670826</v>
+        <v>36.6290068454485</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.749114556069321</v>
+        <v>6.827073535332318</v>
       </c>
       <c r="C7" t="n">
-        <v>31.62013005838127</v>
+        <v>40.12402867256714</v>
       </c>
       <c r="D7" t="n">
-        <v>31.26081039862693</v>
+        <v>36.83026512481909</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.840016181936775</v>
+        <v>7.677267047210056</v>
       </c>
       <c r="C8" t="n">
-        <v>18.60902773399829</v>
+        <v>25.11801501315464</v>
       </c>
       <c r="D8" t="n">
-        <v>29.37389131106456</v>
+        <v>37.05115835827462</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.77031209493525</v>
+        <v>8.320311793491715</v>
       </c>
       <c r="C9" t="n">
-        <v>21.74374815365835</v>
+        <v>30.7296848906294</v>
       </c>
       <c r="D9" t="n">
-        <v>30.17499743772996</v>
+        <v>38.49530923122167</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.270602513473626</v>
+        <v>7.829437941368314</v>
       </c>
       <c r="C10" t="n">
-        <v>21.35301256736813</v>
+        <v>31.03304493124168</v>
       </c>
       <c r="D10" t="n">
-        <v>33.16834618797849</v>
+        <v>44.12955930589413</v>
       </c>
     </row>
     <row r="11">
@@ -5882,13 +5882,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.731623023842126</v>
+        <v>7.107853378746905</v>
       </c>
       <c r="C11" t="n">
-        <v>20.25738212942868</v>
+        <v>30.56376952861169</v>
       </c>
       <c r="D11" t="n">
-        <v>34.65078522139116</v>
+        <v>46.20104696185489</v>
       </c>
     </row>
     <row r="12">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.037527396939631</v>
+        <v>6.075054793879263</v>
       </c>
       <c r="C12" t="n">
-        <v>19.96089432274615</v>
+        <v>31.46010518258904</v>
       </c>
       <c r="D12" t="n">
-        <v>31.89403766786613</v>
+        <v>44.47807974090174</v>
       </c>
     </row>
     <row r="13">
@@ -5910,13 +5910,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.341468274628643</v>
+        <v>4.682936549257286</v>
       </c>
       <c r="C13" t="n">
-        <v>18.99190933865455</v>
+        <v>30.95941385342317</v>
       </c>
       <c r="D13" t="n">
-        <v>30.43908757017236</v>
+        <v>42.14642894331557</v>
       </c>
     </row>
     <row r="14">
@@ -5924,13 +5924,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.536435157146258</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>17.20807376003809</v>
+        <v>28.88498095434966</v>
       </c>
       <c r="D14" t="n">
-        <v>29.49955501720816</v>
+        <v>41.79103627437823</v>
       </c>
     </row>
     <row r="15">
@@ -5938,13 +5938,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>16.12520604225386</v>
+        <v>27.23368131580652</v>
       </c>
       <c r="D15" t="n">
-        <v>27.95035713990669</v>
+        <v>40.85052197370977</v>
       </c>
     </row>
     <row r="16">
@@ -5952,13 +5952,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>3.306526267903257</v>
       </c>
       <c r="C16" t="n">
-        <v>15.70599977254047</v>
+        <v>27.69215749368978</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>38.02505208088746</v>
       </c>
     </row>
     <row r="17">
@@ -5966,13 +5966,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.416661937228147</v>
+        <v>3.305544520199011</v>
       </c>
       <c r="C17" t="n">
-        <v>16.52772260099505</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
-        <v>23.61103228713579</v>
+        <v>35.8887690764464</v>
       </c>
     </row>
     <row r="18">
@@ -5980,13 +5980,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.070104997629023</v>
+        <v>3.745367491701582</v>
       </c>
       <c r="C18" t="n">
-        <v>17.12167996206437</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>29.96293993361265</v>
       </c>
     </row>
     <row r="19">
@@ -5994,13 +5994,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.203622685406589</v>
+        <v>3.610868056219768</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>24.07245370813179</v>
       </c>
     </row>
     <row r="20">
@@ -6008,13 +6008,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1.34499435481813</v>
+        <v>4.03498306445439</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>10.08745766113597</v>
+        <v>15.46743508040849</v>
       </c>
     </row>
     <row r="21">
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.049020076605427</v>
+        <v>17.34518009984526</v>
       </c>
       <c r="C21" t="n">
-        <v>66.08456321817587</v>
+        <v>115.345447663971</v>
       </c>
       <c r="D21" t="n">
-        <v>4.405637547878392</v>
+        <v>4.336295024961315</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.6479945425319</v>
+        <v>1.664062358698343</v>
       </c>
       <c r="C2" t="n">
-        <v>11.81238837749762</v>
+        <v>13.03368252158065</v>
       </c>
       <c r="D2" t="n">
-        <v>13.96830633602362</v>
+        <v>18.89962505445535</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21.81934272688536</v>
+        <v>5.757950285407543</v>
       </c>
       <c r="C3" t="n">
-        <v>38.32743037379548</v>
+        <v>51.64483798190346</v>
       </c>
       <c r="D3" t="n">
-        <v>37.92491381505428</v>
+        <v>59.48900213883547</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>35.77390459504952</v>
+        <v>10.41437964665016</v>
       </c>
       <c r="C4" t="n">
-        <v>69.86313012961152</v>
+        <v>76.92091437544184</v>
       </c>
       <c r="D4" t="n">
-        <v>38.84972015245478</v>
+        <v>70.92243590249383</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>36.37375244234433</v>
+        <v>16.56699250916493</v>
       </c>
       <c r="C5" t="n">
-        <v>87.44917675578465</v>
+        <v>102.5190040159732</v>
       </c>
       <c r="D5" t="n">
-        <v>31.48955761371645</v>
+        <v>50.78090000216628</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>26.3648345975481</v>
+        <v>15.8994040702771</v>
       </c>
       <c r="C6" t="n">
-        <v>99.74360325606746</v>
+        <v>112.3021198887927</v>
       </c>
       <c r="D6" t="n">
-        <v>32.4428346345401</v>
+        <v>40.97618567985338</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>12.27675504160636</v>
+        <v>9.701630813366979</v>
       </c>
       <c r="C7" t="n">
-        <v>71.44472568115313</v>
+        <v>80.00851090529807</v>
       </c>
       <c r="D7" t="n">
-        <v>33.23706852727577</v>
+        <v>39.16584291322225</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.841398840268521</v>
+        <v>7.844164156932015</v>
       </c>
       <c r="C8" t="n">
-        <v>32.29459073119883</v>
+        <v>38.97047512007713</v>
       </c>
       <c r="D8" t="n">
-        <v>31.71045084717197</v>
+        <v>38.38633523605029</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.103124566674919</v>
+        <v>8.320311793491715</v>
       </c>
       <c r="C9" t="n">
-        <v>23.18593553119691</v>
+        <v>31.8390597964283</v>
       </c>
       <c r="D9" t="n">
-        <v>31.39530983410874</v>
+        <v>39.60468413702056</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.697662764820988</v>
+        <v>8.256498192715677</v>
       </c>
       <c r="C10" t="n">
-        <v>24.34243432679967</v>
+        <v>34.16482010778901</v>
       </c>
       <c r="D10" t="n">
-        <v>33.31069960509428</v>
+        <v>43.84485247166256</v>
       </c>
     </row>
     <row r="11">
@@ -6193,13 +6193,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.08701569277947</v>
+        <v>7.285549713215578</v>
       </c>
       <c r="C11" t="n">
-        <v>23.27821981539612</v>
+        <v>33.7623035490478</v>
       </c>
       <c r="D11" t="n">
-        <v>35.36157055926586</v>
+        <v>46.91183229972957</v>
       </c>
     </row>
     <row r="12">
@@ -6207,13 +6207,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.254493639578176</v>
+        <v>6.292021036517808</v>
       </c>
       <c r="C12" t="n">
-        <v>22.1305567491316</v>
+        <v>33.62976760897449</v>
       </c>
       <c r="D12" t="n">
-        <v>33.1958351236974</v>
+        <v>44.91201222617883</v>
       </c>
     </row>
     <row r="13">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.601631416254048</v>
+        <v>4.943099690882691</v>
       </c>
       <c r="C13" t="n">
-        <v>21.07321447165778</v>
+        <v>33.30088212805181</v>
       </c>
       <c r="D13" t="n">
-        <v>30.95941385342317</v>
+        <v>42.92691836819179</v>
       </c>
     </row>
     <row r="14">
@@ -6235,13 +6235,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>19.35908298004286</v>
+        <v>31.03599017435442</v>
       </c>
       <c r="D14" t="n">
-        <v>30.11412908006666</v>
+        <v>42.09832330580748</v>
       </c>
     </row>
     <row r="15">
@@ -6249,13 +6249,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>17.5585576904542</v>
+        <v>29.02537087605695</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>40.85052197370977</v>
       </c>
     </row>
     <row r="16">
@@ -6263,13 +6263,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>2.89321048441535</v>
       </c>
       <c r="C16" t="n">
-        <v>16.53263133951629</v>
+        <v>28.51878906066559</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>38.43836786437537</v>
       </c>
     </row>
     <row r="17">
@@ -6277,13 +6277,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>2.833323874456295</v>
       </c>
       <c r="C17" t="n">
-        <v>16.99994324673777</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>35.8887690764464</v>
       </c>
     </row>
     <row r="18">
@@ -6291,13 +6291,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.070104997629023</v>
+        <v>3.21031499288707</v>
       </c>
       <c r="C18" t="n">
-        <v>17.12167996206437</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>30.49799243242716</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0.6018113427032947</v>
+        <v>3.009056713516474</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>24.67426505083508</v>
       </c>
     </row>
     <row r="20">
@@ -6319,13 +6319,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0.672497177409065</v>
+        <v>3.362485887045325</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>15.46743508040849</v>
       </c>
     </row>
     <row r="21">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.268019813039549</v>
+        <v>17.74203632158444</v>
       </c>
       <c r="C21" t="n">
-        <v>75.40570556028534</v>
+        <v>128.6297633314872</v>
       </c>
       <c r="D21" t="n">
-        <v>5.451014859779662</v>
+        <v>5.322610896475333</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.716315971201677</v>
+        <v>1.516800203061322</v>
       </c>
       <c r="C2" t="n">
-        <v>10.73050240741764</v>
+        <v>8.132797981980577</v>
       </c>
       <c r="D2" t="n">
-        <v>20.60492081673206</v>
+        <v>14.89409442112836</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.50870954171587</v>
+        <v>7.382742735936015</v>
       </c>
       <c r="C3" t="n">
-        <v>42.85819602889451</v>
+        <v>70.98526775556563</v>
       </c>
       <c r="D3" t="n">
-        <v>40.30074325933157</v>
+        <v>65.82618356974864</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>39.34746623850791</v>
+        <v>7.951174656694918</v>
       </c>
       <c r="C4" t="n">
-        <v>84.98695351353363</v>
+        <v>99.16633560597032</v>
       </c>
       <c r="D4" t="n">
-        <v>49.13647259755286</v>
+        <v>65.83011056056563</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>46.01942363656924</v>
+        <v>8.933904108645976</v>
       </c>
       <c r="C5" t="n">
-        <v>110.8393158094649</v>
+        <v>67.1024555852695</v>
       </c>
       <c r="D5" t="n">
-        <v>38.41087892865646</v>
+        <v>39.58897617375263</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>38.44033135978387</v>
+        <v>5.997496725243765</v>
       </c>
       <c r="C6" t="n">
-        <v>120.2719477518683</v>
+        <v>52.68941753922207</v>
       </c>
       <c r="D6" t="n">
-        <v>34.97868895460962</v>
+        <v>25.76105975943631</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>22.51736534460484</v>
+        <v>5.150248456478767</v>
       </c>
       <c r="C7" t="n">
-        <v>111.329207913884</v>
+        <v>27.36818075128833</v>
       </c>
       <c r="D7" t="n">
-        <v>35.51275970571987</v>
+        <v>26.94897448157494</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.763480918734528</v>
+        <v>5.757950285407543</v>
       </c>
       <c r="C8" t="n">
-        <v>65.84090978531233</v>
+        <v>23.44904391593506</v>
       </c>
       <c r="D8" t="n">
-        <v>33.46287049925253</v>
+        <v>29.12354564648163</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.768749510154256</v>
+        <v>5.879687000734146</v>
       </c>
       <c r="C9" t="n">
-        <v>32.61562223048752</v>
+        <v>26.07031028627404</v>
       </c>
       <c r="D9" t="n">
-        <v>32.8374972116473</v>
+        <v>33.39218466454675</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.982369599052563</v>
+        <v>5.267076433284139</v>
       </c>
       <c r="C10" t="n">
         <v>26.47773558353648</v>
       </c>
       <c r="D10" t="n">
-        <v>34.02246669067321</v>
+        <v>36.72718161587318</v>
       </c>
     </row>
     <row r="11">
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.442408361716816</v>
+        <v>4.620104696185489</v>
       </c>
       <c r="C11" t="n">
-        <v>26.29905750136355</v>
+        <v>26.83214650476957</v>
       </c>
       <c r="D11" t="n">
-        <v>35.53926689373453</v>
+        <v>35.89465956267188</v>
       </c>
     </row>
     <row r="12">
@@ -6518,13 +6518,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.471459882216721</v>
+        <v>3.688426124855267</v>
       </c>
       <c r="C12" t="n">
-        <v>24.73415166079414</v>
+        <v>27.12078032981814</v>
       </c>
       <c r="D12" t="n">
-        <v>34.28066633689012</v>
+        <v>34.93156506480576</v>
       </c>
     </row>
     <row r="13">
@@ -6535,10 +6535,10 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>22.89435646303562</v>
+        <v>25.49598787928967</v>
       </c>
       <c r="D13" t="n">
-        <v>31.47974013667398</v>
+        <v>34.86186097780424</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>2.458296251434013</v>
       </c>
       <c r="C14" t="n">
-        <v>21.51009220004762</v>
+        <v>24.27567548291088</v>
       </c>
       <c r="D14" t="n">
-        <v>30.42141611149592</v>
+        <v>34.10886048864694</v>
       </c>
     </row>
     <row r="15">
@@ -6560,13 +6560,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>2.150027472300515</v>
       </c>
       <c r="C15" t="n">
-        <v>19.35024725070463</v>
+        <v>24.00864010735575</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>32.6087499965578</v>
       </c>
     </row>
     <row r="16">
@@ -6574,13 +6574,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>2.066578917439536</v>
       </c>
       <c r="C16" t="n">
-        <v>17.77257868998001</v>
+        <v>24.79894700927443</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>30.58536797810513</v>
       </c>
     </row>
     <row r="17">
@@ -6588,13 +6588,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>2.361103228713579</v>
       </c>
       <c r="C17" t="n">
-        <v>17.47216389248049</v>
+        <v>26.9165768073348</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>25.97213551584937</v>
       </c>
     </row>
     <row r="18">
@@ -6602,13 +6602,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>2.140209995258047</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>28.89283493598363</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>21.40209995258047</v>
       </c>
     </row>
     <row r="19">
@@ -6616,13 +6616,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0.6018113427032947</v>
+        <v>2.407245370813179</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>31.29418982057133</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>13.23984953947248</v>
       </c>
     </row>
     <row r="20">
@@ -6630,13 +6630,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>13.4499435481813</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>97.51209072431442</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>4.03498306445439</v>
       </c>
     </row>
     <row r="21">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.472814648280793</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>84.06916479315893</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>6.538712817245695</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
